--- a/excel_system/modules/서무규정.xlsx
+++ b/excel_system/modules/서무규정.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C689"/>
+  <dimension ref="A1:C518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1584,47 +1584,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>[행정업무의 운영 및 혁신에 관한 규정] 제44조의2</t>
+          <t>[행정업무의 운영 및 혁신에 관한 규정] 제45조(협의체 구성 및 업무협약 체결)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>제44조의2</t>
+          <t>제45조(협의체 구성 및 업무협약 체결)
+행정기관은 행정업무 혁신의 효율적인 수행을 위하여 필요한 경우 관련 행정기관과 협의체를 구성하거나 행정업무 혁신의 목적, 협력 범위 및 기능 분담 등에 관한 업무협약을 체결할 수 있다.&lt;개정 2016. 4. 26., 2023. 6. 27.&gt;</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>[행정업무의 운영 및 혁신에 관한 규정] 제44조의3</t>
+          <t>[행정업무의 운영 및 혁신에 관한 규정] 제46조(혁신책임관)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
-        <is>
-          <t>제44조의3</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>[행정업무의 운영 및 혁신에 관한 규정] 제45조(협의체 구성 및 업무협약 체결)</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>제45조(협의체 구성 및 업무협약 체결)
-행정기관은 행정업무 혁신의 효율적인 수행을 위하여 필요한 경우 관련 행정기관과 협의체를 구성하거나 행정업무 혁신의 목적, 협력 범위 및 기능 분담 등에 관한 업무협약을 체결할 수 있다.&lt;개정 2016. 4. 26., 2023. 6. 27.&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>[행정업무의 운영 및 혁신에 관한 규정] 제46조(혁신책임관)</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
         <is>
           <t>제46조(혁신책임관)
 ① 행정기관의 장은 소속 기획조정실장 또는 이에 준하는 직위의 공무원을 해당 행정기관의 행정업무 혁신을 총괄하는 책임관(이하 “혁신책임관”이라 한다)으로 임명하여야 한다.&lt;개정 2023. 6. 27.&gt;
@@ -1642,13 +1618,13 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제46조의2(행정업무혁신시스템의 구축ㆍ운영)</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>제46조의2(행정업무혁신시스템의 구축ㆍ운영)
 ① 행정안전부장관은 행정기관이 제41조제2항 각 호의 업무를 원활하게 수행할 수 있도록 전자적 시스템(이하 “행정업무혁신시스템”이라 한다)을 구축할 수 있다.&lt;개정 2023. 6. 27.&gt;
@@ -1659,13 +1635,13 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제46조의3(행정업무혁신시스템의 활용 촉진)</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>제46조의3(행정업무혁신시스템의 활용 촉진)
 ① 행정기관의 장은 소관 업무 중 행정업무혁신시스템을 이용하여 업무를 수행한 실적 등 행정업무혁신시스템 활용 실태를 평가ㆍ분석하고 그 활용을 촉진하여야 한다.&lt;개정 2016. 4. 26., 2023. 6. 27.&gt;
@@ -1675,13 +1651,13 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제46조의4(행정정보시스템의 상호 연계 및 통합)</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>제46조의4(행정정보시스템의 상호 연계 및 통합)
 ① 행정기관의 장은 행정업무 혁신의 원활한 추진을 위하여 행정기관 간 행정정보시스템의 상호 연계나 통합을 적극적으로 추진하여야 한다.&lt;개정 2016. 4. 26., 2023. 6. 27.&gt;
@@ -1691,13 +1667,13 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제46조의5(행정협업조직의 설치)</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>제46조의5(행정협업조직의 설치)
 ① 행정기관의 장은 다수의 행정기관이 수행하는 사무의 목적, 대상 또는 관할구역 등이 유사하거나 연관성이 높은 경우에는 관련 기능, 업무처리절차 및 정보시스템 등을 연계ㆍ통합하거나 시설ㆍ인력 등을 공동으로 활용하는 등 협력하여 업무를 수행하는 조직(이하 “행정협업조직”이라 한다)을 설치ㆍ운영할 수 있다.&lt;개정 2016. 4. 26.&gt;
@@ -1708,13 +1684,13 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제46조의6(행정업무 혁신 관련 시설 등의 확보)</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>제46조의6(행정업무 혁신 관련 시설 등의 확보)
 ① 행정기관의 장은 행정업무 혁신을 위하여 필요한 경우 공동시설ㆍ공간ㆍ설비 등을 마련하여 다른 행정기관에 제공할 수 있다.&lt;개정 2023. 6. 27.&gt;
@@ -1724,13 +1700,13 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제46조의7(행정업무 혁신문화의 조성 및 국제협력 등)</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>제46조의7(행정업무 혁신문화의 조성 및 국제협력 등)
 ① 행정안전부장관은 행정업무 혁신에 대한 인식을 높이고, 행정업무 혁신문화를 조성하기 위하여 다음 각 호의 사업을 추진할 수 있다.&lt;개정 2017. 7. 26., 2017. 10. 17., 2023. 6. 27.&gt;
@@ -1747,13 +1723,13 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제46조의8(행정업무 혁신우수기관 포상 및 홍보 등)</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>제46조의8(행정업무 혁신우수기관 포상 및 홍보 등)
 ① 행정안전부장관은 행정업무 혁신의 성과가 우수한 행정기관을 선정하여 포상 또는 홍보할 수 있다.&lt;개정 2017. 7. 26., 2023. 6. 27.&gt;
@@ -1763,13 +1739,13 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제46조의9(행정업무 특별성과 포상금)</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>제46조의9(행정업무 특별성과 포상금)
 ① 행정기관의 장은 소속 직원(해당 행정기관에 파견된 직원을 포함한다. 이하 이 조에서 같다)이 혁신적인 업무 수행으로 다음 각 호의 어느 하나에 해당하는 우수한 성과를 거둔 경우에는 포상금(이하 “특별성과 포상금”이라 한다)을 지급할 수 있다.&lt;개정 2026. 5. 19.&gt;
@@ -1784,51 +1760,26 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>[행정업무의 운영 및 혁신에 관한 규정] 제47조</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>제47조</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>[행정업무의 운영 및 혁신에 관한 규정] 제48조</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>제48조
-삭제&lt;2023. 6. 27.&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제49조(정책연구)</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>제49조(정책연구)
 중앙행정기관(그 소속기관을 포함한다. 이하 이 절에서 같다)의 장은 정책의 개발 또는 주요 정책현안에 대한 조사ㆍ연구 등을 목적으로 정책연구를 수행할 자(이하 “연구자”라 한다)와의 계약을 통하여 정책연구를 하게 할 수 있다.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정 시행규칙] 제35조(정책연구심의위원회의 구성 및 운영)</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>제35조(정책연구심의위원회의 구성 및 운영)
 ① 영 제50조제1항에 따른 정책연구심의위원회(이하 “위원회”라 한다)는 위원장 1명을 포함하여 10명 이상 30명 이하의 위원으로 성별을 고려하여 구성하되, 제2항에 따라 위촉하는 위원의 수가 전체 위원 수의 과반수가 되도록 구성하여야 한다.&lt;개정 2014. 2. 18.&gt;
@@ -1847,13 +1798,13 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제50조(정책연구심의위원회 설치)</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>제50조(정책연구심의위원회 설치)
 ① 중앙행정기관의 장은 제49조에 따른 계약을 통한 정책연구(이하 “정책연구”라 한다)에 관한 다음 각 호의 사항을 심의하기 위하여 정책연구심의위원회(이하 이 절에서 “위원회”라 한다)를 둔다.
@@ -1867,13 +1818,13 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정 시행규칙] 제35조(정책연구심의위원회의 구성 및 운영)</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>제35조(정책연구심의위원회의 구성 및 운영)
 ① 영 제50조제1항에 따른 정책연구심의위원회(이하 “위원회”라 한다)는 위원장 1명을 포함하여 10명 이상 30명 이하의 위원으로 성별을 고려하여 구성하되, 제2항에 따라 위촉하는 위원의 수가 전체 위원 수의 과반수가 되도록 구성하여야 한다.&lt;개정 2014. 2. 18.&gt;
@@ -1895,13 +1846,13 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제51조(연구과제와 연구자의 선정)</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>제51조(연구과제와 연구자의 선정)
 ① 중앙행정기관의 장은 공정하고 투명하게 정책연구가 이루어지도록 위원회의 심의를 거쳐 연구과제를 선정하여야 하며 연구과제별로 담당부서의 과장급 공무원을 과제담당관으로 지정하여야 한다. 다만, 다음 각 호의 어느 하나에 해당하는 경우에는 위원회의 심의를 거치지 아니한다.
@@ -1914,13 +1865,13 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정 시행규칙] 제37조(연구과제 심의 신청 등)</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>제37조(연구과제 심의 신청 등)
 ① 정책연구를 하려는 부서의 장은 영 제51조제1항 각 호 외의 부분 본문에 따라 연구과제 선정에 관하여 위원회의 심의를 거치려면 별지 제10호의2서식의 정책연구과제 심의 신청서와 별지 제10호의3서식의 정책연구과제 차별성 검토보고서를 위원회에 제출하여야 한다. 다만, 선정하려는 연구과제와 유사하거나 중복되는 연구과제에 관한 다른 정책연구가 없는 경우에는 별지 제10호의3서식은 제출하지 아니할 수 있다.&lt;개정 2017. 10. 17.&gt;
@@ -1942,26 +1893,26 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제52조(연구결과의 평가 및 활용)</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>제52조(연구결과의 평가 및 활용)
 중앙행정기관의 장은 정책연구가 종료된 후 그 정책연구결과를 평가하여야 하며, 정책연구 종료일부터 6개월 이내에 정책연구결과 활용상황을 점검하여야 한다. 이 경우 정책연구결과 평가 및 활용상황 점검에 관한 사항은 위원회의 심의를 거쳐야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정 시행규칙] 제41조(연구결과의 평가)</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>제41조(연구결과의 평가)
 ① 영 제52조에 따른 정책연구결과 평가는 과제담당관과 과제담당관이 지정한 외부 전문가 1명이 공동으로 평가하는 방법이나 외부 전문가가 참석하는 정책연구완료 보고회를 개최하여 평가하는 방법으로 하여야 한다.
@@ -1969,26 +1920,26 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제53조(정책연구관리시스템의 구축ㆍ운영)</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>제53조(정책연구관리시스템의 구축ㆍ운영)
 행정안전부장관은 중앙행정기관이 전자적으로 정책연구과정을 관리하고 정책연구결과를 공동으로 이용할 수 있도록 정책연구관리시스템을 구축ㆍ운영하여야 한다.&lt;개정 2013. 3. 23., 2014. 11. 19., 2017. 7. 26.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제54조(정책연구의 공개)</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>제54조(정책연구의 공개)
 ① 중앙행정기관의 장은 다음 각 호의 사항을 그 공개가 가능한 때에 지체 없이 정책연구관리시스템을 통하여 공개하여야 한다.&lt;개정 2014. 2. 18.&gt;
@@ -2001,13 +1952,13 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정 시행규칙] 제42조(연구결과의 공개 등)</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>제42조(연구결과의 공개 등)
 ① 행정기관의 장은 정책연구에 관한 사항이 영 제54조제3항에 따른 비공개대상정보에 해당하면 다른 법령에 특별한 규정이 있는 경우를 제외하고는 2년의 범위에서 비공개 기간을 정하되, 기간의 경과 등으로 비공개의 필요성이 없어지거나 「공공기록물 관리에 관한 법률」 제35조에 따라 공개하는 것으로 재분류된 경우에는 영 제54조제1항 및 제2항에 따라 공개하여야 한다.&lt;개정 2014. 2. 18.&gt;
@@ -2015,13 +1966,13 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제55조(기관별 성과점검 등 관리)</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>제55조(기관별 성과점검 등 관리)
 ① 중앙행정기관의 장은 매년 기관의 정책연구 추진과정, 연구결과의 공개 및 활용상황 등을 점검하여야 한다.
@@ -2031,13 +1982,13 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제56조(다른 법령에 따라 관리되는 정책연구 등)</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>제56조(다른 법령에 따라 관리되는 정책연구 등)
 중앙행정기관이 다음 각 호의 어느 하나에 해당하는 연구 또는 조사를 하는 경우에는 이 절의 규정을 적용하지 아니한다.&lt;개정 2012. 1. 20., 2013. 3. 23., 2014. 11. 19., 2017. 7. 26.&gt;
@@ -2050,13 +2001,13 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제57조(영상회의실의 설치ㆍ운영 및 지정)</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>제57조(영상회의실의 설치ㆍ운영 및 지정)
 ① 행정기관의 장은 다음 각 호의 회의를 개최하기 위하여 영상회의실을 설치ㆍ운영할 수 있다.&lt;개정 2013. 3. 23., 2014. 2. 18.&gt;
@@ -2073,13 +2024,13 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정 시행규칙] 제43조(정부영상회의실 등의 관리ㆍ운영)</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>제43조(정부영상회의실 등의 관리ㆍ운영)
 ① 정부청사관리소장은 정부영상회의실의 관리ㆍ운영을 위하여 다음 각 호의 조치를 하여야 한다.
@@ -2093,52 +2044,26 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>[행정업무의 운영 및 혁신에 관한 규정] 제58조</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>제58조
-삭제&lt;2024. 5. 21.&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>[행정업무의 운영 및 혁신에 관한 규정] 제59조</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>제59조
-삭제&lt;2024. 5. 21.&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제60조(업무의 분장)</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>제60조(업무의 분장)
 각 처리과의 장은 업무를 효율적으로 처리하고 책임소재를 명확하게 하기 위하여 소관 업무를 단위업무별로 분장하되, 소속 공무원 간의 업무량이 균형을 이룰 수 있도록 하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정 시행규칙] 제6조(기안자 등의 표시)</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>제6조(기안자 등의 표시)
 ① 기안문에는 영 제8조제4항에 따라 발의자와 보고자의 직위나 직급의 앞 또는 위에 발의자는 ★표시를, 보고자는 ⊙표시를 한다.
@@ -2148,13 +2073,13 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제61조(업무의 인계ㆍ인수)</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>제61조(업무의 인계ㆍ인수)
 ① 공무원이 조직개편, 인사발령 또는 업무분장 조정 등의 사유로 업무를 인계ㆍ인수할 때에는 해당 업무에 관한 모든 사항이 구체적으로 나타나도록 행정안전부령으로 정하는 바에 따라 업무관리시스템이나 전자문서시스템을 이용하여 인계ㆍ인수하여야 한다.&lt;개정 2013. 3. 23., 2014. 11. 19., 2017. 7. 26.&gt;
@@ -2162,13 +2087,13 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정 시행규칙] 제45조(업무의 인계ㆍ인수)</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>제45조(업무의 인계ㆍ인수)
 ① 영 제61조제1항에 따라 업무관리시스템이나 전자문서시스템을 이용하여 업무를 인계ㆍ인수하는 사람은 별지 제12호서식의 업무인계ㆍ인수서를 작성하여야 한다.
@@ -2176,13 +2101,13 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제62조(업무편람의 작성ㆍ활용)</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>제62조(업무편람의 작성ㆍ활용)
 ① 행정기관이 상당 기간에 걸쳐 반복적으로 하는 업무는 그 업무의 처리가 표준화ㆍ전문화될 수 있도록 업무편람을 작성하여 활용하는 것을 원칙으로 한다.
@@ -2193,13 +2118,13 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정 시행규칙] 제46조(직무편람의 작성ㆍ관리 등)</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>제46조(직무편람의 작성ㆍ관리 등)
 ① 영 제62조제2항제2호에 따른 직무편람(이하 “직무편람”이라 한다)은 특별한 사유가 없으면 행정기관의 직제에 규정된 최하 단위 부서별로 작성하여야 하며, 처리과의 장은 정기적으로 또는 수시로 그 내용을 수정하거나 보완하여야 한다.
@@ -2211,13 +2136,13 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제63조(정책의 실명 관리)</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>제63조(정책의 실명 관리)
 ① 행정기관의 장은 주요 정책의 결정이나 집행과 관련되는 다음 각 호의 사항을 종합적으로 기록ㆍ관리하여야 한다.
@@ -2228,13 +2153,13 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제63조의2(정책실명제 책임관 지정)</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>제63조의2(정책실명제 책임관 지정)
 ① 행정기관의 장은 해당 기관의 정책실명제를 효율적으로 운영하기 위하여 기획조정실장 등 해당 기관의 기획 업무를 총괄하는 직위에 있는 공무원을 정책실명제 책임관으로 지정하여야 한다.
@@ -2247,13 +2172,13 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제63조의3(정책실명제 중점관리 대상 선정)</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>제63조의3(정책실명제 중점관리 대상 선정)
 ① 행정기관의 장은 다음 각 호의 사항 중에서 정책실명제 중점관리 대상사업을 선정하여 관리하여야 한다.&lt;개정 2018. 11. 27.&gt;
@@ -2269,26 +2194,26 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제63조의4(정책실명제 평가)</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>제63조의4(정책실명제 평가)
 행정안전부장관은 정책실명제의 활성화를 위하여 필요한 경우 각 행정기관의 정책실명제 추진실적 등을 평가할 수 있다.&lt;개정 2014. 11. 19., 2017. 7. 26.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제63조의5(정책실명제 세부 규정)</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>제63조의5(정책실명제 세부 규정)
 ① 정책실명제 중점관리 대상사업 선정, 심의위원회의 구성, 정책실명제 추진실적 평가기준 및 그 밖에 정책실명제 운영을 위하여 필요한 세부 사항은 행정안전부장관이 정한다.&lt;개정 2014. 11. 19., 2017. 7. 26.&gt;
@@ -2297,52 +2222,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>[행정업무의 운영 및 혁신에 관한 규정] 제64조</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>제64조
-삭제&lt;2023. 6. 27.&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제65조(행정업무 운영에 관한 교육)</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>제65조(행정업무 운영에 관한 교육)
 행정기관의 장은 소속 공무원에 대하여 매년 1회 이상 행정업무의 효율성 증진을 위한 교육을 하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제66조(행정업무 운영에 관한 감사)</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>제66조(행정업무 운영에 관한 감사)
 행정안전부장관이 필요하다고 인정하면 국무총리의 명을 받아 각급 행정기관에 대하여 이 영에서 규정하는 업무운영에 관한 감사를 할 수 있다.&lt;개정 2013. 3. 23., 2014. 11. 19., 2017. 7. 26.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제67조(문서 미등록자 등에 대한 조치)</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>제67조(문서 미등록자 등에 대한 조치)
 행정기관의 장은 다음 각 호의 어느 하나에 해당하는 공무원에게 징계나 그 밖에 필요한 조치를 하여야 한다.
@@ -2354,26 +2266,26 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제68조(대통령 또는 국무총리 명의로 시행하는 문서에 관한 특례)</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>제68조(대통령 또는 국무총리 명의로 시행하는 문서에 관한 특례)
 법령에 따라 대통령 또는 국무총리 명의로 시행하여야 하는 문서의 형식 및 처리 방법에 관한 사항은 법령에 특별한 규정이 있는 경우를 제외하고는 대통령훈령으로 정한다.</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제69조(국가정보원의 업무운영에 대한 특례)</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>제69조(국가정보원의 업무운영에 대한 특례)
 ① 제8조제3항에 따라 국가정보원이 아닌 행정기관에서 문서를 기안할 경우 국가정보원 소관 사항은 국가정보원에서 따로 기안할 수 있다.
@@ -2382,39 +2294,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>[행정업무의 운영 및 혁신에 관한 규정] 제70조(권한의 위임)</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>제70조(권한의 위임)
 행정안전부장관은 정부영상회의실의 관리ㆍ운영에 관한 권한을 정부청사관리본부장에게 위임한다.&lt;개정 2013. 3. 23., 2014. 11. 19., 2016. 12. 27., 2017. 7. 26.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제1조(목적)</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>제1조(목적)
 이 영은 「지방공무원법」에 따라 지방공무원의 복무에 관한 사항을 규정하는 것을 목적으로 한다.</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제1조의2(근무기강의 확립)</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>제1조의2(근무기강의 확립)
 ① 지방공무원(이하 “공무원”이라 한다)은 법령과 직무상 명령을 준수하여 근무기강을 확립하고 질서를 존중하여야 한다.
@@ -2429,13 +2341,13 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제1조의3(복장 및 복제 등)</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>제1조의3(복장 및 복제 등)
 ① 공무원은 근무 중 그 품위를 유지할 수 있는 단정한 복장을 착용하여야 한다.
@@ -2444,13 +2356,13 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제2조(근무시간 등)</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>제2조(근무시간 등)
 ① 공무원의 1주간 근무시간은 점심시간을 제외하고 40시간으로 하며, 토요일은 휴무함을 원칙으로 한다.
@@ -2461,13 +2373,13 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제2조의2(비상근무의 종류)</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>제2조의2(비상근무의 종류)
 비상근무는 그 상황에 따라 다음 각 호와 같이 구분하여 발령한다.
@@ -2487,13 +2399,13 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제2조의3(비상근무의 발령)</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>제2조의3(비상근무의 발령)
 ① 지방자치단체의 장과 지방의회의 의장은 제2조의2 각 호의 구분에 따라 소속 공무원에 대하여 비상근무를 발령할 수 있다. 이 경우 특별시장ㆍ광역시장ㆍ특별자치시장ㆍ도지사 또는 특별자치도지사(이하 “시ㆍ도지사”라 한다)와 시ㆍ도의회의 의장은 행정안전부장관에게, 교육감은 교육부장관에게 비상근무의 종류, 발령일시, 발령사유 등을 지체 없이 보고하여야 하며, 시장ㆍ군수 또는 자치구의 구청장은 지체 없이 특별시장ㆍ광역시장 또는 도지사를, 시ㆍ군ㆍ자치구의회의 의장은 지체 없이 시ㆍ도의회의 의장을 거쳐 행정안전부장관에게 보고하여야 한다.&lt;개정 2013. 3. 23., 2014. 11. 19., 2017. 7. 26., 2021. 11. 30.&gt;
@@ -2506,13 +2418,13 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제2조의4(비상근무 요령)</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>제2조의4(비상근무 요령)
 ① 지방자치단체의 장과 지방의회의 의장은 제2조의3에 따라 비상근무를 발령하거나 비상근무가 발령된 때에는 청사 등 중요 시설물에 대한 경계와 경비를 강화하여야 한다.&lt;개정 2021. 11. 30.&gt;
@@ -2528,13 +2440,13 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제2조의5(비상근무 발령의 해제)</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>제2조의5(비상근무 발령의 해제)
 ① 행정안전부장관(교육감 소속 공무원에 대하여 비상근무 발령을 해제하는 경우에는 교육부장관을 말한다) 및 지방자치단체의 장과 지방의회의 의장은 제2조의2 각 호에 규정된 비상근무 발령 상황이 종료된 경우에는 비상근무 발령을 해제하여야 한다.&lt;개정 2013. 3. 23., 2014. 11. 19., 2017. 7. 26., 2021. 11. 30.&gt;
@@ -2543,26 +2455,26 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제2조의6(위임규정)</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>제2조의6(위임규정)
 비상근무의 발령 및 그에 따른 복무 등에 관하여 이 영에서 규정한 사항을 제외하고는 해당 지방자치단체의 장이나 지방의회의 의장이 정한다.&lt;개정 2021. 11. 30.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제3조(근무시간 등의 변경)</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>제3조(근무시간 등의 변경)
 ① 지방자치단체의 장과 지방의회의 의장은 직무의 성질, 지역 또는 기관의 특수성에 따라 필요하다고 인정할 때에는 근무시간 또는 근무일을 변경할 수 있다.&lt;개정 2018. 12. 18., 2021. 11. 30.&gt;
@@ -2572,13 +2484,13 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제4조(시간외근무 및 공휴일 등 근무)</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>제4조(시간외근무 및 공휴일 등 근무)
 ① 지방자치단체의 장과 지방의회의 의장은 민원편의 등 공무수행상 필요하다고 인정할 때에는 제2조 및 제3조에도 불구하고 근무시간 외의 근무를 명하거나 토요일 또는 공휴일의 근무를 명할 수 있다.&lt;개정 2017. 4. 25., 2021. 11. 30.&gt;
@@ -2591,13 +2503,13 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제4조의2(출장공무원)</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>제4조의2(출장공무원)
 ① 상사의 명에 따라 정규 근무지 외의 장소에서 공무를 수행하는 공무원(이하 “출장공무원”이라 한다)은 해당 공무 수행을 위해 전력을 다해야 하며, 사적인 일을 위하여 시간을 소비해서는 안 된다.&lt;개정 2019. 12. 31.&gt;
@@ -2608,13 +2520,13 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제4조의3(선거 관련 사무 수행 공무원의 휴무)</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>제4조의3(선거 관련 사무 수행 공무원의 휴무)
 ① 지방자치단체의 장과 지방의회의 의장은 다음 각 호의 어느 하나에 해당하는 선거 관련 사무를 수행한 공무원에 대하여 해당 선거일(사전투표일을 포함한다. 이하 이 조에서 같다) 다음 정상근무일을 휴무하게 해야 한다. 다만, 해당 기관의 업무 사정이나 그 밖의 부득이한 사유가 있는 경우에는 해당 선거일부터 6개월 이내의 범위에서 다른 정상근무일을 지정하여 휴무하게 할 수 있다.
@@ -2627,26 +2539,26 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제5조(현업 공무원 등의 근무시간과 근무일)</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>제5조(현업 공무원 등의 근무시간과 근무일)
 지방자치단체의 장과 지방의회의 의장은 현업 기관 및 직무의 성질상 상시근무체제를 유지할 필요가 있거나 토요일 또는 공휴일에도 정상근무를 할 필요가 있는 기관 소속 공무원에 대해서는 그 근무시간과 근무일을 따로 정할 수 있다.&lt;개정 2021. 11. 30.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제6조(휴가의 종류)</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>제6조(휴가의 종류)
 ① 공무원의 휴가는 연가ㆍ병가ㆍ공가(公暇) 및 특별휴가로 구분한다.&lt;개정 2019. 12. 31.&gt;
@@ -2655,13 +2567,13 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제7조(연가일수 및 연가보상비의 지급)</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>제7조(연가일수 및 연가보상비의 지급)
 ① 공무원의 재직기간별 연가일수는 다음과 같다. 다만, 법 제27조제2항제2호ㆍ제3호 및 제9호에 따라 임용된 경력직공무원 및 특수경력직공무원의 재직기간이 5년 미만인 경우로서 지방자치단체의 조례로 정하는 공무원 경력 외의 유사경력이 있는 경우에는 5년 미만의 재직기간별 연가일수에 각각 3일을 더한다.&lt;개정 2013. 12. 11., 2018. 12. 18., 2023. 7. 18., 2024. 7. 2.&gt;
@@ -2677,13 +2589,13 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제7조의2(연가 일수의 공제)</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>제7조의2(연가 일수의 공제)
 ① 결근 일수ㆍ정직 일수ㆍ직위해제 일수 및 강등 처분에 따라 직무에 종사하지 못하는 일수는 연가 일수(결근의 경우에 한정하여 제7조의10에 따른 저축연가 일수를 포함한다)에서 뺀다. 다만, 「지방공무원 임용령」 제31조의6제2항제2호에 따른 기간 중 직무에 종사하지 못하는 일수는 연가 일수에서 빼지 않되, 본문에 따라 이미 빼어 사용하지 못하게 된 연가 일수는 저축연가 일수에 더한다.&lt;개정 2019. 12. 31., 2020. 10. 20.&gt;
@@ -2706,26 +2618,26 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제7조의3(연가 당겨쓰기)</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>제7조의3(연가 당겨쓰기)
 지방자치단체의 장과 지방의회의 의장은 소속 공무원에게 제7조제1항에 따른 연가 일수(제7조의10에 따른 저축연가 일수를 포함한다)가 없거나 재직기간별 연가 일수를 초과하는 휴가 사유가 발생한 경우에는 같은 항에 따른 재직기간 구분 중 그 다음 재직기간의 연가 일수를 다음 표에 따라 미리 사용하게 할 수 있다.&lt;개정 2019. 12. 31., 2021. 11. 30.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제7조의4(연가 사용의 권장)</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>제7조의4(연가 사용의 권장)
 ① 지방자치단체의 장과 지방의회의 의장은 소속 공무원의 연가 사용을 촉진하기 위해 매년 3월 31일까지 소속 공무원이 그 해에 최소한으로 사용해야 할 10일 이상의 권장 연가 일수와 미사용 권장 연가 일수에 대한 연가보상비 지급 여부를 정해 공지해야 한다.&lt;개정 2019. 12. 31., 2021. 11. 30.&gt;
@@ -2737,13 +2649,13 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제7조의5(병가)</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>제7조의5(병가)
 ① 지방자치단체의 장과 지방의회의 의장은 소속 공무원이 다음 각 호의 어느 하나에 해당할 경우에는 연 60일의 범위에서 병가를 허가할 수 있다. 이 경우 질병이나 부상으로 인한 지각ㆍ조퇴 및 외출은 누계 8시간을 병가 1일로 계산하고, 제7조의2제7항 본문에 따라 연가 일수에서 빼는 병가는 병가 일수에 산입하지 않는다.&lt;개정 2021. 11. 30.&gt;
@@ -2756,13 +2668,13 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제7조의6(공가)</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>제7조의6(공가)
 지방자치단체의 장과 지방의회의 의장은 소속 공무원(제10호의 경우 「공무원의 노동조합 설립 및 운영 등에 관한 법률 시행령」 제3조의3제2항에 따른 근무시간 면제자는 제외한다)이 다음 각 호의 어느 하나에 해당할 때에는 직접적으로 필요한 기간 또는 시간을 공가로 허가해야 한다.&lt;개정 2011. 9. 29., 2012. 8. 31., 2016. 11. 29., 2018. 12. 18., 2019. 4. 16., 2019. 12. 24., 2020. 10. 20., 2021. 11. 30., 2021. 12. 31., 2023. 12. 5., 2026. 6. 23.&gt;
@@ -2787,13 +2699,13 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제7조의7(특별휴가)</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>제7조의7(특별휴가)
 ① 공무원의 특별휴가는 이 영에서 정하는 바에 따른다. 다만, 이 영에서 정하지 아니하는 사항은 지방자치단체의 조례로 정하는 바에 따른다.
@@ -2835,13 +2747,13 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제7조의8(휴가기간 중의 토요일 또는 공휴일)</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>제7조의8(휴가기간 중의 토요일 또는 공휴일)
 휴가기간 중의 토요일 또는 공휴일은 그 휴가일수에 산입하지 않는다. 다만, 다음 각 호의 어느 하나에 해당하는 경우에는 그 휴가일수에 토요일 또는 공휴일을 산입한다.&lt;개정 2019. 12. 31., 2021. 12. 31.&gt;
@@ -2854,26 +2766,26 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제7조의9(시간선택제공무원 등에 대한 휴가에 관한 특례)</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>제7조의9(시간선택제공무원 등에 대한 휴가에 관한 특례)
 「지방공무원 임용령」 제3조의2제2호에 따른 시간선택제임기제공무원, 같은 조 제3호에 따른 한시임기제공무원, 같은 영 제3조의5제1항에 따른 시간선택제채용공무원 및 같은 영 제38조의15제1항 본문에 따른 시간선택제전환공무원(이하 “시간선택제공무원등”이라 한다)에 대한 휴가는 제4조제2항, 제7조제1항, 제7조의4제1항ㆍ제2항, 제7조의5, 제7조의7제7항ㆍ제8항 및 제7조의8에도 불구하고 별표 2에 따른다.&lt;개정 2019. 4. 16., 2019. 12. 31., 2020. 10. 20.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제7조의10(연가의 저축)</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>제7조의10(연가의 저축)
 ① 공무원은 연가보상비 지급대상인 연가 일수 및 제4조제4항에 따라 전환된 연가 일수 중 사용하지 않고 남은 연가 일수를 그 해의 마지막 날을 기준으로 이월ㆍ저축하여 사용할 수 있다.&lt;개정 2023. 6. 13.&gt;
@@ -2885,26 +2797,26 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제7조의11(10일 이상 연속된 연가 사용의 보장)</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>제7조의11(10일 이상 연속된 연가 사용의 보장)
 지방자치단체의 장과 지방의회의 의장은 소속 공무원이 제7조제1항에 따른 연가 일수 또는 제7조의10제1항에 따른 저축연가 일수를 활용하여 10일 이상 연속된 연가 일수 사용을 신청한 경우에는 공무 수행에 특별한 지장이 없으면 이를 허가해야 한다. 이 경우 지방자치단체의 장과 지방의회의 의장은 연가 사용에 따른 업무대행자 지정, 인력 보충 등 원활한 업무 수행과 자유로운 연가 사용 보장에 필요한 조치를 해야 한다.&lt;개정 2021. 11. 30.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제8조(공무원의 범위)</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>제8조(공무원의 범위)
 법 제3조제2항에 따른 공무원의 범위는 다음 각 호와 같다.&lt;개정 2013. 12. 11., 2018. 12. 18.&gt;
@@ -2914,13 +2826,13 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제9조(정치적 행위)</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>제9조(정치적 행위)
 ① 법 제57조에 따른 정치적 행위는 다음 각 호의 어느 하나에 해당하는 정치적 목적을 가진 것을 말한다.
@@ -2936,13 +2848,13 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제10조(영리업무의 금지)</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>제10조(영리업무의 금지)
 공무원은 다음 각 호의 어느 하나에 해당하는 행위를 함으로써 공무원의 직무상의 능률을 저해하거나, 공무에 대하여 부당한 영향을 주거나, 해당 지방자치단체의 이익과 상반되는 이익을 취득하거나, 해당 지방자치단체에 대하여 불명예스러운 영향을 초래할 우려가 있는 경우에는 이에 종사할 수 없다.
@@ -2954,13 +2866,13 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제11조(겸직 허가)</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>제11조(겸직 허가)
 ① 공무원이 제10조의 영리업무에 해당하지 아니하는 다른 직무를 겸직하려는 경우에는 지방자치단체의 장이나 지방의회의 의장의 사전 허가를 받아야 한다.&lt;개정 2021. 11. 30.&gt;
@@ -2969,26 +2881,26 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제12조(면직된 공무원의 근무)</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>제12조(면직된 공무원의 근무)
 지방자치단체의 장과 지방의회의 의장은 사무 인계 또는 남은 업무의 처리를 위하여 필요한 경우에는 면직된 공무원을 15일 한도로 계속 근무하게 할 수 있다.&lt;개정 2021. 11. 30.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>[지방공무원 복무규정] 제13조(근무시간 면제 시간의 사용)</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>제13조(근무시간 면제 시간의 사용)
 ① 「공무원의 노동조합 설립 및 운영 등에 관한 법률 시행령」 제3조의3제2항에 따른 근무시간 면제자는 같은 영 제3조의4에 따라 근무시간의 전부 또는 일부에 대하여 면제 시간을 사용할 수 있다.
@@ -2997,25 +2909,25 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>[경상북도 공무원 여비 조례] 제1조(목적)</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>제1조(목적)이 조례는 경상북도 지방공무원(이하 "공무원"이라 한다)이 공무로 국내 또는 국외여행을 할 때에 지급하는 여비에 관한 사항을 규정함을 목적으로 한다.&lt;개정 '13.9.16&gt;</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>[경상북도 공무원 여비 조례] 제2조(상시출장 공무원의 여비)</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>제2조(상시출장 공무원의 여비)  ①상시출장을 요하는 공무원에 대하여는 예산의 범위안에서 상시출장여비(이하 "월액여비"라 한다)를 일괄 지급할 수 있다.
 ②제1항의 경우에 출장일수가 월 15일 이상인 때에는 월액여비 전액을 지급하고, 출장일수가 월 15일 미만인 때에는 월액여비를 15로 나눈 금액에 출장일수를 곱하여 산정한 금액을 지급한다. 이 경우에 출장일수는 관할구역외에 출장한 일수와 본 업무 외의 용무로 출장한 일수는 통산하지 아니한다.&lt;개정 '13.9.16&gt;
@@ -3023,38 +2935,38 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>[경상북도 공무원 여비 조례] 제3조(여비의 지급 구분)</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>제3조(여비의 지급 구분)①도지사는 「공무원여비규정」(이하 "영"이라 한다) 별표 1 제1호가목을 적용한다.&lt;개정 '13.9.16&gt;
 ②제1항 이외의 공무원에게는 계급별로 영 별표 1의 각 호를 적용한다.&lt;개정 '13.9.16, '16.05.26.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>[경상북도 공무원 여비 조례] 제4조(운임 및 숙박비 지급)</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>제4조(운임 및 숙박비 지급)공무원이 공무로 국내여행을 할 때 운임과 숙박비는 영 별표 2에 따라 지급한다.&lt;개정 '13.9.16., 2019. 10. 31., 2023. 7. 13.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>[경상북도 공무원 여비 조례] 제5조(여비 부정 수령시 환수 및 가산징수)</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>제5조(여비 부정 수령시 환수 및 가산징수)① 도지사는 공무원이 여비를 부정 수령한 경우 부정 수령금액을 환수한다.&lt;신설 '13.9.16&gt;
 ② 제1항의 여비 부정 수령이란 다음 각 호와 같다.&lt;신설 '13.9.16&gt;
@@ -3064,13 +2976,13 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>[경상북도 공무원 여비 조례] 제6조(공무원 여비 규정의 준용)</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>제6조(공무원 여비 규정의 준용) 공무원의 여비지급에 관하여 조례에 정한 것을 제외하고는 영을 준용하되, 다음 각 호에 따른다.&lt;개정 '13.9.16, '16.05.26.&gt;
 1. 영 제8조의2제5항은 준용하지 아니한다.&lt;개정 11.09.26, '13.9.16, '16.05.26., 2019. 10. 31.&gt;
@@ -3084,142 +2996,25 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 여비 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>부 칙
-이 조례는 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 여비 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>부 칙(2010. 11. 15)
-이 조례는 2011년 1월 1일부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 여비 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>부 칙(2011.09.26)
-이 조례는 공포한 날로부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 여비 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>부 칙(2013.9.16)
-이 조례는 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 여비 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>부 칙(2016.05.26.)
-이 조례는 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 여비 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>부 칙&lt;2019. 10. 31.&gt;
-이 조례는 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 여비 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;2022. 7. 11.&gt;
-이 조례는 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 여비 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;2023. 7. 13.&gt;
-이 조례는 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 여비 조례] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>별지/별표
-&lt;삭제 2023.7.13.&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제1조(목적)</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>제1조(목적)이 조례는 경상북도 공무원의 복무에 관한 사항을 규정함을 목적으로 한다.</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제2조(복무선서)</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>제2조(복무선서)① 경상북도 공무원(이하 “공무원”이라 한다)은「지방공무원법」(이하 “법”이라 한다) 제47조의 규정에 따라 취임할 때에 경상북도지사(이하 “도지사”라 한다) 앞에서 선서를 하여야 한다.
 ② 선서는 별표 1의 선서문에 따른다.
@@ -3227,25 +3022,25 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제3조(책임완수)</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>제3조(책임완수)공무원은 주민 전체의 봉사자로서 직무를 민주적이고 능률적으로 수행하기 위하여 창의와 성실로써 맡은 바 책임을 완수하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제4조(비밀엄수)</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>제4조(비밀엄수)공무원 또는 공무원이었던 사람은 다음 각 호의 사항을 타인에게 누설하거나 부당한 목적을 위하여 사용하여서는 아니된다.
 1. 법령에 따라 비밀로 지정된 사항
@@ -3255,26 +3050,26 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제5조(근무기강 확립)</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>제5조(근무기강 확립)① 공무원은 법령 및 직무상의 명령을 준수하여 근무기강을 확립하고 질서를 존중하여야 한다.
 ② 공무원은 별표 3의 공직자 행동규범을 준수하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+    <row r="155">
+      <c r="A155" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제6조(친절·공정)</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>제6조(친절·공정)① 공무원은 공과 사를 명백히 분별하고, 주민의 권리를 존중하며, 친절하고, 신속·정확하게 모든 업무를 처리하여야 한다.
 ② 공무원은 주권을 가진 국민의 수임자로서 국민의 신임을 받기위하여 노력하여야 한다.
@@ -3282,13 +3077,13 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제7조(당직 및 비상근무)</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>제7조(당직 및 비상근무)① 휴일 또는 근무시간 외의 화재ㆍ도난 그 밖의 사고의 경계와 문서처리 및 업무연락을 하기 위한 일직ㆍ숙직 근무자 및 방호원 등의 당직근무자는 모든 사고를 방지하여야 하며 사고가 발생한 때에는 신속하게 필요한 조치를 취하여야 한다.
 ② 소속기관의 장(「지방자치단체의 행정기구와 정원기준 등에 관한 규정」제2조 각 호의 행정기관의 장을 말한다. 이하 같다)은 전시ㆍ사변 또는 천재지변 기타 이에 준하는 비상사태의 발생 또는 이의 대비를 위한 훈련의 경우에는 이에 따른 근무상의 필요한 조치를 하여야 한다.
@@ -3298,26 +3093,26 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제8조(겸임근무)</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>제8조(겸임근무)① 법 제30조의3에 따라 겸임근무하는 사람은 복무에 관하여 원 소속기관의 장의 지휘, 감독을 받는다. 다만, 겸임업무와 관련한 복무에 관하여는 겸임기관의 장의 지휘ㆍ감독을 받는다.
 ② 겸임근무하는 사람이 겸임업무와 관련하여 징계사유에 해당하게 된 때에는 그 겸임기관의 장은 해당 겸임근무자의 원 소속기관의 장에게 그 사실을 통보하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제9조(파견근무)</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>제9조(파견근무)① 법 제30조의4에 따라 다른 기관에서 파견근무하는 사람은 복무에 관하여 파견받은 기관의 장의 지휘ㆍ감독을 받는다.
 ② 다른 기관에서 파견근무하는 사람이 그 파견기간 중에 징계사유에 해당 하게 된 때에는 파견받은 기관의 장은 원 소속기관의 장에게 그 사실을 통보하여야 한다.
@@ -3325,62 +3120,62 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제10조(면직된 공무원의 근무)</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>제10조(면직된 공무원의 근무)도지사는 사무인계 또는 남은 업무처리를 위하여 필요한 경우에는 면직된 공무원을 15일 한도로 계속 근무하게 할 수 있다.</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제11조(복장 등)</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>제11조(복장 등)① 공무원은 근무 중 그 품위를 유지할 수 있는 단정한 복장을 착용하여야 한다.
 ② 공무원의 신분증 발급 및 휴대 등에 관하여는「국가공무원 복무규칙」을 준용한다.</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제12조(휴가의 종류)</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>제12조(휴가의 종류)공무원의 휴가는 연가, 병가, 공가 및 특별휴가로 구분한다.</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
+    <row r="162">
+      <c r="A162" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제13조(경력직공무원 및 특수경력직공무원의 연가가산)</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>제13조(경력직공무원 및 특수경력직공무원의 연가가산)「지방공무원 복무규정」(이하 “영”이라 한다) 제7조제1항의 단서에 따른 재직기간 5년 미만의 경력직공무원 및 특수경력직공무원의 연가가산을 위한 민간경력 인정은 별표 4와 같다. &lt;개정 2023.12.28.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
+    <row r="163">
+      <c r="A163" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제14조(연가계획 및 허가)</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>제14조(연가계획 및 허가)① 도지사는 공무원이 자유롭게 연가를 사용하여 심신을 새롭게 하고 공ㆍ사 생활의 만족도를 높여 직무 생산성을 높일 수 있도록 특정한 계절에 편중되지 아니하게 연가계획을 수립하여 실시하여야 한다.
 ② 연가는 오전 또는 오후의 반일단위로 허가할 수 있으며, 반일 연가 2회는 연가 1일로 계산한다.
@@ -3389,39 +3184,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
+    <row r="164">
+      <c r="A164" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제14조의2(시간외근무시간 연가 전환)</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>제14조의2(시간외근무시간 연가 전환)영 제4조제4항에 따라 공무원은 시간외근무수당을 지급받는 대신에 해당 근무시간을 연가로 전환하여 사용할 수 있으며, 그 운영에 필요한 사항은 도지사가 따로 정한다.
 [본조신설 2025. 7. 14.]</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제15조(연가일수에서의 공제)</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>제15조(연가일수에서의 공제)① 질병이나 부상 외의 사유로 인한 지각ㆍ조퇴 및 외출은 누계 8시간을 연가 1일로 한다.
 ② 제16조제1항에 따른 병가 중 연간 6일을 초과하는 병가일수는 연가일수에서 공제한다. 다만, 의사의 진단서가 첨부된 병가일수는 연가일수에는 공제하지 아니한다.</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제16조(병가)</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>제16조(병가)① 소속기관의 장은 소속 공무원이 다음 각 호의 어느 하나에 해당하는 경우에는 연간 60일의 범위에서 병가를 허가할 수 있다. 이 경우 질병이나 부상으로 인한 지각ㆍ조퇴 및 외출은 누계 8시간을 병가 1일로 계산하고, 제15조제2항에 따라 연가일수에서 공제하는 병가는 병가일수에 산입하지 아니한다.
 1. 질병 또는 부상으로 인하여 직무를 수행할 수 없는 경우
@@ -3431,13 +3226,13 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
+    <row r="167">
+      <c r="A167" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제17조(특별휴가)</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>제17조(특별휴가)① 공무원은 본인이 결혼하거나 그 밖의 경조사가 있을 경우에는 별표 5의 기준에 따라 경조사 휴가를 얻을 수 있다.
 ② 한국방송통신대학교에 재학 중인 공무원은「한국방송통신대학교 설립 및 운영에 관한 법률」에 따른 출석수업에 참석하기 위하여 영 제7조제1항의 연가일수를 초과하는 출석수업기간에 대한 수업 휴가를 얻을 수 있다. 다만, 시간선택제 공무원의 경우에는 그렇지 않다.
@@ -3455,270 +3250,86 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제18조(휴가기간의 초과)</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>제18조(휴가기간의 초과)이 조례가 정한 휴가일수를 초과한 휴가는 결근으로 본다.</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제19조(공무외의 국외여행)</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>제19조(공무외의 국외여행)공무원은 휴가기간의 범위에서 공무외의 목적으로 국외여행을 할 수 있다.</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
+    <row r="170">
+      <c r="A170" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제20조(준용)</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>제20조(준용)이 조례에 규정되지 아니한 사항은 영을 준용한다.</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
+    <row r="171">
+      <c r="A171" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제21조(시행규칙)</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>제21조(시행규칙)이 조례 시행에 관하여 필요한 사항은 규칙으로 정한다.</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;2023.01.02.&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 제1조(시행일)</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>제1조(시행일)
-이 조례는 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
+    <row r="172">
+      <c r="A172" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] 제2조(장기재직휴가에 관한 경과조치)</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>제2조(장기재직휴가에 관한 경과조치)
 이 조례 시행 전에 종전의 규정에 따라 장기재직 휴가를 사용한 공무원은 기존 사용한 휴가일수 및 사용횟수를 포함하여 제17조제4항의 개정 규정에 따른 휴가일수 및 사용횟수를 부여한다.</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;2023.12.28.&gt;
-이 조례는 공포한 날부터 시행한다. 다만, 제17조제4항의 개정규정은 2024년 1월 1일부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;2024.05.23.&gt;
-이 조례는 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;2025. 7. 14.&gt;
-이 조례는 공포한 날부터 시행한다. 다만, 별표5의 개정규정 중 입양 관련 부분은 2025년 7월 19일부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 별표 1] 선서문</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>[별표 1] 선서문</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 별표 2] 선서의 절차 및 방법</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>[별표 2] 선서의 절차 및 방법</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 별표 3] 공직자의 행동규범</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>[별표 3] 공직자의 행동규범</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 별표 4] 경력직공무원 및 특수경력직공무원 연가가산 방법</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>[별표 4] 경력직공무원 및 특수경력직공무원 연가가산 방법</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 복무 조례] 별표 5] 경조사별 휴가일수표</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>[별표 5] 경조사별 휴가일수표</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
+    <row r="173">
+      <c r="A173" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제1조(목적)</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>제1조(목적) 이 조례는 도의 취득·보관·사용·처분등에 관한 사항을 규정함으로써 물품의 효율적이고 적정한 관리를 도모함을 목적으로 한다.</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+    <row r="174">
+      <c r="A174" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제2조(관리책임)</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>제2조(관리책임) ①도지사는 모든 물품을 효율적으로 운영·관리하여야 한다.
 ②도지사는 물품관리공무원(이하 “물품관리관”이라 한다)을 지정하고, 용도에 따라 그 소관에 속하는 물품관리책임공무원(이하 “물품출납원("분임물품출납원"을 포함한다)”이라 한다)을 지정할 수 있다.
@@ -3727,13 +3338,13 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+    <row r="175">
+      <c r="A175" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제3조(물품관리관등의 직무)</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>제3조(물품관리관등의 직무)①물품관리관은 물품의 관리·청구·검수·반환·수리 기타 출납보관에 관한 사무를 처리한다.
 ②물품운용관은 물품관리관의 지휘감독을 받아 물품관리에 관한 사무를 처리한다. &lt;신설 '06. 5. 4&gt;
@@ -3741,87 +3352,87 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+    <row r="176">
+      <c r="A176" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제4조(관리서무의 위임)</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>제4조(관리서무의 위임)도지사는 필요하다고 인정할 경우에는 시장·군수에게 소유 물품관리에 관한 사무의 일부를 위임할 수 있다.</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+    <row r="177">
+      <c r="A177" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제5조(물품의 분류)</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>제5조(물품의 분류)물품의 품종, 상태의 구분의 ［별표 1］에 의한다.</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
+    <row r="178">
+      <c r="A178" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제6조(물품의 정리구분)</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>제6조(물품의 정리구분)물품의 정리구분은 ［별표2］에 의한다.</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제7조(연도구분)</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>제7조(연도구분)①물품의 회계연도는 매년 1월 1일부터 동년 12월 31일에 종료한다.
 ②물품출납의 소속년도는 그 출납을 집행한 날이 속하는 연도에 의한다.</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제8조(물품매입등의 요구)</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>제8조(물품매입등의 요구)물품을 매입·수리·제조할 필요가 있을 때에는 주관과장은 물품출납원을 거쳐 재무관에게 규칙이 정하는 물품 매입, 수리제조품의 요구서에 의하여 요구하여야 한다. &lt;개정 '95. 1. 13., 2022. 9. 22.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
+    <row r="181">
+      <c r="A181" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제9조(물품매입요구의 심사)</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>제9조(물품매입요구의 심사)①주관과장이 제8조의 규정에 의거 물품매입요구를 하였을 때에는 물품관리관은『공유재산 및 물품관리법 시행령』(이하"영"이라한다) 제58조의 규정에 의하여 정수관리대상물품에 포함되었는지의 여부와 물품수급관리계획에 반영된 물품인지의 여부를 심사하여 물품을 매입토록 하여야 한다. &lt;개정 '06. 5. 4., 2022. 9. 22.&gt;
 ②재무관은 제1항의 심사에 의하지 아니하고는 제8조에서 요구한 물품의 매입등을 할 수 없다. &lt;개정 2022. 9. 22.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제10조(일상경비에 의한 물품매입)</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>제10조(일상경비에 의한 물품매입) ①일상경비에 의한 물품의 매입은 소모품에 한한다. &lt;개정 '89. 1. 30, '90. 5. 14., 2022. 9. 22.&gt;
 ②물품을 매입하고자 하는 경우에는 규칙이 정하는 물품매입(수리·제조)품의요구서에 물품출납원의 확인을 거쳐 물품을 매입하여야 한다. &lt;개정 '92. 6. 18&gt;
@@ -3830,13 +3441,13 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
+    <row r="183">
+      <c r="A183" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제11조(기증품의 취득)</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>제11조(기증품의 취득)①물품의 기부 또는 증여의 신고를 받은 주관부서의 물품운용관 또는 물품출납원(분임물품출납원이 있는 경우는 분임물품출납원)은 물품관리관의 사전협의후 기부심사위원회 심의를 받아야 한다.  &lt;개정 '89. 1. 30, '06. 5. 4&gt;
 ②주관부서의 장은 기부심사위원회의 심의결과를 물품관리관에게 통보하여야 한다. &lt;개정 '89. 1. 30, '90. 5. 14, '06. 5. 4&gt;
@@ -3845,50 +3456,37 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 제11조의2</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>제11조의2 &lt;삭제 '06. 5. 4&gt;
-제2절 출납</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
+    <row r="184">
+      <c r="A184" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제12조(분류전환)</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>제12조(분류전환) 물품관리관이 물품의 품종 또는 품목의 분류전환을 결정하였을 때에는 물품출납원에게 통지하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
+    <row r="185">
+      <c r="A185" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제13조(소모품으로서 정리하는 물품)</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>제13조(소모품으로서 정리하는 물품) 비품의 수리 또는 보충의 목적으로 수입한 물품 및 급여하는 물품은 소모품으로 정리할 수 있다.</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
+    <row r="186">
+      <c r="A186" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제14조(물품의 가격)</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>제14조(물품의 가격) 물품의 가격은 다음 구분에 의한다.
 1. 구입물품은 그 매입가격
@@ -3901,38 +3499,38 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제14조의2(물품의 무상대부)</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>제14조의2(물품의 무상대부)영 제75조제4호에 따라 소관 물품을 무상으로 대부할 수 있는 대상은 「사회적기업 육성법 시행령」제2조각 호에 따른 취약계층에 해당하는 주민으로 한다.
 [본조신설 2022. 9. 22.]</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
+    <row r="188">
+      <c r="A188" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제15조(잔품의 이월)</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>제15조(잔품의 이월) 물품출납원은 연도말 현재의 물품에 대하여는 이월의 출납명령이 있는 것으로 보고 다음 연도의 동일품목에 이월하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+    <row r="189">
+      <c r="A189" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제16조(불용품의 소요조회와 불용결정)</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>제16조(불용품의 소요조회와 불용결정) ①물품관리관은 다음 각호의 1에 해당하는 물품에 대하여 국가 및 지방자치단체에 소요조회를 한 후 소요기관이 없는 때와 임산물, 축산물 기타 생산물을 매각하는 때에는 규칙이 정하는 불용결정통보서에 의거 도지사의 결재를 받아 불용의 결정을 하여야 한다. &lt;개정 '89. 1. 30&gt;
 1. 사용할 필요가 없게된 물품으로서 앞으로도 사용할 전망이 없는 것
@@ -3955,13 +3553,13 @@
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+    <row r="190">
+      <c r="A190" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제17조(불용품의 매각)</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>제17조(불용품의 매각) ①제16조의 규정에 의하여 불용의 결정을 한 물품으로서 다음 각호의 1에 해당하는 경우를 제외하고는 불용품 매각처분조서를 작성하고 이를 매각 처분하여야 한다.
 1. 매각대금이 매각에 요하는 비용을 보상하고 남음이 없을 때
@@ -3981,13 +3579,13 @@
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
+    <row r="191">
+      <c r="A191" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제18조(불용품의 폐기)</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B191" t="inlineStr">
         <is>
           <t>제18조(불용품의 폐기)①제17조 제1항 각호에 해당하는 물품은 물품관리관이 규칙이 정하는 불용품폐기(해체) 조서를 작성하고 이를 소각 또는 폐기하여야 한다.
 ②제1항의 규정에 의한 폐기처분은 지정하는 공무원의 참관 하에 하여야 한다. &lt;개정 2023.5.25.&gt;
@@ -3996,51 +3594,51 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
+    <row r="192">
+      <c r="A192" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제19조(보관의 구분)</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B192" t="inlineStr">
         <is>
           <t>제19조(보관의 구분) ①물품은 보관상 이를 재고품·공용품의 2종으로 구분한다.
 ②공용품중 각자 전용하는 것은 전용품으로, 공동 사용하는 것은 공용품으로 한다.</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+    <row r="193">
+      <c r="A193" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제20조(보관책임)</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>제20조(보관책임)재고품은 물품출납원 또는 분임물품출납원이, 공용품은 물품출납원, 분임물품출납원 또는 물품운용관이, 전용품은 물품운용관이 지정된 경우 물품운용관의 지도감독을 받아 전용자가 책임을 지고 이를 보관하여야 한다. &lt;개정 '06. 5. 4&gt;</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
+    <row r="194">
+      <c r="A194" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제21조(일시보관)</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>제21조(일시보관)①물품출납원 또는 물품운용관은 물품의 보관상 특히 필요하다고 인정할 때에는 도지사 또는 청·소의 장의 결재를 받아 금고 기타 신용이 확실한 자에게 물품을 일시 보관시킬 수 있다. &lt;개정 '06. 5. 4&gt;
 ②제1항의 규정에 의해 물품을 일시 보관할 때에는 물품수탁서를 받은 다음 수취인에게 물품을 인도하여야 한다. &lt;개정 '06. 5. 4&gt;</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
+    <row r="195">
+      <c r="A195" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제22조(물품의 망실·훼손)</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>제22조(물품의 망실·훼손)①물품운용관 또는 분임물품 출납원은 그 보관의 물품을 망실·훼손하였을 때에는 즉시 사유를 상세히 기입한 경위서를 작성하여 물품출납원에게 보고하여야 한다. 다만, 전용자의 보관물품으로써 분임물품출납원으로부터 교부받은 것일 때에는 그 분임물품출납원을 경유하여야 한다. &lt;개정 '06. 5. 4&gt;
 ②물품출납원은 제1항의 보고를 받았을 때에는 사실을 조사하고, 의견을 부쳐 물품관리관에게 보고하여야 한다. &lt;개정 '06. 5. 4&gt;
@@ -4049,13 +3647,13 @@
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+    <row r="196">
+      <c r="A196" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제23조(물품보관자의 변상책임)</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B196" t="inlineStr">
         <is>
           <t>제23조(물품보관자의 변상책임)①도지사는 제22조의 보고를 받았을 때에는 다음의 구분에 따라 보관책임자에게 기한을 정하여 변상을 명하여야 한다.
 1. 물품을 망실하였을 때에는 대품을 납입시키거나 또는 상당한 기액을 변상시킨다.
@@ -4065,13 +3663,13 @@
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+    <row r="197">
+      <c r="A197" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제24조(물품출납원의 장부)</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>제24조(물품출납원의 장부) ①물품출납원은 규칙이 정하는 서식에 의거 다음의 장부를 비치하고 정리하여야 한다.
 1. 물품수입 및 출급원장
@@ -4085,52 +3683,52 @@
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
+    <row r="198">
+      <c r="A198" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제25조(장부의 작성)</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>제25조(장부의 작성) ①비품관계 장표를 제외한 장부는 매년도 별도 작성하여야 한다. 다만, 기재사항이 적은 장부는 연도구분을 명백히 하여 구 장부를 계속 사용할 수 있다. &lt;개정 '06. 5. 4&gt;
 ②제1항에서 규정하는 장부는 전산입력처리로 장부작성에 갈음한다. &lt;개정 '06. 5. 4&gt;</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
+    <row r="199">
+      <c r="A199" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제26조(증빙서류 및 장부의 보존)</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>제26조(증빙서류 및 장부의 보존)물품관리관·물품출납원·물품운용관 또는 분임물품출납원은 그 소관에 속하는 증빙서류 및 장부를 5년간 보관하여야 한다. &lt;개정 '06. 5. 4&gt;
 제5절 검사 및 인계</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
+    <row r="200">
+      <c r="A200" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제27조(물품출납사무의 검사)</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>제27조(물품출납사무의 검사)①영 제90조의 규정에 의한 물품관리에 관한 검사는 물품관리관(과장이 있는 청·소포함)이, 기타청·소의 경우에는 청·소의 장이 하여야 한다. &lt;개정 '06. 5. 4&gt;
 ②제1항의 규정에 불구하고 도지사 또는 청·소의 장이 필요다하고 인정하는 경우에는 소속직원중에서 검사원을 임명하여 물품의 출납사무를 검사하게 할 수 있다.</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
+    <row r="201">
+      <c r="A201" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제28조(검사 또는 검수자의 지정 및 참관)</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>제28조(검사 또는 검수자의 지정 및 참관)①제27조의 검사를 집행함에 있어서 검사를 받을 물품출납원이 부득이한 사유로 검사를 받을 수 없을 때에는 그 검사원은 소속 직원중에서 지정한 자로 하여금 참관하게 하여야 한다. &lt;개정 2023.5.25.&gt;
 ②물품의 매입, 수리, 수선 기타의 검사 또는 검수는 물품출납원(분임물품출납원이 있는 경우에는 분임물품출납원)이 행하고 회계과 관계공무원이 참관한다. 다만, 특히 필요한 경우에는 재무관이 따로 검사 또는 검수자를 지정할 수 있다. &lt;개정 '89. 1. 30., 2022. 9. 22., 2023.5.25.&gt;
@@ -4139,340 +3737,112 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
+    <row r="202">
+      <c r="A202" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제29조(물품검사서)</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B202" t="inlineStr">
         <is>
           <t>제29조(물품검사서)①검사원은 제27조 및 제28조 제1항의 규정에 의하여 검사를 하였을 때에는 규칙이 정하는 서식에 의한 물품검사서를 2통 작성하고 1통을 당해 물품출납원 또는 참관자에게 교부하고 다른 1통은 도지사 또는 청·소의 장에게 제출하여야 한다. &lt;개정 2023.5.25.&gt;
 ②제1항의 검사서에는 검사원과 당해 물품출납원 또는 참관자가 연서 날인하여야 한다. &lt;개정 2023.5.25.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 제30조</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>제30조 &lt;삭제 '06. 5. 4&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
+    <row r="203">
+      <c r="A203" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제31조(물품출납사무의 인계)</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>제31조(물품출납사무의 인계) 물품출납원이 경질되었을 때에는 인계자는 발령일로부터 5일 이내에 그 사무를 인수자에게 인계하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
+    <row r="204">
+      <c r="A204" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제32조(인계의 절차)</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>제32조(인계의 절차)①제31조의 규정에 의한 인계를 할 때에는 인계 전일로서 물품출납부를 마감하여 인계연월일을 기입하고 인계 인수자가 연서 날인하여야 한다.
 ②&lt;삭제 '89. 1. 30&gt;</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
+    <row r="205">
+      <c r="A205" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제33조(타직원에 의한 인계)</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B205" t="inlineStr">
         <is>
           <t>제33조(타직원에 의한 인계)물품출납원이 사망 기타의 사고로 말미암아 본인이 인계할 수 없을 때에는 도지사 또는 청·소의 장이 그 소속 직원중에서 지정한 자로 하여금 제32조의 규정에 의한 인계사무를 처리하게 하여야 한다. &lt;개정 '90. 10. 25&gt;</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
+    <row r="206">
+      <c r="A206" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제34조(기구개편에 수반하는 사무인계)</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>제34조(기구개편에 수반하는 사무인계) 물품출납원은 기구 개편으로 인하여 그 소관 사무의 전부 또는 일부가 그 소속을 달리할 때에는 제31조 내지 제33조의 규정에 준하여 인계하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
+    <row r="207">
+      <c r="A207" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제35조(물품운영상황의 공개)</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>제35조(물품운영상황의 공개)도지사는 「공유재산 및 물품관리법」 (이하“법”이라한다) 제92조에 따라 중요 물품의 증감 및 현재액이 포함된 결산서 등을 경상북도 홈페이지를 통하여 회계연도마다 1회 이상 도민에게 공개한다.
 [본조신설 2022. 9. 22.]</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>부칙
-①(시행일) 이 조례는 공포한 날로부터 시행한다.
-②(경과조치) 이 조례 시행당시 종전의 규정에 의하여 결정된 사항에 대하여는 종전의 예에 의한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>부칙(1989. 1. 30)
-이 조례는 공포한 날로부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>부칙(1990. 5. 14)
-이 조례는 공포한 날로부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>부칙(1990. 10. 25)
-이 조례는 공포한 날로부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>부칙(1992. 6. 18)
-이 조례는 공포한 날로부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>부칙(1995. 1. 13)
-이 조례는 공포한 날로부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>부칙(1999. 1. 14)
-이 조례는 공포한 날로부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>부 칙(2006.5.4)
-이 조례는 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;2022. 9. 22.&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 제1조(시행일)</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>제1조(시행일)
-이 조례는 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 제2조(다른 조례의 개정)</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>제2조(다른 조례의 개정)
-경상북도 공유재산 관리조례 일부를 다음과 같이 개정한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 제7조</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>제7조를 다음과 같이 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
+    <row r="208">
+      <c r="A208" t="inlineStr">
         <is>
           <t>[경상북도 물품관리 조례] 제7조(공유재산 운영상황의 공개)</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>제7조(공유재산 운영상황의 공개) 도지사는 법 제92조 및 영 제52조에 따른 공유재산의 증감 및 현황이 포함된 결산서 등을 경상북도 홈페이지를 통하여 회계연도마다 1회 이상 도민에게 공개한다.</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 부칙</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;조례 제4823호, 2023. 5. 25.&gt; (어려운 용어 정비를 위한 99개 경상북도 조례의 일부개정에 관한 조례)
-이 조례는 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 별표 1] 물품의 품종․상태 구분</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>[별표 1] 물품의 품종․상태 구분</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리 조례] 별표 2] 물품출납이동부의 정리구분</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>[별표 2] 물품출납이동부의 정리구분</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
+    <row r="209">
+      <c r="A209" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제1조(목적)</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>제1조(목적) 이 규칙은 경상북도물품관리조례(이하 "조례"라 한다)의 시행에 관하여 필요한 사항을 규정함을 목적으로 한다.</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
+    <row r="210">
+      <c r="A210" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제2조(물품사무관리자의 지정)</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>제2조(물품사무관리자의 지정) ①조례 제2조의 규정에 의하여 물품관리관, 물품운용관, 물품출납원, 분임물품출납원을 다음 구분에 의하여 각각 지정한다. &lt;개정'91.7.18, '06.5.4, '09.2.26&gt;
 1. 도 본청
@@ -4489,73 +3859,61 @@
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
+    <row r="211">
+      <c r="A211" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제3조(물품매입등의 품의요구서)</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>제3조(물품매입등의 품의요구서) 조례 제8조의 규정에 의한 물품매입, 수리ㆍ제조품의 요구서는 별지 제1호서식에 의한다.&lt;개정'09.2.26&gt;</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
+    <row r="212">
+      <c r="A212" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제4조(기증품조서)</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>제4조(기증품조서)①조례 제11조의 규정에 의한 기증품조서 및 수령증은 별지 제2호서식에 의한다.&lt;개정 '89.1.30, '09.2.26&gt;</t>
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
+    <row r="213">
+      <c r="A213" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제5조(불용결정 통보서)</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>제5조(불용결정 통보서)①조례 제16조의 규정에 의한 불용결정 통보서는 별지 제4호서식에 의한다.&lt;개정'09.2.26&gt;</t>
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
+    <row r="214">
+      <c r="A214" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제6조(불용품 폐기조서)</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>제6조(불용품 폐기조서)①조례 제18조의 규정에 의한 불용품폐기(해체)조서는 별지 제5호서식에 의한다.&lt;개정 09.2.26&gt;</t>
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 제7조</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>제7조&lt;삭제 89.01.30&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
+    <row r="215">
+      <c r="A215" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제8조(출납명령)</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>제8조(출납명령)①물품관리관이 물품을 출납하게 하고자 할 때에는 물품관리관에게 출납하여야 할 물품의 분류를 명백히 하여 출납을 명령하여야 한다.
 ②물품은 제1항의 출납명령이 없으면 출납할 수 없다.
@@ -4566,37 +3924,37 @@
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
+    <row r="216">
+      <c r="A216" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제9조(출납명령 발행요건)</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>제9조(출납명령 발행요건)물품관리관이 출납명령을 하고자 할 때에는 품명, 수량, 납품자, 수령자, 출납의 시기 및 이유의 적정여부를 조사하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
+    <row r="217">
+      <c r="A217" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제10조(물품의 청구)</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B217" t="inlineStr">
         <is>
           <t>제10조(물품의 청구)분임물품출납원이 물품을 교부받고자 할 때에는 청구 및 출급증에 의하여 주관과장을 거쳐 물품관리관에게 청구하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
+    <row r="218">
+      <c r="A218" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제11조(물품의 교부)</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B218" t="inlineStr">
         <is>
           <t>제11조(물품의 교부)①물품관리관은 제10조의 청구를 받았을 때에는 이를 심사한 후 물품출납원에게 필요한 조치를 명하여야 한다.
 ②물품출납원은 제1항의 명령을 받아 물품을 교부할 때에는 청구 및 출급증에 수령인(분임물품출납원을 지정한 경우에는 분임물품출납원의 수령인)을 받아야 한다.
@@ -4604,26 +3962,26 @@
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
+    <row r="219">
+      <c r="A219" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제12조(소모품의 교부)</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>제12조(소모품의 교부)①상시 소모하는 물품, 우표, 수입증지 기타에 대하여는 수요예상량을 미리 분임물품출납원에게 교부할 수 있다.
 ②우표의 출납은 별지 제9호서식에 의한 우표출납부에 의하여 정리하여야 한다.&lt;개정'09.2.26&gt;</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
+    <row r="220">
+      <c r="A220" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제13조(물품의 반납)</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>제13조(물품의 반납)①분임물품출납원은 물품중 사용 불능물품과 공사(수리등을 포함)후 발생품, 초과품에 대하여는 별지 제10호서식에 의한 반납 및 인수증을 주관과장을 거쳐 물품관리관에게 즉시 반납하여야 한다.&lt;개정'09.2.26&gt;
 ②공유재산관리 담당부서에서는 공유재산 관리과정에서 그 재산이 물품으로 편입되었을 때에는 반납 및 영수증에 의하여 물품관리관에게 통지하여야 한다.
@@ -4633,13 +3991,13 @@
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
+    <row r="221">
+      <c r="A221" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제14조(관리전환 및 양여)</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B221" t="inlineStr">
         <is>
           <t>제14조(관리전환 및 양여)①물품관리관(물품운용관)이 물품을 관리전환 하고자 할 때에는 "별지 제11호서식"에 의한 물품관리전환(물품무상양여) 합의서를 작성하여 안전행정실장(소방본부장, 직속기관·사업소의 장, 도의회사무처장)의 결재를 받아야 한다.&lt;개정 '89.1.30, '91.7.18, '94.12.13, '09.2.26, 2023.12.28.&gt;
 ②제1항의 규정에 의거 물품관리전환을 합의하였을 때에는 안전행정실장의 결재를 받아 물품관리전환(물품무상양여)합의서에 의거 인계인수한다.&lt;개정'89.1.30, '09.2.26, 2023.12.28.&gt;
@@ -4647,13 +4005,13 @@
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
+    <row r="222">
+      <c r="A222" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제14조의2(물품의 대부)</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>제14조의2(물품의 대부)① 「공유재산 및 물품 관리법」 제74조에 따라 물품을 대부받고자 하는 사람은 별지 제23호서식의 물품 대부신청서를 작성하여 도지사에게 대부 신청을 하여야 하며, 도지사는 대부 가능 여부를 심사하여 처리하여야 한다.
 ② 도지사는 제1항에 따라 소관 물품을 대부하기로 결정한 때에는 별지 제24호서식의 물품 대부계약서에 따라 대부계약을 체결하여야 하며, 계약서 1부는 대부계약의 당사자에게 교부하고, 나머지 1부는 보관하여야 한다.
@@ -4667,13 +4025,13 @@
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
+    <row r="223">
+      <c r="A223" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제15조(기재를 생략하는 물품)</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B223" t="inlineStr">
         <is>
           <t>제15조(기재를 생략하는 물품)다음에 게기하는 물품은 물품출납원의 보관으로 하고 물품출납에 관한 장부에 기재를 요하지 아니한다.
 1. 구입과 동시에 소모하는 것
@@ -4682,13 +4040,13 @@
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
+    <row r="224">
+      <c r="A224" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제16조(불용의 결정)</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>제16조(불용의 결정)도지사는 본청 또는 소방본부, 직속기관, 지역본부, 사업소, 도의회사무처 소속 직원에 대하여 다음 각 호의 구분에 따라 불용결정을 위임하여 처리하게 할 수 있다.
 1. 본청
@@ -4704,13 +4062,13 @@
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
+    <row r="225">
+      <c r="A225" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제17조(물품출납원의 장부서식)</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t>제17조(물품출납원의 장부서식)조례 제24조의 규정에 의한 장부의 서식은 다음 각호와 같다.
 1. 물품수입 및 출급원장 별지 제13호서식&lt;개정'09.2.26&gt;
@@ -4722,910 +4080,75 @@
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
+    <row r="226">
+      <c r="A226" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제18조(물품검수조서 등)</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>제18조(물품검수조서 등)조례 제28조의 규정에 의한 물품검수조서는 별지 제19호서식에 의하고, 조례 제29조의 규정에 의한 물품검사서는 별지 제20호서식에 의한다.&lt;개정'09.2.26&gt;</t>
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 제19조</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>제19조&lt;삭제'06.5.4&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제20조(물품 재고조사 등)</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>제20조(물품 재고조사 등)조례 제32조의 규정에 의한 사무인계보고서는 "별지 제22호서식"에 의한다.&lt;개정'09.2.26&gt;</t>
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>부 칙
-①(시행일)
-이 규칙은 공포한 날로부터 시행한다.
-②(경과조치)
-이 규칙 시행당시 종전의 규정에 의하여 결정된 사항에 대하여는 종전의 예에 의한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>부 칙(1989.01.30)
-이 규칙은 공포한 날로부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>부 칙(1991.07.18)
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>부 칙(1991.11.28)
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>부 칙(1994.12.13)
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>부 칙(1999. 1.14 )
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>부 칙(2006.5.4)
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>부 칙(2006.12.28)</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 제1조(시행일)</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>제1조(시행일)
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 제2조(다른 규칙의 개정)</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>제2조(다른 규칙의 개정)
-⑫경상북도물품관리조례시행규칙 일부를 다음과 같이 개정한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 제2조</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>제2조제1항제1호중 “재정과장”을 “회계과장”으로 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 제16조</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>제16조제1호중 “자치행정국장”을“행정지원국장”으로 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>부칙(2009. 2. 26)
-①(시행일)
-이 규칙은 공포한 날부터 시행한다.
-②(경과조치)
-이 규칙 시행당시 종전의 규정에 의하여 처리중인 사무에 대하여는 종전의 규정에 의한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;2021. 6. 7.&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 제1조(시행일)</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>제1조(시행일)
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
+    <row r="228">
+      <c r="A228" t="inlineStr">
         <is>
           <t>[경상북도 물품관리조례 시행규칙] 제2조(물품의 대부에 대한 경과조치)</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>제2조(물품의 대부에 대한 경과조치)
 이 규칙 시행 당시 물품의 대부 계약을 체결한 자는 제14조의2 개정규정에 따라 계약을 체결한 것으로 본다.</t>
         </is>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;규칙 제3041호, 2023. 12. 28.&gt; (경상북도 행정기구 설치 조례 시행규칙)
-이 규칙은 2023년 12월 31일부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>부 칙(2024.10.7.)
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별표] 물품의 대부료 산정기준</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>[별표] 물품의 대부료 산정기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제01호서식</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>별지제01호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제02호서식</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>별지제02호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제03호서식</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>별지제03호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제04호서식</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>별지제04호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제05호서식</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>별지제05호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제06호서식</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>별지제06호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제07호서식</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>별지제07호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제08호서식</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>별지제08호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제09호서식</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>별지제09호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제10호서식</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>별지제10호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제11호서식</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>별지제11호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제12호서식</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>별지제12호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제13호서식</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>별지제13호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제14호서식</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>별지제14호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제15호서식</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>별지제15호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제16호서식</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>별지제16호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제17호서식</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>별지제17호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제18호서식</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>별지제18호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제19호서식</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>별지제19호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제20호서식</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>별지제20호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제21호서식</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>별지제21호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지제22호서식</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>별지제22호서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지 제23호서식] 물품 대부신청서</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>[별지 제23호서식] 물품 대부신청서</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>[경상북도 물품관리조례 시행규칙] 별지 제24호서식] 물품 대부계약서</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>[별지 제24호서식] 물품 대부계약서</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
+    <row r="229">
+      <c r="A229" t="inlineStr">
         <is>
           <t>[경상북도 물품조달규정] 제1조(목적)</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
+      <c r="B229" t="inlineStr">
         <is>
           <t>제1조(목적)이 규정은 도 본청이 행하는 물품의 구매·제조 및 관리에 관하여 필요한 사항을 규정함으로써 조달업무의 원활을 기함을 목적으로 한다.</t>
         </is>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
+    <row r="230">
+      <c r="A230" t="inlineStr">
         <is>
           <t>[경상북도 물품조달규정] 제2조(범위)</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>제2조(범위)①이 규정에 의하여 도 본청이 구매·제조 및 관리할 물품은 예산명세서에 정한 품목중 늘 사용되고 각 실·과에 공통적으로 수요되는 물품(이하 "공통물품"이라 한다)에 한한다.
 ②전항의 공통품목은 회계관리과장이 정한다. &lt;개정 '06.11.6, 2024.06.27.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
+    <row r="231">
+      <c r="A231" t="inlineStr">
         <is>
           <t>[경상북도 물품조달규정] 제3조(물품요구서 제출)</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
+      <c r="B231" t="inlineStr">
         <is>
           <t>제3조(물품요구서 제출)①수요기관은 매 회계년도내에 소요되는 연간수요 공통품목을 기본운영계획 시행예정표에 맞추어 연도 개시후 10일 이내에 물품요구서로 경리관에게 제출하여야 한다.
 ②기본운영계획이 수정될 때에는 전항에 준하여 수정요구서를 제출하여야 한다.
@@ -5633,213 +4156,126 @@
         </is>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
+    <row r="232">
+      <c r="A232" t="inlineStr">
         <is>
           <t>[경상북도 물품조달규정] 제4조(수요량 결정)</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
+      <c r="B232" t="inlineStr">
         <is>
           <t>제4조(수요량 결정)경리관은 전조의 물품요구서를 집계하여 분기별 수요량을 결정한다. 다만, 필요에 따라 수요기관과 합의를 얻어 수요량을 조절할 수 있다.</t>
         </is>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
+    <row r="233">
+      <c r="A233" t="inlineStr">
         <is>
           <t>[경상북도 물품조달규정] 제5조(일괄구입)</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
+      <c r="B233" t="inlineStr">
         <is>
           <t>제5조(일괄구입)전조의 기별수요 공통품목은 긴급·불가피한 경우를 제외하고는 이를 일괄 구입한다.</t>
         </is>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
+    <row r="234">
+      <c r="A234" t="inlineStr">
         <is>
           <t>[경상북도 물품조달규정] 제6조(공급)</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B234" t="inlineStr">
         <is>
           <t>제6조(공급)물품관리관은 수요기관의 예산추산 범위 안에서 물품청구서를 받았을 때에는 이를 심사한후 분임물품출납원에게 수령인을 받고, 물품을 교부한다.</t>
         </is>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>[경상북도 물품조달규정] 부칙</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>부 칙
-이 규정은 1971년 8월 1일부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>[경상북도 물품조달규정] 부칙</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>부 칙(2006.11.6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>[경상북도 물품조달규정] 제1조(시행일)</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>제1조(시행일)
-이 규정은 발령한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>[경상북도 물품조달규정] 제2조(생 략)</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>제2조(생 략)</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>[경상북도 물품조달규정] 부칙</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;훈령 제1641호, 2024.06.27.&gt; (경상북도 공무원 정원배정 및 세부분장사무에 관한 규정 일부개정령)</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>[경상북도 물품조달규정] 제1조(시행일)</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>제1조(시행일)
-이 영은 2024년 7월 1일부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>[경상북도 물품조달규정] 제2조</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>제2조~제4조 생략</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
+    <row r="235">
+      <c r="A235" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제1조(목적)</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>제1조(목적) 이 영은 국가공무원이 공무(公務)로 여행을 하는 경우에 지급하는 여비에 관한 사항을 규정함으로써 공무의 원활한 수행과 국가예산의 적정한 지출을 도모함을 목적으로 한다.
 [전문개정 2010. 11. 10.]</t>
         </is>
       </c>
     </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
+    <row r="236">
+      <c r="A236" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제2조(여비의 종류)</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
+      <c r="B236" t="inlineStr">
         <is>
           <t>제2조(여비의 종류) 여비는 운임ㆍ일비ㆍ숙박비ㆍ식비ㆍ이전비ㆍ가족여비 및 준비금 등으로 구분한다.</t>
         </is>
       </c>
     </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
+    <row r="237">
+      <c r="A237" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제3조(여비의 지급 구분)</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr">
+      <c r="B237" t="inlineStr">
         <is>
           <t>제3조(여비의 지급 구분) 국가공무원(이하 “공무원”이라 한다)의 여비는 별표 1의 여비 지급 구분표에 따라 지급한다.
 [전문개정 2010. 11. 10.]</t>
         </is>
       </c>
     </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
+    <row r="238">
+      <c r="A238" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제4조(여비의 계산)</t>
         </is>
       </c>
-      <c r="B364" t="inlineStr">
+      <c r="B238" t="inlineStr">
         <is>
           <t>제4조(여비의 계산) 여비는 일반적인 경로 및 방법에 의하여 계산한다. 다만, 공무의 형편상 또는 천재지변이나 그 밖의 부득이한 사유로 일반적인 경로 및 방법에 의한 여행을 하기 곤란한 경우에는 실제로 여행한 경로 및 방법에 의하여 계산한다.
 [전문개정 2010. 11. 10.]</t>
         </is>
       </c>
     </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
+    <row r="239">
+      <c r="A239" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제5조(여행일수의 계산)</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr">
+      <c r="B239" t="inlineStr">
         <is>
           <t>제5조(여행일수의 계산) 여행일수는 여행을 위하여 실제로 필요한 일수에 의하여 계산한다. 다만, 공무의 형편상 또는 천재지변이나 그 밖의 부득이한 사유로 늘어나는 일수는 여행일수에 포함한다.
 [전문개정 2010. 11. 10.]</t>
         </is>
       </c>
     </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
+    <row r="240">
+      <c r="A240" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제6조(근무지 외 거주지 등으로부터 직접 여행 시의 여비)</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B240" t="inlineStr">
         <is>
           <t>제6조(근무지 외 거주지 등으로부터 직접 여행 시의 여비) 근무지 또는 출장지 외의 곳에 거주하거나 체재(滯在)하는 공무원이 그 거주지 또는 체재지로부터 목적지까지 직접 여행하는 경우에는 그곳에서 목적지에 이르는 여비를 지급한다. 다만, 그 여비는 근무지 또는 출장지로부터 목적지까지의 여비를 초과하지 못한다.
 [전문개정 2010. 11. 10.]</t>
         </is>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
+    <row r="241">
+      <c r="A241" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제7조(여비의 구분 계산)</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>제7조(여비의 구분 계산) ① 여행 중 법령이나 계급ㆍ직무등급 또는 호봉의 변경 등에 의하여 여비를 구분하여 계산할 필요가 있는 경우에는 그 사유가 발생한 날을 기준으로 계산한다. 다만, 해당 공무원이 이동 중인 경우에는 그 사유가 발생한 후 최초의 목적지에 도착한 날을 기준으로 구분하여 계산한다.
 ② 여행 중 같은 날에 여비를 달리하여야 할 경우에는 그 중 많은 금액을 기준으로 지급한다.
@@ -5847,26 +4283,26 @@
         </is>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제8조(근무지 외의 거주자를 임용한 경우의 여비)</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>제8조(근무지 외의 거주자를 임용한 경우의 여비) 근무지 외의 곳에 거주하는 사람을 임용한 경우에는 공무원 부임(赴任)의 예에 준하여 새로운 직(職)에 해당하는 여비를 지급할 수 있다.
 [전문개정 2010. 11. 10.]</t>
         </is>
       </c>
     </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
+    <row r="243">
+      <c r="A243" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제8조의2(여비의 결제와 정산 등)</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>제8조의2(여비의 결제와 정산 등) ① 국내 여행자 및 국외 여행자가 여비 중 운임(국외 여행의 운임은 제외한다)과 숙박비를 결제할 때에는 「국고금관리법」 제24조제5항에 따른 정부구매카드(이하 “정부구매카드”라 한다) 또는 「여신전문금융업법」 제2조제3호에 따른 신용카드(이하 “신용카드”라 한다)를 사용해야 한다. 다만, 출장지에서 정부구매카드 또는 신용카드를 사용할 수 없는 경우 등 특별한 사유가 있는 경우에는 그렇지 않다. &lt;개정 2011. 2. 9., 2017. 1. 31., 2021. 11. 30.&gt;
 ② 국내 여행자 및 국외 여행자는 여행을 마친 날의 다음 날부터 기산(起算)하여 2주일 이내에, 운임과 숙박비의 세부 사용내용을 확인할 수 있는 증거서류를 갖추어 회계 관계 공무원에게 운임과 숙박비의 정산을 신청하여야 한다. 다만, 국외 여행자의 숙박비 정산 신청기한은 인사혁신처장이 정하는 바에 따라 연장할 수 있다. &lt;개정 2011. 2. 9., 2013. 3. 23., 2014. 11. 19., 2017. 1. 31.&gt;
@@ -5879,13 +4315,13 @@
         </is>
       </c>
     </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
+    <row r="244">
+      <c r="A244" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제9조(운임의 구분)</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>제9조(운임의 구분) ① 운임은 철도운임ㆍ선박운임ㆍ항공운임ㆍ자동차운임으로 구분하되, 철도운임은 철도여행에, 선박운임은 수로(水路)여행에, 항공운임은 항공여행에, 자동차운임은 철도 외의 육로여행에 각각 지급한다.
 ② 국외 여행의 경우 제1항의 운임에는 통행세를 포함한다.
@@ -5893,13 +4329,13 @@
         </is>
       </c>
     </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
+    <row r="245">
+      <c r="A245" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제10조(철도운임의 지급)</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t>제10조(철도운임의 지급) ① 국내 철도운임은 별표 2에 따라 지급한다. 다만, 전철 구간에서 철도운임 외에 전철요금이 따로 책정되어 있는 경우에는 철도운임을 갈음하여 전철요금을 지급할 수 있으며, 이 경우 전철요금은 실비(實費)로 지급한다.
 ② 국외 철도운임은 다음 각 호의 구분에 따라 지급한다.
@@ -5910,13 +4346,13 @@
         </is>
       </c>
     </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
+    <row r="246">
+      <c r="A246" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제11조(선박운임의 지급)</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr">
+      <c r="B246" t="inlineStr">
         <is>
           <t>제11조(선박운임의 지급) ① 국내 선박운임은 별표 2에 따라 지급한다.
 ② 국외 선박운임[부선(艀船) 및 부두(埠頭) 사용료를 포함한다]은 다음 각 호의 구분에 따라 지급한다. &lt;개정 2021. 1. 5.&gt;
@@ -5927,13 +4363,13 @@
         </is>
       </c>
     </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
+    <row r="247">
+      <c r="A247" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제12조(항공운임의 지급)</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr">
+      <c r="B247" t="inlineStr">
         <is>
           <t>제12조(항공운임의 지급) ① 국내 항공운임은 별표 2에 따라 지급한다.
 ② 국외 항공운임은 별표 3에서 정하는 바에 따라 지급한다. &lt;개정 2021. 11. 30.&gt;
@@ -5944,25 +4380,13 @@
         </is>
       </c>
     </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>[공무원 여비 규정] 제12조의2</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>제12조의2 삭제 &lt;2021. 5. 25.&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
+    <row r="248">
+      <c r="A248" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제13조(자동차운임의 지급)</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr">
+      <c r="B248" t="inlineStr">
         <is>
           <t>제13조(자동차운임의 지급) ① 국내 자동차운임은 별표 2에 따라 지급한다.
 ② 국외 자동차운임은 실비로 지급한다.
@@ -5970,25 +4394,13 @@
         </is>
       </c>
     </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>[공무원 여비 규정] 제14조</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>제14조 삭제 &lt;2007. 11. 13.&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
+    <row r="249">
+      <c r="A249" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제15조(운임 지급의 제한)</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr">
+      <c r="B249" t="inlineStr">
         <is>
           <t>제15조(운임 지급의 제한) 공용의 차량ㆍ선박 또는 항공기 등을 이용하여 여행하는 경우에는 운임을 지급하지 않는다. &lt;개정 2021. 11. 30.&gt;
 [전문개정 2010. 11. 10.]
@@ -5996,13 +4408,13 @@
         </is>
       </c>
     </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
+    <row r="250">
+      <c r="A250" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제16조(일비ㆍ숙박비ㆍ식비의 지급)</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t>제16조(일비ㆍ숙박비ㆍ식비의 지급) ① 국내 여행자의 일비(日費)ㆍ숙박비 및 식비는 별표 2에 따라 지급하고, 국외 여행자의 경우는 별표 4에 따라 지급한다. 다만, 공무의 형편이나 그 밖의 부득이한 사유로 숙박비의 상한액 및 지급받은 식비(국내 여행의 경우 식비는 제외한다)를 초과하여 여비를 지출하였을 때에는 국내 여행의 경우에는 숙박비 상한액의 10분의 3을, 국외 여행의 경우에는 숙박비 및 식비의 2분의 1을 넘지 아니하는 범위에서 여비를 추가로 지급할 수 있다. &lt;개정 2011. 2. 9.&gt;
 ② 제1항 단서에 따라 여비를 추가로 지급받으려는 공무원은 여행을 마친 날의 다음 날부터 기산하여 1주일 이내(국외 여행의 경우에는 2주일 이내를 말한다)에 정부구매카드 또는 신용카드를 사용하고 받은 매출전표에 세부 사용내용이 명시된 증거자료를 갖추어 회계 관계 공무원에게 정산을 신청하여야 한다. &lt;개정 2011. 2. 9.&gt;
@@ -6014,13 +4426,13 @@
         </is>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
+    <row r="251">
+      <c r="A251" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제17조(동일 지역 장기체재 중 일비의 감액)</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr">
+      <c r="B251" t="inlineStr">
         <is>
           <t>제17조(동일 지역 장기체재 중 일비의 감액) ① 같은 곳에 장기간 체재하는 경우의 일비는 그곳에 도착한 다음 날부터 기산하여 15일을 초과한 경우에는 그 초과일수에 대하여 정액의 10분의 1에 상당한 액을, 30일을 초과한 경우에는 그 초과일수에 대하여 정액의 10분의 2에 상당한 액을, 60일을 초과한 경우에는 그 초과일수에 대하여 정액의 10분의 3에 상당한 금액을 빼고 지급한다. 다만, 소속 장관은 업무의 성질 또는 지역의 실정에 비추어 본문의 감액비율을 적용하는 것이 부적당하다고 인정하는 경우에는 인사혁신처장과 협의하여 감액비율을 따로 정할 수 있다. &lt;개정 2011. 2. 9., 2013. 3. 23., 2014. 11. 19.&gt;
 ② 제1항의 경우에 장기체재 기간 중 일시 다른 지역에 출장하는 경우에는 그 출장기간을 빼고 그 체재기간을 계산한다.
@@ -6029,13 +4441,13 @@
         </is>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
+    <row r="252">
+      <c r="A252" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제18조(근무지 내 국내 출장 시의 여비)</t>
         </is>
       </c>
-      <c r="B380" t="inlineStr">
+      <c r="B252" t="inlineStr">
         <is>
           <t>제18조(근무지 내 국내 출장 시의 여비) ① 근무지 내 국내 출장의 경우에는 제16조에도 불구하고 출장 여행시간이 4시간 이상인 공무원에게는 2만원을 지급하고, 4시간 미만인 공무원에게는 1만원을 지급한다. 다만, 「공무용 차량 관리 규정」 제4조 및 별표에 따른 전용 차량 배정자에게는 이를 지급하지 않으며, 공무용 차량을 이용하는 경우 등 인사혁신처장이 정하는 바에 따라 출장을 하는 공무원에게는 1만원을 감액하여 지급한다. &lt;개정 2013. 3. 23., 2014. 11. 19., 2021. 11. 30., 2024. 7. 2.&gt;
 ② 제1항에서 “근무지 내 국내 출장”이란 다음 각 호의 어느 하나에 해당하는 출장을 말한다. &lt;개정 2026. 6. 30.&gt;
@@ -6046,13 +4458,13 @@
         </is>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
+    <row r="253">
+      <c r="A253" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제19조(이전비의 지급 대상)</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>제19조(이전비의 지급 대상) ① 국내 이전비는 다음 각 호의 어느 하나에 해당하는 공무원(이하 “국내 이전자”라 한다)으로서 전임지(前任地)(제2호의 경우에는 구청사 소재지를 말한다. 이하 같다)에서 신임지(新任地)(제2호의 경우에는 신청사 소재지를 말한다. 이하 같다)로 거주지와 이사화물을 이전한 공무원에게 지급한다. 다만, 같은 시ㆍ군 및 섬 안에서 거주지를 이전하는 공무원에게는 국내 이전비를 지급하지 아니한다.
 1. 근무지 외의 지역으로 부임의 명을 받은 공무원
@@ -6064,13 +4476,13 @@
         </is>
       </c>
     </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
+    <row r="254">
+      <c r="A254" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제20조(이전비의 지급)</t>
         </is>
       </c>
-      <c r="B382" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t>제20조(이전비의 지급) ① 이전비(移轉費)는 별표 5에 따라 지급한다.
 ② 이전비를 지급받으려는 공무원은 이전한 날의 다음 날부터 기산하여 6개월 이내에 거주지의 변경 및 이사화물의 운송 명세(이동구간ㆍ이동거리ㆍ운송비 등을 말한다)를 확인할 수 있는 증거서류를 갖추어 새 근무기관(청사 소재지가 이전된 경우에는 소속 기관을 말한다. 이하 같다)에 이전비의 지급을 신청하여야 한다. 이 경우 전 근무기관과 새 근무기관이 협의하여 전 근무기관이 이전비를 지급하기로 한 경우에는 전 근무기관에 이전비의 지급을 신청하여야 한다.
@@ -6079,13 +4491,13 @@
         </is>
       </c>
     </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
+    <row r="255">
+      <c r="A255" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제21조(국내 가족여비)</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr">
+      <c r="B255" t="inlineStr">
         <is>
           <t>제21조(국내 가족여비) ① 국내 가족여비는 국내 이전자로서 이전할 때 가족(배우자, 본인 및 배우자의 직계존속ㆍ직계비속으로서 생계를 같이 하는 사람을 말한다. 이하 같다)을 동반하거나 이전 후에 가족을 불러 오는 공무원에게 지급한다.
 ② 국내 이전자가 특별한 사정으로 소속 기관의 장의 허가를 받아 부임의 명을 받은 날 또는 청사 이전이 완료된 날의 다음 날부터 기산하여 6개월 이내에 전임지 또는 전임지 외의 지역에서 신임지 외의 지역으로 가족을 이전하는 경우에는 가족여비를 지급할 수 있다.
@@ -6100,26 +4512,26 @@
         </is>
       </c>
     </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
+    <row r="256">
+      <c r="A256" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제22조(국외 가족여비)</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr">
+      <c r="B256" t="inlineStr">
         <is>
           <t>제22조(국외 가족여비) 국외 가족여비는 별표 6의2에 따라 지급한다. 다만, 취업하여 독립생계를 유지하고 있는 자녀 및 26세 이상의 자녀에 대해서는 국외 가족여비를 지급하지 아니하되, 정신적ㆍ육체적인 장애로 인하여 부모에게 의존하여 동거하는 26세 이상의 자녀로서 소속 장관이 확인하는 자녀와 외국에서 다른 지역 또는 본국으로 전근하는 경우에 출국 시 가족여비를 지급받은 29세 미만의 미혼자녀에 대해서는 국외 가족여비를 지급한다.
 [전문개정 2010. 11. 10.]</t>
         </is>
       </c>
     </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
+    <row r="257">
+      <c r="A257" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제23조(준비금)</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr">
+      <c r="B257" t="inlineStr">
         <is>
           <t>제23조(준비금) ① 외국에 부임하거나 국외 출장명령을 받은 공무원에게는 인사혁신처장이 정하는 항목에 대한 준비금을 실비로 지급한다. &lt;개정 2013. 3. 23., 2014. 11. 19.&gt;
 ② 제1항에 따른 준비금을 지급받으려는 공무원은 출국 전 또는 출장을 마친 날의 다음 날부터 기산하여 2주일 이내에 준비금의 세부 사용내용을 확인할 수 있는 증거자료를 갖추어 회계 관계 공무원에게 정산을 신청하여야 한다. &lt;개정 2011. 2. 9.&gt;
@@ -6128,13 +4540,13 @@
         </is>
       </c>
     </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
+    <row r="258">
+      <c r="A258" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제24조(여행 중 퇴직 또는 휴직한 공무원의 여비)</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>제24조(여행 중 퇴직 또는 휴직한 공무원의 여비) ① 부임 도중에 퇴직 또는 휴직한 공무원에게는 전임지로부터 신임지까지의 전직(前職) 또는 본직(本職)에 상당하는 여비(가족을 동반하지 아니하는 경우에는 가족여비는 제외한다)를 지급한다.
 ② 출장 중에 퇴직 또는 휴직한 공무원에게는 출장지로부터 전임지 또는 근무지까지의 전직 또는 본직에 상당하는 여비를 지급한다.
@@ -6145,26 +4557,26 @@
         </is>
       </c>
     </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
+    <row r="259">
+      <c r="A259" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제25조(퇴직 또는 휴직한 공무원의 사무 인계 등을 위한 여비)</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>제25조(퇴직 또는 휴직한 공무원의 사무 인계 등을 위한 여비) 사무 인계 또는 잔무(殘務) 정리 등을 위하여 퇴직 또는 휴직한 공무원에게 출장을 명한 경우에는 전직 또는 본직에 상당하는 여비를 지급한다.
 [전문개정 2010. 11. 10.]</t>
         </is>
       </c>
     </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
+    <row r="260">
+      <c r="A260" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제26조(여행 중 사망한 경우의 여비)</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>제26조(여행 중 사망한 경우의 여비) ① 공무원이 국내 여행 중 사망하였을 때에는 부임인 경우에는 전임지로부터 신임지까지의 전직에 상당하는 여비의 2배액을, 출장인 경우에는 출장지로부터 전임지까지의 전직에 상당하는 여비의 2배액을 각각 그 유족에게 지급할 수 있다.
 ② 공무원(제22조에 따라 국외 가족여비를 지급받는 가족을 포함한다)이 외국 여행 또는 외국 근무 중 사망하였을 때에는 사망자의 처리 및 수습 등을 위하여 필요한 경우 사망자 유족 중 2명 이내의 범위에서 여행지 또는 근무지까지의 여비와 시신 운구비를 지급한다. &lt;개정 2016. 1. 22.&gt;
@@ -6175,13 +4587,13 @@
         </is>
       </c>
     </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
+    <row r="261">
+      <c r="A261" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제27조(전역한 사람 등의 여비)</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>제27조(전역한 사람 등의 여비) ① 지원에 의하지 아니하고 임용된 현역하사 및 현역병으로서 전역하거나 병역을 면제받아 귀가하는 사람에 대한 귀가 여비와 휴가자에 대한 여비는 국방부장관이 인사혁신처장 및 기획예산처장관의 의견을 들어 정한다. &lt;개정 2013. 3. 23., 2014. 11. 19., 2025. 12. 30.&gt;
 ② 의무경찰 및 의무소방대원으로서 퇴직하여 귀가하는 사람과 휴가자에게는 제1항에 따라 국방부장관이 정하는 여비를 지급한다. &lt;개정 2015. 11. 20., 2016. 11. 29.&gt;
@@ -6191,13 +4603,13 @@
         </is>
       </c>
     </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
+    <row r="262">
+      <c r="A262" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제28조(여비의 조정)</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>제28조(여비의 조정) ① 소속 기관의 장은 예산의 부족 또는 그 밖의 사유로 여비를 지급하지 아니할 충분한 이유가 있다고 인정될 때에는 지급하는 여비를 감액하거나 여비의 전부 또는 일부를 지급하지 아니할 수 있다.
 ② 외국정부 또는 국제연합기구 등으로부터 여비의 전부 또는 일부를 지급받은 경우에는 이 영에 규정된 여비 중에서 그 금액을 빼고 지급한다.
@@ -6206,13 +4618,13 @@
         </is>
       </c>
     </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
+    <row r="263">
+      <c r="A263" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제29조(여비 지급의 특례)</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>제29조(여비 지급의 특례) ① 소속 장관은 특별한 사유로 이 영에 따른 여비의 지급액, 지급 방법 또는 정산절차 등이 불합리하다고 인정할 때에는 인사혁신처장 및 기획예산처장관과 협의하여 그 규정을 따로 정할 수 있다. &lt;개정 2013. 3. 23., 2014. 11. 19., 2025. 12. 30.&gt;
 ② 상시 출장이 필요한 공무원에 대한 여비는 별표 8에 따라 지급하되, 그 지급액 및 지급 대상에 관한 사항은 소속 장관이 인사혁신처장 및 기획예산처장관의 의견을 들어 정한다. &lt;개정 2013. 3. 23., 2014. 11. 19., 2025. 12. 30.&gt;
@@ -6222,39 +4634,39 @@
         </is>
       </c>
     </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
+    <row r="264">
+      <c r="A264" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제29조의2(지방자치단체 등에 근무하는 공무원의 여비에 관한 특례)</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>제29조의2(지방자치단체 등에 근무하는 공무원의 여비에 관한 특례) 이 영에도 불구하고 지방자치단체에 근무하는 공무원의 여비에 관하여는 해당 지방자치단체의 여비에 관한 조례를 적용한다.
 [본조신설 2020. 3. 10.]</t>
         </is>
       </c>
     </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
+    <row r="265">
+      <c r="A265" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제30조(공무원이 아닌 사람의 여비)</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr">
+      <c r="B265" t="inlineStr">
         <is>
           <t>제30조(공무원이 아닌 사람의 여비) 공무수행을 위하여 공무원이 아닌 사람을 여행하도록 하는 경우 여비 지급이 필요하다고 인정할 때에는 그 공무원이 아닌 사람에 대해서도 이 영을 준용하여 여비를 지급할 수 있으며, 그 지급 구분은 별표 9에 따른다.
 [전문개정 2010. 11. 10.]</t>
         </is>
       </c>
     </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
+    <row r="266">
+      <c r="A266" t="inlineStr">
         <is>
           <t>[공무원 여비 규정] 제31조(가산징수 등)</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
+      <c r="B266" t="inlineStr">
         <is>
           <t>제31조(가산징수 등) ① 「국가공무원법」 제48조제3항에 따라 각급 행정기관의 장은 소속 공무원이 거짓이나 그 밖의 부정한 방법으로 여비를 지급받았을 때에는 부정 수령액의 5배에 해당하는 금액을 가산하여 징수한다. &lt;개정 2021. 11. 30.&gt;
 ② 제1항에 따른 징수의 절차 등에 관하여 필요한 세부 사항은 인사혁신처장이 정한다. &lt;개정 2013. 3. 23., 2014. 11. 19.&gt;
@@ -6262,51 +4674,38 @@
         </is>
       </c>
     </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>[공무원 여비 규정] 부칙</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>부칙  &lt;제36492호, 2026. 6. 30.&gt;
-이 영은 2026년 7월 1일부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
+    <row r="267">
+      <c r="A267" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제1조(목적)</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>제1조 (목적)이 규칙은 「경상북도 공무원 복무 조례」 제7조에 따라 경상북도 소속 공무원의 당직 및 비상근무에 관한 사항을 규정함을 목적으로 한다.&lt;개정'06. 10. 2., 2020. 1. 2., 2026. 8. 20.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
+    <row r="268">
+      <c r="A268" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제2조(적용 범위)</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
+      <c r="B268" t="inlineStr">
         <is>
           <t>제2조 (적용 범위)이 규칙은 경상북도 본청 및 직속기관ㆍ지역본부ㆍ사업소(이하 “소속기관”이라 한다)에 근무하는 공무원에게 적용한다. &lt;개정'06. 10. 2., 2020. 1. 2., 2026. 8. 20.&gt;
 [제목개정 2020. 1. 2.]</t>
         </is>
       </c>
     </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
+    <row r="269">
+      <c r="A269" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제3조(정의)</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
+      <c r="B269" t="inlineStr">
         <is>
           <t>제3조 (정의)이 규칙에서 사용하는 용어의 뜻은 다음과 같다. &lt;개정 2020. 1. 2.&gt;
 1. “당직사령”이라 함은 도의 본청과 그 소속기관의 당직근무자를 총괄 지휘 감독하는 근무자를 말한다.
@@ -6316,13 +4715,13 @@
         </is>
       </c>
     </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
+    <row r="270">
+      <c r="A270" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제4조(당직의 구분)</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
+      <c r="B270" t="inlineStr">
         <is>
           <t>제4조 (당직의 구분)① 당직은 일직과 숙직으로 구분한다.
 ② 일직은 토요일 및 공휴일에 두며, 근무시간은 정상근무일의 근무시간에 준한다.&lt;개정 '06. 10. 2., 2020. 1. 2.&gt;
@@ -6330,26 +4729,26 @@
         </is>
       </c>
     </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
+    <row r="271">
+      <c r="A271" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제5조(당직근무자의 휴무)</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
+      <c r="B271" t="inlineStr">
         <is>
           <t>제5조 (당직근무자의 휴무)당직근무자(재택당직 근무자는 제외한다)에 대하여는 긴급한 민원업무처리, 재해발생대비 등 업무상의 불가피한 경우를 제외하고는 그 근무종료 시각이 속하는 날을 휴무하게 하여야 한다.다만, 당직근무 종료시각이 속하는 날이 토요일 또는 공휴일인 경우에는 다음 정상 근무일부터 6주 이내에 1일을 지정하여 휴무하게 할 수 있다. &lt;개정'12.6.21.'17.12.28., 2020. 1. 2., 2026. 8. 20.&gt;
 [제목개정 2020. 1. 2.]</t>
         </is>
       </c>
     </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
+    <row r="272">
+      <c r="A272" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제6조(당직근무자의 편성)</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
+      <c r="B272" t="inlineStr">
         <is>
           <t>제6조 (당직근무자의 편성)① 당직근무자는 공무원으로 함을 원칙으로 한다. &lt;개정 2020. 1. 2.&gt;
 ② 본청의 당직근무자는 1명 이상으로 하되, 청사 내외의 경비와 비상사태에 대비하기 위하여 청원경찰, 운전원 등으로 별도의 당직원을 둘 수 있으며, 운전원은 22:00시까지 근무 후 당직사령 책임하에 재택근무하게 할 수 있다. &lt;개정 2026. 8. 20.&gt;
@@ -6369,39 +4768,39 @@
         </is>
       </c>
     </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
+    <row r="273">
+      <c r="A273" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제6조의2(당직수당 지급)</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
+      <c r="B273" t="inlineStr">
         <is>
           <t>제6조의2(당직수당 지급)당직근무를 수행한 공무원에게는 1명당 1회에 60,000원의 당직수당을 지급한다. 다만, 재택당직 근무자는 당직실 및 사무실에서 3시간을 초과하여 대기근무한 경우에 한하여 30,000원을 지급한다.
 [전문개정 2020. 1. 2.]</t>
         </is>
       </c>
     </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
+    <row r="274">
+      <c r="A274" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제7조(당직명령 및 변경)</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
+      <c r="B274" t="inlineStr">
         <is>
           <t>제7조 (당직명령 및 변경)① 당직명령은 근무예정일 7일전까지 일일 명령에 의하여 해당 기관의 장이 발령하고 소속 팀장·과장을 거쳐 당직자에게 통지하여야 한다. &lt;개정 2020. 1. 2.&gt;
 ② 소속팀장·과장은 당직명령을 받은 자가 출장, 휴가 기타 부득이한 사유로 당직근무를 할 수 없을 경우에는 지체없이 동일직급의 대리근무자를 정하여 당직명령자로부터 당직근무일의 변경승인을 받아야 한다.&lt;개정 '06. 10. 2&gt;</t>
         </is>
       </c>
     </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
+    <row r="275">
+      <c r="A275" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제8조(당직신고 및 인계인수)</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
+      <c r="B275" t="inlineStr">
         <is>
           <t>제8조 (당직신고 및 인계인수)① 당직사령, 당직반장 및 당직원은 당직근무 개시시간 30분전에 행정지원과장에게 신고하여야 한다. 다만, 토요일 및 공휴일의 당직근무자는 그 전일인 정상근무일에 당직신고를 하여야 한다.&lt;개정'06. 10. 2, 2024.06.27.&gt;
 ② 당직사령은 제1항의 당직신고전에 당직주무부서로부터 당직근무일지 기타 필요한 당직원 비품을 인수확인하고 당직근무 종료시는 이를 당직주무부서로 인계하여야 한다. 다만, 토요일 및 공휴일인 경우에는 일직근무자와 숙직근무자간에 인계인수하여야 한다.&lt;개정'06. 10. 2&gt;
@@ -6412,13 +4811,13 @@
         </is>
       </c>
     </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
+    <row r="276">
+      <c r="A276" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제9조(교대근무)</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr">
+      <c r="B276" t="inlineStr">
         <is>
           <t>제9조 (교대근무)당직근무자는 다음 각 호에 의하여 전후반으로 나누어 교대로 근무한다. 다만, 지역의 치안상황에 따라 당직명령자 또는 당직사령은 전원 동시근무를 명할 수 있다. &lt;개정 2020. 1. 2.&gt;
 1. 일직시의 전반 근무시간은 일직개시 시간부터 13:00까지로 하고, 후반 근무시간은 13:00부터 일직종료시까지 한다.
@@ -6427,50 +4826,50 @@
         </is>
       </c>
     </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
+    <row r="277">
+      <c r="A277" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제10조(당직근무자의 위치)</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>제10조 (당직근무자의 위치)당직사령, 당직반장 및 그 이하의 당직근무자는 당직실에 위치하여야 하며, 전후반 교대근무시 근무에 임하지 않은 당직근무자는 당직실에서 휴식하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
+    <row r="278">
+      <c r="A278" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제11조(당직근무자의 준수사항)</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>제11조 (당직근무자의 준수사항)① 당직근무자는 음주, 도박, 그 밖에 공무원의 품위를 손상하거나 당직근무에 지장이 있는 일을 하여서는 아니된다. &lt;개정 2020. 1. 2.&gt;
 ② 당직근무자는 복장을 단정히 하고 당직근무자임을 표시하는 규정된 표찰을 패용하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제12조(당직차량의 운영)</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>제12조(당직차량의 운영)차량관리 부서장은 당직업무의 원활한 수행을 위하여 당직차량은 1대 이상 운영하도록 필요한 조치를 취하여야 한다. &lt;개정'12.6.21., 2020. 1. 2.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
+    <row r="280">
+      <c r="A280" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제13조(당직의 일반업무)</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>제13조 (당직의 일반업무)① 당직근무자는 다음 각 호의 사항을 철저히 이행하여 모든 사고를 미리 방지하여야 한다. &lt;개정 2020. 1. 2., 2020. 2. 20.&gt;
 1. 경비용역업체가 경비용역을 이행할 수 있도록 하고, 근무시간중 경비용역업체 관제실과 긴밀한 연락체계유지
@@ -6480,25 +4879,25 @@
         </is>
       </c>
     </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
+    <row r="281">
+      <c r="A281" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제14조(팀장·과장의 임무)</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr">
+      <c r="B281" t="inlineStr">
         <is>
           <t>제14조 (팀장·과장의 임무)각 사무실에 비치되어 있는 "별지 제1호 서식"에 의한 보안점검표의 점검은 팀장·과장 책임하에 사무실별 최종퇴청자가 점검기록하여야 한다.&lt;개정'06. 10. 2&gt;</t>
         </is>
       </c>
     </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
+    <row r="282">
+      <c r="A282" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제15조(당직근무자의 긴급사태시 임무)</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr">
+      <c r="B282" t="inlineStr">
         <is>
           <t>제15조 (당직근무자의 긴급사태시 임무)①당직근무자는 근무중 청사에 화재가 발생한 때에는 지체없이 다음 각 호의 긴급조치를 취하여야 한다.
 1. 경비용역업체, 관할소방관서와 경상북도지사(이하 "도지사"라 한다), 행정부지사, 안전행정실장, 소방본부장에게 급보&lt;개정'06. 10. 2, 2015.05.21, 2015.07.02., 2023.12.28.&gt;
@@ -6515,13 +4914,13 @@
         </is>
       </c>
     </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
+    <row r="283">
+      <c r="A283" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제16조(당직실의 비품)</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr">
+      <c r="B283" t="inlineStr">
         <is>
           <t>제16조 (당직실의 비품)① 당직실에는 다음 각 호의 비품 및 물품을 비치하여야 한다. &lt;개정 2020. 1. 2.&gt;
 1. "별지 제2호 서식"의 당직근무일지
@@ -6538,13 +4937,13 @@
         </is>
       </c>
     </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
+    <row r="284">
+      <c r="A284" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제17조(당직사령)</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>제17조 (당직사령)① 도지사는 도의 본청과 그 소속기관의 당직근무자를 지휘·감독하기 위하여 당직사령을 둔다.
 ② 제1항의 당직사령은 특별한 사유가 없는 한 제6조 규정에 의한다.
@@ -6553,25 +4952,25 @@
         </is>
       </c>
     </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
+    <row r="285">
+      <c r="A285" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제18조(당직반장)</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
+      <c r="B285" t="inlineStr">
         <is>
           <t>제18조 (당직반장)당직사령을 보좌하기 위하여 2일 이상 연휴일때에는 당직반장을 지정할 수 있다.</t>
         </is>
       </c>
     </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
+    <row r="286">
+      <c r="A286" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제19조(당직사령의 임무)</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
+      <c r="B286" t="inlineStr">
         <is>
           <t>제19조 (당직사령의 임무)① 당직사령은 도 본청과 산하기관의 당직근무자 및 청원경찰을 지휘 감독하고 다음 각 호의 사항을 점검한다. &lt;개정 2020. 1. 2.&gt;
 1. 당직근무자의 준수사항 및 당직임무의 이행여부
@@ -6581,13 +4980,13 @@
         </is>
       </c>
     </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
+    <row r="287">
+      <c r="A287" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제20조(당직사령실의 비품)</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr">
+      <c r="B287" t="inlineStr">
         <is>
           <t>제20조 (당직사령실의 비품)당직사령실에 다음 각 호의 서류 및 물품을 비치하여야 한다. &lt;개정 2020. 1. 2.&gt;
 1. 기관간 연락체계도 및 전화번호부
@@ -6597,13 +4996,13 @@
         </is>
       </c>
     </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
+    <row r="288">
+      <c r="A288" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제21조(비상근무의 종류)</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>제21조 (비상근무의 종류)비상근무는 그 상황에 따라 다음 각호와 같이 구분하여 발령한다.
 1. 비상근무 제1호는 다음 각 목의 어느 하나에 해당하는 경우에 발령한다. &lt;개정'12.3.5&gt;
@@ -6621,13 +5020,13 @@
         </is>
       </c>
     </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
+    <row r="289">
+      <c r="A289" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제22조(비상소집)</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr">
+      <c r="B289" t="inlineStr">
         <is>
           <t>제22조 (비상소집)① 당직사령은 근무중 비상소집명령을 받으면 즉시 도지사에게 보고하는 동시에 제반 통신수단을 이용하여 신속히 비상소집명단에 따라 연락한다.
 ② 당직사령은 당직원 및 연락반(종합상황실, 소방상황실)을 활용, 다음과 같이 연락한다.
@@ -6639,13 +5038,13 @@
         </is>
       </c>
     </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
+    <row r="290">
+      <c r="A290" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제23조(비상근무의 요령)</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr">
+      <c r="B290" t="inlineStr">
         <is>
           <t>제23조 (비상근무의 요령)① 제21조에 따라 비상근무가 발령된 때에는 청사 등 중요 시설물에 대한 경계와 경비를 강화하여야 한다. &lt;개정'12.3.5&gt;
 ② 비상근무가 발령 중에는 부득이한 경우를 제외하고는 출장을 억제하고, 소속 직원의 소재지를 파악하여야 한다. &lt;개정'12.3.5&gt;
@@ -6659,38 +5058,38 @@
         </is>
       </c>
     </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
+    <row r="291">
+      <c r="A291" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제24조(비상소집 대상자 명단작성)</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr">
+      <c r="B291" t="inlineStr">
         <is>
           <t>제24조 (비상소집 대상자 명단작성)비상소집의 신속을 기하기 위하여 도지사와 행정지원과장은 평시에 미리 비상소집대상자명단 "별지 제4호 서식"을 작성하여 비치하여야 한다.&lt;개정'06. 10. 2., 2024.06.27.&gt;</t>
         </is>
       </c>
     </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
+    <row r="292">
+      <c r="A292" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제25조(응소자의 임무)</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
+      <c r="B292" t="inlineStr">
         <is>
           <t>제25조 (응소자의 임무)① 응소자는 비상연락을 받으면 지체없이 빠른 교통수단을 이용, 등청하여 등록하고 당직책임자 또는 당직주무부서의 지시에 의하여 근무에 임한다.
 ② 소집된 응소자는 부여받은 임무를 성실히 수행하여야 하며 근무지를 무단이탈하지 못한다.</t>
         </is>
       </c>
     </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
+    <row r="293">
+      <c r="A293" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제26조(비상근무중의 당직)</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr">
+      <c r="B293" t="inlineStr">
         <is>
           <t>제26조 (비상근무중의 당직)① 비상근무령이 발령되고 비상 근무중일 때에는 당직근무를 중지한다. 다만, 정상근무위치외에서 비상근무를 하는 경우는 그러하지 아니한다.
 ② 당직근무자가 당직근무중 비상근무가 발령되어 제1항의 규정에 의하여 당직근무를 중지할 때에는 당직주무부서에 당직근무일지 등을 인계하여야 한다.
@@ -6708,13 +5107,13 @@
         </is>
       </c>
     </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
+    <row r="294">
+      <c r="A294" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제27조(상황실 설치)</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr">
+      <c r="B294" t="inlineStr">
         <is>
           <t>제27조 (상황실 설치)① 비상근무 발령시 도본청에 비상근무 상황실을 설치한다.
 ② 비상근무 상황실의 통신망은 다음 각 호와 같다.
@@ -6725,13 +5124,13 @@
         </is>
       </c>
     </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
+    <row r="295">
+      <c r="A295" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제28조(당직반장의 임무)</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr">
+      <c r="B295" t="inlineStr">
         <is>
           <t>제28조 (당직반장의 임무)비상시 당직반장은 당직주무부서에 당직업무를 인계할 때까지 다음의 임무를 수행한다.
 1. 도지사 및 당직사령의 지시를 받아 비상대기 근무자 및 당직 근무자를 지휘 감독하여 자체경계강화, 화재·도난방지와 상급기관의 지시, 하급기관의 보고 및 보고된 업무의 조치
@@ -6751,13 +5150,13 @@
         </is>
       </c>
     </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
+    <row r="296">
+      <c r="A296" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제29조(비상근무 보고)</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr">
+      <c r="B296" t="inlineStr">
         <is>
           <t>제29조 (비상근무 보고)① 비상시 당직사령은 당직주무부서에 당직업무를 인계할 때까지 지사에게 다음 각 호의 사항을 수시 보고하여야 한다.
 1. 상급 및 하급기관의 중요지시 및 보고사항의 조치상황
@@ -6767,633 +5166,113 @@
         </is>
       </c>
     </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 제30조(예비군중대장의 임무)</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>제30조 (예비군중대장의 임무)&lt;삭제'06. 10. 2&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
+    <row r="297">
+      <c r="A297" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제31조(문서연락)</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr">
+      <c r="B297" t="inlineStr">
         <is>
           <t>제31조 (문서연락)비상근무령 발령기간중 문서연락은 전언통신문 또는 팩스로 한다.</t>
         </is>
       </c>
     </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
+    <row r="298">
+      <c r="A298" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제32조(통신시설)</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
+      <c r="B298" t="inlineStr">
         <is>
           <t>제32조 (통신시설)각급 기관의 장은 비상근무령 발령시 근무할 장소를 평시에 지시하여 두고 사전에 상급협조기관 및 소속기관과 신속한 통신유지가 될 수 있는 충분한 각종 통신망을 구성, 필요시 전화기만 연결하여 즉시 통화할 수 있는 조치를 취하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
+    <row r="299">
+      <c r="A299" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제33조(직원연락체계의 유지)</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr">
+      <c r="B299" t="inlineStr">
         <is>
           <t>제33조 (직원연락체계의 유지)① 공무원은 근무시간이 아닌 때에도 항상 소재파악이 가능하도록 연락체계를 유지하여야 한다.
 ② 공무원은 주소, 전화번호등 연락체계의 유지를 위하여 필요한 사항의 변경이 있는 때에는 이를 즉시 주관부서에 신고하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
+    <row r="300">
+      <c r="A300" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제34조(필수요원의 지정)</t>
         </is>
       </c>
-      <c r="B430" t="inlineStr">
+      <c r="B300" t="inlineStr">
         <is>
           <t>제34조 (필수요원의 지정)① 각급기관의 장은 정상근무시간이 아닌때에 긴급사태가 발생할 경우에 대비하여 소속직원중 일부를 미리 필수요원으로 지정하고 긴급사태 발생시 신속히 필요한 조치를 하도록 하여야 한다.
 ② 제1항의 필수요원은 비상소집시 1시간 이내에 응소 가능한 자를 우선적으로 지정하되 문서보관자, 통신요원 등 사무보조에 필요한 인원이 포함되도록 하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
+    <row r="301">
+      <c r="A301" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제35조(직원비상소집대장의 정비·보완)</t>
         </is>
       </c>
-      <c r="B431" t="inlineStr">
+      <c r="B301" t="inlineStr">
         <is>
           <t>제35조 (직원비상소집대장의 정비·보완)도지사는 복무관계 업무를 담당하는 소속공무원중에서 직원연락체계의 유지 및 직원비상소집대장의 정비·보완을 위한 책임자 및 보조자 각 1인을 지정하여야 한다.</t>
         </is>
       </c>
     </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
+    <row r="302">
+      <c r="A302" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제36조(시행세칙)</t>
         </is>
       </c>
-      <c r="B432" t="inlineStr">
+      <c r="B302" t="inlineStr">
         <is>
           <t>제36조 (시행세칙)이 규칙에 준하여 각급기관장은 비상근무에 필요한 세부사항을 제정 운영한다.</t>
         </is>
       </c>
     </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>부 칙
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>부 칙 (2012.3.5)
-이 규칙은 공포한 날로부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>부 칙 (2012.6.21)
-이 규칙은 공포한 날부터 시행한다. 다만, 제6조의2의 개정규정은 2012년 7월 1일부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>부칙(2014.2.24)
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>부칙 &lt;규칙 2801호, 2015.05.21.&gt; (경상북도 행정기구 설치 조례 시행규칙)</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 제1조(시행일)</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>제1조(시행일)
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 제2조(다른 규칙의 개정)</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>제2조(다른 규칙의 개정)
-① 생략
-② 경상북도공무원 당직 및 비상근무 규칙 일부를 다음과 같이 개정한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
+    <row r="303">
+      <c r="A303" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제15조</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr">
+      <c r="B303" t="inlineStr">
         <is>
           <t>제15조제1항1호 및 제15조제2항1호 중 “행정지원국장”을 각각“안전행정국장”으로 한다.
 ③ 부터 ⑥까지 생략</t>
         </is>
       </c>
     </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>부칙(2015.06.25.)
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>부칙 &lt;규칙 제2809호, 2015.07.02.&gt; 경상북도 행정기구 설치 조례 시행규칙</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 제1조(시행일)</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>제1조(시행일)
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 제2조(다른 규칙의 개정)</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>제2조(다른 규칙의 개정)
-① 경상북도공무원 당직 및 비상근무 규칙 일부를 다음과 같이 개정한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
+    <row r="304">
+      <c r="A304" t="inlineStr">
         <is>
           <t>[경상북도 공무원 당직 및 비상근무 규칙] 제15조</t>
         </is>
       </c>
-      <c r="B445" t="inlineStr">
+      <c r="B304" t="inlineStr">
         <is>
           <t>제15조제1항1호 및 제15조제2항1호 중 “안전행정국장”을 각각“자치행정국장”으로 한다.
 ② 부터 ④까지 생략</t>
         </is>
       </c>
     </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>부 칙&lt;2017.12.28&gt;
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;2020. 1. 2.&gt;
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;규칙 제2946호, 2020. 2. 20.&gt; (어려운 한자어 정비를 위한 7개 경상북도 규칙의 일부개정에 관한 규칙)
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;규칙 제3041호, 2023. 12. 28.&gt; (경상북도 행정기구 설치 조례 시행규칙)
-이 규칙은 2023년 12월 31일부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;규칙 제3062호, 2024.06.27.&gt; (경상북도 행정기구 설치 조례 시행규칙 일부개정규칙)</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 제1조(시행일)</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>제1조(시행일)
-이 규칙은 2023년 12월 31일부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 제2조</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>제2조~제4조 생략</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 부칙</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>부 칙 &lt;2026. 8. 20.&gt;
-이 규칙은 공포한 날부터 시행한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지 제1호 서식</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>별지 제1호 서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지 제2호 서식</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>별지 제2호 서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지 제3호 서식</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>별지 제3호 서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지 제4호 서식</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>별지 제4호 서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지 제5호 서식</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>별지 제5호 서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지 제6호 서식</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>별지 제6호 서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지 제7호 서식</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>별지 제7호 서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지 제8호 서식</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>별지 제8호 서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지 제9호 서식</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>별지 제9호 서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지 제10호 서식</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>별지 제10호 서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지/별표</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>별지/별표</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>[경상북도 공무원 당직 및 비상근무 규칙] 별지 제11호 서식</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>별지 제11호 서식</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
+    <row r="305">
+      <c r="A305" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 사무관리비 (201)</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>01. 사무관리비
 1. 일반수용비
@@ -7502,13 +5381,13 @@
         </is>
       </c>
     </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
+    <row r="306">
+      <c r="A306" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 공공운영비 (201)</t>
         </is>
       </c>
-      <c r="B477" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>02. 공공운영비
 1. 공공요금 및 제세
@@ -7553,13 +5432,13 @@
         </is>
       </c>
     </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
+    <row r="307">
+      <c r="A307" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 행사운영비 (201)</t>
         </is>
       </c>
-      <c r="B478" t="inlineStr">
+      <c r="B307" t="inlineStr">
         <is>
           <t>03. 행사운영비
 1. 행사운영을 위한 일체의 일반운영비
@@ -7572,13 +5451,13 @@
         </is>
       </c>
     </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
+    <row r="308">
+      <c r="A308" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 맞춤형복지제도 시행경비 (201)</t>
         </is>
       </c>
-      <c r="B479" t="inlineStr">
+      <c r="B308" t="inlineStr">
         <is>
           <t>04. 맞춤형복지제도 시행경비
 1. 맞춤형복지제도 시행경비(정무직, 공무직(무기계약) 포함)
@@ -7588,13 +5467,13 @@
         </is>
       </c>
     </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
+    <row r="309">
+      <c r="A309" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 공립대학 운영비 (201)</t>
         </is>
       </c>
-      <c r="B480" t="inlineStr">
+      <c r="B309" t="inlineStr">
         <is>
           <t>05. 공립대학 운영비
 1. 「국립대학의 회계 설치 및 재정 운영에 관한 법률」 제2조 및 제4조에 따른 지원금
@@ -7602,13 +5481,13 @@
         </is>
       </c>
     </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
+    <row r="310">
+      <c r="A310" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 국내여비 (202)</t>
         </is>
       </c>
-      <c r="B481" t="inlineStr">
+      <c r="B310" t="inlineStr">
         <is>
           <t>01. 국내여비
 1. 기본업무수행을 위한 관할구역내 출장여비
@@ -7624,26 +5503,26 @@
         </is>
       </c>
     </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
+    <row r="311">
+      <c r="A311" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 월액여비 (202)</t>
         </is>
       </c>
-      <c r="B482" t="inlineStr">
+      <c r="B311" t="inlineStr">
         <is>
           <t>02. 월액여비
 1. 상시출장을 요하는 공무원 및 공무직에 대하여 자치단체별로 편성 여부 및 대상 부서, 월정액을 자율 결정(월액여비를 운영하지 않는 경우는 국내여비를 적용)</t>
         </is>
       </c>
     </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
+    <row r="312">
+      <c r="A312" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 국외업무여비 (202)</t>
         </is>
       </c>
-      <c r="B483" t="inlineStr">
+      <c r="B312" t="inlineStr">
         <is>
           <t>03. 국외업무여비
 1. 「공무원 여비 규정」 에 의한 공무원의 국외출장여비 중 업무수행관련 여비
@@ -7652,13 +5531,13 @@
         </is>
       </c>
     </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
+    <row r="313">
+      <c r="A313" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 국제화여비 (202)</t>
         </is>
       </c>
-      <c r="B484" t="inlineStr">
+      <c r="B313" t="inlineStr">
         <is>
           <t>04. 국제화여비
 1. 업무능력 향상을 위한 각종 해외시찰, 견학, 참관, 자료수집 등
@@ -7666,13 +5545,13 @@
         </is>
       </c>
     </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
+    <row r="314">
+      <c r="A314" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 기관운영업무추진비 (203)</t>
         </is>
       </c>
-      <c r="B485" t="inlineStr">
+      <c r="B314" t="inlineStr">
         <is>
           <t>01. 기관운영업무추진비
 1. 예산편성 : 「지방자치단체 예산편성 운영기준」 제4조에 따른 기준경비에 의함
@@ -7681,13 +5560,13 @@
         </is>
       </c>
     </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
+    <row r="315">
+      <c r="A315" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 정원가산업무추진비 (203)</t>
         </is>
       </c>
-      <c r="B486" t="inlineStr">
+      <c r="B315" t="inlineStr">
         <is>
           <t>02. 정원가산업무추진비
 1. 동호인 취미클럽, 체육대회, 생일기념품, 불우 공무원 지원 등 직원사기 진작을 위한 경비에 한하여 편성 및 집행
@@ -7695,13 +5574,13 @@
         </is>
       </c>
     </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
+    <row r="316">
+      <c r="A316" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 시책추진업무추진비 (203)</t>
         </is>
       </c>
-      <c r="B487" t="inlineStr">
+      <c r="B316" t="inlineStr">
         <is>
           <t>03. 시책추진업무추진비
 1. 예산편성 : 「지방자치단체 예산편성 운영기준」 제4조에 따른 기준경비에 의함
@@ -7710,13 +5589,13 @@
         </is>
       </c>
     </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
+    <row r="317">
+      <c r="A317" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 부서운영업무추진비 (203)</t>
         </is>
       </c>
-      <c r="B488" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>04. 부서운영업무추진비
 1.통상적인 실·과·소 조직운영에 소요되는 부서운영업무추진 제잡비
@@ -7729,13 +5608,13 @@
         </is>
       </c>
     </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
+    <row r="318">
+      <c r="A318" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 직책급업무수행경비 (204)</t>
         </is>
       </c>
-      <c r="B489" t="inlineStr">
+      <c r="B318" t="inlineStr">
         <is>
           <t>01. 직책급업무수행경비
 경비
@@ -7744,13 +5623,13 @@
         </is>
       </c>
     </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
+    <row r="319">
+      <c r="A319" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 특정업무경비 (204)</t>
         </is>
       </c>
-      <c r="B490" t="inlineStr">
+      <c r="B319" t="inlineStr">
         <is>
           <t>02. 특정업무경비
 1.특수업무담당분야에 근무하는 자에 대한 활동비로 월정액으로 지급하는 경비
@@ -7758,13 +5637,13 @@
         </is>
       </c>
     </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
+    <row r="320">
+      <c r="A320" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 의원국내여비 (205)</t>
         </is>
       </c>
-      <c r="B491" t="inlineStr">
+      <c r="B320" t="inlineStr">
         <is>
           <t>03. 의원국내여비
 1.「지방자치법 시행령」 제33조 별표6 및 관련 조례의 규정에 의하여 의원의 공무상 국내 출장시 지급하는 여비
@@ -7772,13 +5651,13 @@
         </is>
       </c>
     </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
+    <row r="321">
+      <c r="A321" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 의원국외여비 (205)</t>
         </is>
       </c>
-      <c r="B492" t="inlineStr">
+      <c r="B321" t="inlineStr">
         <is>
           <t>04. 의원국외여비
 1.「지방자치법 시행령」 제33조 별표6 및 관련 조례의 규정에 의하여 의원의 공무상 국외출장시 지급하는 경비
@@ -7792,13 +5671,13 @@
         </is>
       </c>
     </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
+    <row r="322">
+      <c r="A322" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 의정운영공통경비 (205)</t>
         </is>
       </c>
-      <c r="B493" t="inlineStr">
+      <c r="B322" t="inlineStr">
         <is>
           <t>05. 의정운영공통경비
 1.의회, 상임위원회, 교섭단체 명의의 공적인 의정활동을 수행하는데 소요되는 경비로서 「지방자치단체 예산편성 운영기준」  제4조에 따른 기준경비에 의함
@@ -7812,13 +5691,13 @@
         </is>
       </c>
     </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
+    <row r="323">
+      <c r="A323" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 의회운영업무추진비 (205)</t>
         </is>
       </c>
-      <c r="B494" t="inlineStr">
+      <c r="B323" t="inlineStr">
         <is>
           <t>06. 의회운영업무추진비
 1. 지방의회의장,부의장,상임위원장, 교섭단체 대표의원의 지방의회운영및업무의 유대를 위한 제경비로서 지방자치단체예산편성기준󰡕 제4조에 의한 기준경비에 의함
@@ -7827,13 +5706,13 @@
         </is>
       </c>
     </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
+    <row r="324">
+      <c r="A324" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 의원역량개발비(공공위탁, 자체교육) (205)</t>
         </is>
       </c>
-      <c r="B495" t="inlineStr">
+      <c r="B324" t="inlineStr">
         <is>
           <t>07. 의원역량개발비(공공위탁, 자체교육)
 지방의회의원의 역량강화를 위한 위탁교육비 및 강사료
@@ -7846,26 +5725,26 @@
         </is>
       </c>
     </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
+    <row r="325">
+      <c r="A325" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 의장협의체 부담금 (205)</t>
         </is>
       </c>
-      <c r="B496" t="inlineStr">
+      <c r="B325" t="inlineStr">
         <is>
           <t>10. 의장협의체 부담금
 1. 지방자치법 제182조에 따라 설립된 전국적 협의체 중 시･도의회 의장, 시･군･자치구의회 의장 협의체 부담금</t>
         </is>
       </c>
     </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
+    <row r="326">
+      <c r="A326" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 재료비 (206)</t>
         </is>
       </c>
-      <c r="B497" t="inlineStr">
+      <c r="B326" t="inlineStr">
         <is>
           <t>01. 재료비
 1. 교육기관의 외래강사 수송용 유류대
@@ -7877,26 +5756,26 @@
         </is>
       </c>
     </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
+    <row r="327">
+      <c r="A327" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 연구용역비 (207)</t>
         </is>
       </c>
-      <c r="B498" t="inlineStr">
+      <c r="B327" t="inlineStr">
         <is>
           <t>01. 연구용역비
 1.지방자치단체사업의 계속적인 연구 등을 위촉받는 자의 조사, 강연, 연구 등 용역에 대한 반대급부</t>
         </is>
       </c>
     </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
+    <row r="328">
+      <c r="A328" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 전산개발비 (207)</t>
         </is>
       </c>
-      <c r="B499" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>02. 전산개발비
 1. 정보화시스템 구축･운영을 위한 S/W개발비
@@ -7906,26 +5785,26 @@
         </is>
       </c>
     </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
+    <row r="329">
+      <c r="A329" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 시험연구비 (207)</t>
         </is>
       </c>
-      <c r="B500" t="inlineStr">
+      <c r="B329" t="inlineStr">
         <is>
           <t>03. 시험연구비
 1. 사업용 및 시험연구, 실험･실습에 소요되는 소모성 기계･기구, 기재, 약품, 비료 및 종축 등의 구입비</t>
         </is>
       </c>
     </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
+    <row r="330">
+      <c r="A330" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 사회보장적수혜금(국고보조재원) (301)</t>
         </is>
       </c>
-      <c r="B501" t="inlineStr">
+      <c r="B330" t="inlineStr">
         <is>
           <t>01. 사회보장적수혜금(국고보조재원)
 1.국고보조사업에 의한 민간에 지급하는 사회보장적 현금성 수혜금 또는 물품지원비(국고보조재원+지방재원 모두 포함)
@@ -7939,13 +5818,13 @@
         </is>
       </c>
     </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
+    <row r="331">
+      <c r="A331" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 사회보장적수혜금(지방재원) (301)</t>
         </is>
       </c>
-      <c r="B502" t="inlineStr">
+      <c r="B331" t="inlineStr">
         <is>
           <t>03. 사회보장적수혜금(지방재원)
 1. 자치단체가 법령(조례포함)의 근거에 따라 자체적으로 추진(민간에 지급)하는 사회보장적 현금성 수혜금 및 물품지원비(지방재원만)
@@ -7954,13 +5833,13 @@
         </is>
       </c>
     </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
+    <row r="332">
+      <c r="A332" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 장학금 및 학자금 (301)</t>
         </is>
       </c>
-      <c r="B503" t="inlineStr">
+      <c r="B332" t="inlineStr">
         <is>
           <t>04. 장학금 및 학자금
 1. 법령또는조례에 의하여 지급하는 장학금및학자금(국고대여장학금은 제외)
@@ -7968,13 +5847,13 @@
         </is>
       </c>
     </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
+    <row r="333">
+      <c r="A333" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 자율방범대 실비지원 (301)</t>
         </is>
       </c>
-      <c r="B504" t="inlineStr">
+      <c r="B333" t="inlineStr">
         <is>
           <t>06. 자율방범대 실비지원
 1. 기조직된 자율방범대 및 결성이 확정된 조직
@@ -7985,13 +5864,13 @@
         </is>
       </c>
     </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
+    <row r="334">
+      <c r="A334" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 통장･이장･반장활동보상금 (301)</t>
         </is>
       </c>
-      <c r="B505" t="inlineStr">
+      <c r="B334" t="inlineStr">
         <is>
           <t>07. 통장･이장･반장활동보상금
 1.조례에 따라 읍․면의 이장과 동의 통장에게 지급하는 수당과 읍･면･동의 반장에게 지급하는 활동비로서, 「지방자치단체 예산편성 운영기준」 제4조에 따른 기준경비에 의함
@@ -8002,26 +5881,26 @@
         </is>
       </c>
     </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
+    <row r="335">
+      <c r="A335" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 민간인 국외여비 (301)</t>
         </is>
       </c>
-      <c r="B506" t="inlineStr">
+      <c r="B335" t="inlineStr">
         <is>
           <t>08. 민간인 국외여비
 1.지방자치단체 사업을 학계, 언론, 기업, 연구기관 등의 전문가에게 수행하는 경우 당해 사업수행을 위한 국외출장시의 여비</t>
         </is>
       </c>
     </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
+    <row r="336">
+      <c r="A336" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 외빈초청여비 (301)</t>
         </is>
       </c>
-      <c r="B507" t="inlineStr">
+      <c r="B336" t="inlineStr">
         <is>
           <t>09. 외빈초청여비
 1. 사업추진에 특별히 소요되는 외빈초청경비 중 여비  (단, 연회비, 선물비, 환송연 행사등 기타부대경비는 업무추진비로 계상)
@@ -8031,13 +5910,13 @@
         </is>
       </c>
     </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
+    <row r="337">
+      <c r="A337" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 사회복무요원 보상금 (301)</t>
         </is>
       </c>
-      <c r="B508" t="inlineStr">
+      <c r="B337" t="inlineStr">
         <is>
           <t>10. 사회복무요원 보상금
 1.「병역법」 제26조 내지 제33조에 따른 사회복무요원의 보수
@@ -8046,13 +5925,13 @@
         </is>
       </c>
     </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
+    <row r="338">
+      <c r="A338" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 행사실비 지원금 (301)</t>
         </is>
       </c>
-      <c r="B509" t="inlineStr">
+      <c r="B338" t="inlineStr">
         <is>
           <t>11. 행사실비 지원금
 1.교육･세미나･공청회･회의·훈련에 참석하는 민간인에게 지급하는 급식비 및 교통비(실비)(급식비는 매식비 기준단가 이내로 함)
@@ -8064,13 +5943,13 @@
         </is>
       </c>
     </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
+    <row r="339">
+      <c r="A339" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 예술단원･운동부 등 보상금 (301)</t>
         </is>
       </c>
-      <c r="B510" t="inlineStr">
+      <c r="B339" t="inlineStr">
         <is>
           <t>12. 예술단원･운동부 등 보상금
 1. 지방자치단체가 운영하는 예술단원에 대한 인건비 및 운영비
@@ -8078,26 +5957,26 @@
         </is>
       </c>
     </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
+    <row r="340">
+      <c r="A340" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 사회성과보상금 (301)</t>
         </is>
       </c>
-      <c r="B511" t="inlineStr">
+      <c r="B340" t="inlineStr">
         <is>
           <t>13. 사회성과보상금
 1. 지방자치단체가 법령 또는 조례에 따라 사회성과보상사업 수행자에게 지급하는 반대 급부적 경비</t>
         </is>
       </c>
     </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
+    <row r="341">
+      <c r="A341" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 기타 보상금 (301)</t>
         </is>
       </c>
-      <c r="B512" t="inlineStr">
+      <c r="B341" t="inlineStr">
         <is>
           <t>14. 기타 보상금
 1. 법령 또는 조례에 민간인에게 반대 급부적 경비를 지급 하도록 규정되어 있는 경우의 보상금 또는 물품
@@ -8107,13 +5986,13 @@
         </is>
       </c>
     </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
+    <row r="342">
+      <c r="A342" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 민간인 이주보상금 (302)</t>
         </is>
       </c>
-      <c r="B513" t="inlineStr">
+      <c r="B342" t="inlineStr">
         <is>
           <t>01. 민간인 이주보상금
 1. 「공공용지의 취득 및 손실보상에 관한 특별법」에 대한 댐건설 등 대규모 공공사업의 수행을 위하여 이주자에게 대가없이(토지의 매입에 의하지 않고 토지를 제공받는 경우 포함) 지급하는 이주 정착비 등 이주보상비
@@ -8121,13 +6000,13 @@
         </is>
       </c>
     </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
+    <row r="343">
+      <c r="A343" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 민간인 재해 및 복구활동 보상금 (302)</t>
         </is>
       </c>
-      <c r="B514" t="inlineStr">
+      <c r="B343" t="inlineStr">
         <is>
           <t>02. 민간인 재해 및 복구활동 보상금
 1. 재해대책을 위하여 민간인(단체)에게 지급하는 보상금 및 물품(재해보상비, 장제비 등)
@@ -8135,13 +6014,13 @@
         </is>
       </c>
     </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
+    <row r="344">
+      <c r="A344" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 포상금 (303)</t>
         </is>
       </c>
-      <c r="B515" t="inlineStr">
+      <c r="B344" t="inlineStr">
         <is>
           <t>01. 포상금
 1. 모범공무원 산업시찰
@@ -8154,13 +6033,13 @@
         </is>
       </c>
     </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
+    <row r="345">
+      <c r="A345" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 연금부담금 (304)</t>
         </is>
       </c>
-      <c r="B516" t="inlineStr">
+      <c r="B345" t="inlineStr">
         <is>
           <t>01. 연금부담금
 1.「공무원연금법」에 따라 지방자치단체가 부담하는 연금부담금, 퇴직수당부담금
@@ -8168,13 +6047,13 @@
         </is>
       </c>
     </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
+    <row r="346">
+      <c r="A346" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 의원상해부담금 (304)</t>
         </is>
       </c>
-      <c r="B517" t="inlineStr">
+      <c r="B346" t="inlineStr">
         <is>
           <t>03. 의원상해부담금
 1. 법령 또는 조례에 의해 지급하는 의원상해부담금
@@ -8187,13 +6066,13 @@
         </is>
       </c>
     </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
+    <row r="347">
+      <c r="A347" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 배상금등 (305)</t>
         </is>
       </c>
-      <c r="B518" t="inlineStr">
+      <c r="B347" t="inlineStr">
         <is>
           <t>01. 배상금등
 1. 손해배상금, 국가배상금
@@ -8202,13 +6081,13 @@
         </is>
       </c>
     </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
+    <row r="348">
+      <c r="A348" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 출연금 (306)</t>
         </is>
       </c>
-      <c r="B519" t="inlineStr">
+      <c r="B348" t="inlineStr">
         <is>
           <t>01. 출연금
 1.지방자치단체가 법령 또는 조례에 의거 민간 및 법인에게 지원하는 경비
@@ -8223,13 +6102,13 @@
         </is>
       </c>
     </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
+    <row r="349">
+      <c r="A349" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 의료 및 회복비 (307)</t>
         </is>
       </c>
-      <c r="B520" t="inlineStr">
+      <c r="B349" t="inlineStr">
         <is>
           <t>01. 의료 및 회복비
 1. 의료비
@@ -8249,13 +6128,13 @@
         </is>
       </c>
     </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
+    <row r="350">
+      <c r="A350" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 민간경상사업보조 (307)</t>
         </is>
       </c>
-      <c r="B521" t="inlineStr">
+      <c r="B350" t="inlineStr">
         <is>
           <t>02. 민간경상사업보조
 1.민간이 행하는 사업에 대하여 자치단체가 이를 권장하기 위하여 교부하는 것으로 자본적 경비를 제외한 보조금
@@ -8264,13 +6143,13 @@
         </is>
       </c>
     </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
+    <row r="351">
+      <c r="A351" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 민간단체 법정운영비보조 (307)</t>
         </is>
       </c>
-      <c r="B522" t="inlineStr">
+      <c r="B351" t="inlineStr">
         <is>
           <t>03. 민간단체 법정운영비보조
 1.「지방재정법」 제17조 및 「지방보조금법」 제6조제2항 따라 운영비를 지원할 수 있는 단체 등에 지원하는 경비
@@ -8282,13 +6161,13 @@
         </is>
       </c>
     </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
+    <row r="352">
+      <c r="A352" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 민간행사사업보조 (307)</t>
         </is>
       </c>
-      <c r="B523" t="inlineStr">
+      <c r="B352" t="inlineStr">
         <is>
           <t>04. 민간행사사업보조
 1.민간이 주관 또는 주최하는 행사에 대하여 자본적 경비를 제외한 보조금
@@ -8297,13 +6176,13 @@
         </is>
       </c>
     </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
+    <row r="353">
+      <c r="A353" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 민간위탁금 (307)</t>
         </is>
       </c>
-      <c r="B524" t="inlineStr">
+      <c r="B353" t="inlineStr">
         <is>
           <t>05. 민간위탁금
 1.국가 또는 지방자치단체가 법령 및 조례에 의하여 민간인에게 위탁관리시키는 사업 중 기금성격의 사업비로서 사업이 종료되거나 위탁이 폐지될 때에는 전액 국고 또는 지방비로 회수가 가능한 사업
@@ -8313,13 +6192,13 @@
         </is>
       </c>
     </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
+    <row r="354">
+      <c r="A354" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 연금지급금 (307)</t>
         </is>
       </c>
-      <c r="B525" t="inlineStr">
+      <c r="B354" t="inlineStr">
         <is>
           <t>07. 연금지급금
 1. 101-02(기타직보수)에 계상하는 기타직 보수지급 대상자에 대한 퇴직금
@@ -8327,26 +6206,26 @@
         </is>
       </c>
     </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
+    <row r="355">
+      <c r="A355" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 이차보전금 (307)</t>
         </is>
       </c>
-      <c r="B526" t="inlineStr">
+      <c r="B355" t="inlineStr">
         <is>
           <t>08. 이차보전금
 1.특정목적을 위하여 필요한 자금이 일반 대출 금리 또는 조달금리보다 낮은 금리로 조성될 수 있도록 하기 위하여 지원되는 경비(환차손 포함)</t>
         </is>
       </c>
     </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
+    <row r="356">
+      <c r="A356" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 운수업계보조금 (307)</t>
         </is>
       </c>
-      <c r="B527" t="inlineStr">
+      <c r="B356" t="inlineStr">
         <is>
           <t>09. 운수업계보조금
 1.에너지세제 개편에 따라 유류세액 인상분 보전을 위해 버스･택시･화물운송사업용 자동차운수업계에 지급되는 보조금
@@ -8355,13 +6234,13 @@
         </is>
       </c>
     </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
+    <row r="357">
+      <c r="A357" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 사회복지시설 법정운영비 보조 (307)</t>
         </is>
       </c>
-      <c r="B528" t="inlineStr">
+      <c r="B357" t="inlineStr">
         <is>
           <t>10. 사회복지시설 법정운영비 보조
 1. 주민 복지를 위해 법령의 명시적 근거에 따라 사회복지시설에 대하여 운영비 지원 목적으로 편성하는 보조금
@@ -8370,13 +6249,13 @@
         </is>
       </c>
     </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
+    <row r="358">
+      <c r="A358" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 사회복지사업보조 (307)</t>
         </is>
       </c>
-      <c r="B529" t="inlineStr">
+      <c r="B358" t="inlineStr">
         <is>
           <t>11. 사회복지사업보조
 1. 주민 복지를 위해 법령 또는 조례상 지원기준에 따라 의무적으로 지출하는 보조금 또는 자치단체가 권장하는 다음 각 호의 사업을 위하여 지급하는 보조금으로서 자본적 경비를 제외한 경비
@@ -8387,13 +6266,13 @@
         </is>
       </c>
     </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
+    <row r="359">
+      <c r="A359" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 민간인위탁교육비 (307)</t>
         </is>
       </c>
-      <c r="B530" t="inlineStr">
+      <c r="B359" t="inlineStr">
         <is>
           <t>12. 민간인위탁교육비
 - 법령 또는 조례 등에 따라 자치단체 사무를 위해 민간인을 위탁교육할 경우 위탁기관에 지급할 위탁교육비
@@ -8401,13 +6280,13 @@
         </is>
       </c>
     </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
+    <row r="360">
+      <c r="A360" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 자치단체 경상보조금 (308)</t>
         </is>
       </c>
-      <c r="B531" t="inlineStr">
+      <c r="B360" t="inlineStr">
         <is>
           <t>01. 자치단체 경상보조금
 이전
@@ -8416,13 +6295,13 @@
         </is>
       </c>
     </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
+    <row r="361">
+      <c r="A361" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 징수교부금 (308)</t>
         </is>
       </c>
-      <c r="B532" t="inlineStr">
+      <c r="B361" t="inlineStr">
         <is>
           <t>02. 징수교부금
 1.국가 또는 지방자치단체가 법령 또는 조례의 규정에 따라 위임한 시‧도세, 사용료, 수수료, 부담금 등 징수사무에 수반하는 경비로서 지방자치단체 지급하는 교부금
@@ -8430,65 +6309,65 @@
         </is>
       </c>
     </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
+    <row r="362">
+      <c r="A362" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 자치구 조정교부금 (308)</t>
         </is>
       </c>
-      <c r="B533" t="inlineStr">
+      <c r="B362" t="inlineStr">
         <is>
           <t>03. 자치구 조정교부금
 1. 「지방재정법」 제29조의2 규정에 따라 특·광역시에서 자치구에 교부하는 조정교부금</t>
         </is>
       </c>
     </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
+    <row r="363">
+      <c r="A363" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 시·군 조정교부금 (308)</t>
         </is>
       </c>
-      <c r="B534" t="inlineStr">
+      <c r="B363" t="inlineStr">
         <is>
           <t>04. 시·군 조정교부금
 1. 「지방재정법」 제29조제1항 및 제2항 규정에 따라 광역시·도에서 시·군에 교부하는 조정교부금</t>
         </is>
       </c>
     </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
+    <row r="364">
+      <c r="A364" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 자치구 기타 재원조정비 (308)</t>
         </is>
       </c>
-      <c r="B535" t="inlineStr">
+      <c r="B364" t="inlineStr">
         <is>
           <t>05. 자치구 기타 재원조정비
 1. 「지방재정법」제29조의2 규정에 따라 조정교부금 이외에 자치구에 교부되는 재원조정경비</t>
         </is>
       </c>
     </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
+    <row r="365">
+      <c r="A365" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 시·군 기타 재원조정비 (308)</t>
         </is>
       </c>
-      <c r="B536" t="inlineStr">
+      <c r="B365" t="inlineStr">
         <is>
           <t>06. 시·군 기타 재원조정비
 1. 「지방재정법」제29조 제1항 및 제2항 규정에 따른 조정교부금 이외에 시·군에 교부되는 재원조정경비</t>
         </is>
       </c>
     </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
+    <row r="366">
+      <c r="A366" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 자치단체 간 부담금 (308)</t>
         </is>
       </c>
-      <c r="B537" t="inlineStr">
+      <c r="B366" t="inlineStr">
         <is>
           <t>07. 자치단체 간 부담금
 1.지방재정법 제12687호(2014.5.28.개정) 부칙 제17조의 규정 등에 의해 시·군·구에서 시·도에 부담금으로 부담하는 경비
@@ -8497,13 +6376,13 @@
         </is>
       </c>
     </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
+    <row r="367">
+      <c r="A367" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 교육기관에 대한 보조 (308)</t>
         </is>
       </c>
-      <c r="B538" t="inlineStr">
+      <c r="B367" t="inlineStr">
         <is>
           <t>08. 교육기관에 대한 보조
 1.시·도 및 시·군·자치구가 「지방자치단체의 교육경비 보조에 관한 규정」제2조에 따라 관할구역 안에 있는 고등학교 이하 각급 학교의 교육에 소요되는 비용을 보조하는 경비로, 조례에 따라 교육기관에 직접 또는 교육감·교육장을 통하여 보조
@@ -8516,13 +6395,13 @@
         </is>
       </c>
     </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
+    <row r="368">
+      <c r="A368" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 지역대학에 대한 경상보조 (308)</t>
         </is>
       </c>
-      <c r="B539" t="inlineStr">
+      <c r="B368" t="inlineStr">
         <is>
           <t>09. 지역대학에 대한 경상보조
 1. 「지방대학 및 지역균형인재 육성에 관한 법률」에 따라 대학에 지원하는 자본형성적 사업 외의 경비
@@ -8530,13 +6409,13 @@
         </is>
       </c>
     </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
+    <row r="369">
+      <c r="A369" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 시‧군‧구 교육비특별회계 법정전출금 (308)</t>
         </is>
       </c>
-      <c r="B540" t="inlineStr">
+      <c r="B369" t="inlineStr">
         <is>
           <t>10. 시‧군‧구 교육비특별회계 법정전출금
 1. 「지방교육재정교부금법」 제14조에 따른 시‧군‧구 부담경비
@@ -8546,13 +6425,13 @@
         </is>
       </c>
     </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
+    <row r="370">
+      <c r="A370" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 예비군육성지원 경상보조 (308)</t>
         </is>
       </c>
-      <c r="B541" t="inlineStr">
+      <c r="B370" t="inlineStr">
         <is>
           <t>12. 예비군육성지원 경상보조
 1.「예비군법」 제14조의3제1항 및 같은 법 시행령 제32조제1항의 규정에 따라 관할구역 안에 있는 예비군부대의 지원·육성에 소요되는 경비
@@ -8561,13 +6440,13 @@
         </is>
       </c>
     </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
+    <row r="371">
+      <c r="A371" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 공기관 등에 대한 경상적 위탁사업비 (308)</t>
         </is>
       </c>
-      <c r="B542" t="inlineStr">
+      <c r="B371" t="inlineStr">
         <is>
           <t>13. 공기관 등에 대한 경상적 위탁사업비
 1. 광역사업 등 당해 자치단체가 시행하여야 할 자본형성적 사업 외의 경비를 공기관에 위임 또는 위탁, 대행하여 시행할 경우 부담하는 제반 경비
@@ -8580,13 +6459,13 @@
         </is>
       </c>
     </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
+    <row r="372">
+      <c r="A372" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 기타부담금 (308)</t>
         </is>
       </c>
-      <c r="B543" t="inlineStr">
+      <c r="B372" t="inlineStr">
         <is>
           <t>14. 기타부담금
 1.법령에 의거 국가등에 부담해야 할 경비
@@ -8595,13 +6474,13 @@
         </is>
       </c>
     </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
+    <row r="373">
+      <c r="A373" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 국외경상이전 (310)</t>
         </is>
       </c>
-      <c r="B544" t="inlineStr">
+      <c r="B373" t="inlineStr">
         <is>
           <t>01. 국외경상이전
 1. 국외교포 또는 외국기관에 지급하는 경상보조금과 교포 교육경비
@@ -8609,13 +6488,13 @@
         </is>
       </c>
     </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
+    <row r="374">
+      <c r="A374" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 국제부담금 (310)</t>
         </is>
       </c>
-      <c r="B545" t="inlineStr">
+      <c r="B374" t="inlineStr">
         <is>
           <t>02. 국제부담금
 1.법령, 조약, 협정 등에 의하여 설립된 법인, 외국기관, 국제기관, 외국인 또는 외국과 공동으로 설립된 기관 및 조합에 대하여 지방비에서 직접 지급할 국제부담금 및 조약 또는 협정에 의하여 지방자치단체가 부담하도록 규정된 부담금
@@ -8623,13 +6502,13 @@
         </is>
       </c>
     </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
+    <row r="375">
+      <c r="A375" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 기타차입금 이자상환 (311)</t>
         </is>
       </c>
-      <c r="B546" t="inlineStr">
+      <c r="B375" t="inlineStr">
         <is>
           <t>05. 기타차입금 이자상환
 1. 601-05(기타국내차입금원금상환)항목의 이자
@@ -8638,13 +6517,13 @@
         </is>
       </c>
     </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
+    <row r="376">
+      <c r="A376" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 시설비 (401)</t>
         </is>
       </c>
-      <c r="B547" t="inlineStr">
+      <c r="B376" t="inlineStr">
         <is>
           <t>01. 시설비
 부대비
@@ -8688,13 +6567,13 @@
         </is>
       </c>
     </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
+    <row r="377">
+      <c r="A377" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 감리비 (401)</t>
         </is>
       </c>
-      <c r="B548" t="inlineStr">
+      <c r="B377" t="inlineStr">
         <is>
           <t>02. 감리비
 1.시설비 또는 도로 및 하천, 항만 등의 대수선비와 자산취득에 직접 소요되는 공사 감리비나 문화재수리를 위한 감리비
@@ -8702,13 +6581,13 @@
         </is>
       </c>
     </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
+    <row r="378">
+      <c r="A378" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 시설부대비 (401)</t>
         </is>
       </c>
-      <c r="B549" t="inlineStr">
+      <c r="B378" t="inlineStr">
         <is>
           <t>03. 시설부대비
 1.시설비 또는 도로 및 하천, 항만 등의 대수선비 (장비임차료 포함)와 재산취득에 직접 소요되는 부대경비로서 시공관리에 필요한 공공요금
@@ -8735,13 +6614,13 @@
         </is>
       </c>
     </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
+    <row r="379">
+      <c r="A379" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 행사관련시설비 (401)</t>
         </is>
       </c>
-      <c r="B550" t="inlineStr">
+      <c r="B379" t="inlineStr">
         <is>
           <t>04. 행사관련시설비
 1. 행사장 각종시설 및 장치 등
@@ -8750,13 +6629,13 @@
         </is>
       </c>
     </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
+    <row r="380">
+      <c r="A380" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 민간자본사업보조(자체재원) (402)</t>
         </is>
       </c>
-      <c r="B551" t="inlineStr">
+      <c r="B380" t="inlineStr">
         <is>
           <t>01. 민간자본사업보조(자체재원)
 1.민간의 자본형성을 위하여 민간이 추진하는 사업을 권장할 목적으로 민간에게 자치단체 자체 재원으로 직접 지급하는 보조금
@@ -8765,13 +6644,13 @@
         </is>
       </c>
     </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
+    <row r="381">
+      <c r="A381" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 민간자본사업보조(이전재원) (402)</t>
         </is>
       </c>
-      <c r="B552" t="inlineStr">
+      <c r="B381" t="inlineStr">
         <is>
           <t>02. 민간자본사업보조(이전재원)
 1.민간의 자본형성을 위하여 민간이 추진하는 사업을 권장할 목적으로 민간에게 국비 또는 시도비를 시도 및 시군구에서 지급하는 보조금
@@ -8780,13 +6659,13 @@
         </is>
       </c>
     </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
+    <row r="382">
+      <c r="A382" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 민간위탁사업비 (402)</t>
         </is>
       </c>
-      <c r="B553" t="inlineStr">
+      <c r="B382" t="inlineStr">
         <is>
           <t>03. 민간위탁사업비
 1. 자치단체가 직접 추진하여야 할 사업으로서 법령의 규정에 의하여 민간에 위임 또는 위탁, 대행시키는 사업의 사업비
@@ -8796,13 +6675,13 @@
         </is>
       </c>
     </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
+    <row r="383">
+      <c r="A383" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 자치단체자본보조 (403)</t>
         </is>
       </c>
-      <c r="B554" t="inlineStr">
+      <c r="B383" t="inlineStr">
         <is>
           <t>01. 자치단체자본보조
 자본이전
@@ -8811,13 +6690,13 @@
         </is>
       </c>
     </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
+    <row r="384">
+      <c r="A384" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 공기관 등에 대한 자본적 위탁사업비 (403)</t>
         </is>
       </c>
-      <c r="B555" t="inlineStr">
+      <c r="B384" t="inlineStr">
         <is>
           <t>02. 공기관 등에 대한 자본적 위탁사업비
 1.광역사업 등 당해 자치단체가 시행하여야 할 자본형성적 사업을 공기관에 위임 또는 위탁, 대행하여 시행할 경우 부담하는 제반경비
@@ -8828,13 +6707,13 @@
         </is>
       </c>
     </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
+    <row r="385">
+      <c r="A385" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 예비군육성지원자본보조 (403)</t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
+      <c r="B385" t="inlineStr">
         <is>
           <t>03. 예비군육성지원자본보조
 자본이전
@@ -8843,13 +6722,13 @@
         </is>
       </c>
     </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
+    <row r="386">
+      <c r="A386" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 지역대학에 대한 자본보조 (403)</t>
         </is>
       </c>
-      <c r="B557" t="inlineStr">
+      <c r="B386" t="inlineStr">
         <is>
           <t>04. 지역대학에 대한 자본보조
 1. 「지방대학 및 지역균형인재 육성에 관한 법률」에 따라 대학에 지원하는 자본형성적 사업 경비
@@ -8857,13 +6736,13 @@
         </is>
       </c>
     </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
+    <row r="387">
+      <c r="A387" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 자산 및 물품취득비 (405)</t>
         </is>
       </c>
-      <c r="B558" t="inlineStr">
+      <c r="B387" t="inlineStr">
         <is>
           <t>01. 자산 및 물품취득비
 1.건물 및 공작물(토지를 포함하여 취득하는 경우에 토지매입비가 구분되지 않는 경우는 이를 포함), 대규모 설비, 선박, 항공기 및 입목죽 등의 취득비
@@ -8879,13 +6758,13 @@
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
+    <row r="388">
+      <c r="A388" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 기타자본이전 (406)</t>
         </is>
       </c>
-      <c r="B559" t="inlineStr">
+      <c r="B388" t="inlineStr">
         <is>
           <t>01. 기타자본이전
 1. 차관물자 용역대
@@ -8904,26 +6783,26 @@
         </is>
       </c>
     </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
+    <row r="389">
+      <c r="A389" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 통화금융기관 융자금 (501)</t>
         </is>
       </c>
-      <c r="B560" t="inlineStr">
+      <c r="B389" t="inlineStr">
         <is>
           <t>02. 통화금융기관 융자금
 1. 민간인에게 융자를 목적으로 금융기관에 대하여 융자하는 융자금  (예) 주택개량사업 등</t>
         </is>
       </c>
     </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
+    <row r="390">
+      <c r="A390" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 공사·공단 등 융자금 (501)</t>
         </is>
       </c>
-      <c r="B561" t="inlineStr">
+      <c r="B390" t="inlineStr">
         <is>
           <t>03. 공사·공단 등 융자금
 1. 지방자치단체가 지방공사·공단에 융자하는 융자금
@@ -8931,13 +6810,13 @@
         </is>
       </c>
     </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
+    <row r="391">
+      <c r="A391" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 출자금 (502)</t>
         </is>
       </c>
-      <c r="B562" t="inlineStr">
+      <c r="B391" t="inlineStr">
         <is>
           <t>01. 출자금
 1.융자금(501)을 제외한 「지방재정법」 제18조 규정에 따른 지방자치단체 출자금
@@ -8951,26 +6830,26 @@
         </is>
       </c>
     </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
+    <row r="392">
+      <c r="A392" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 의무예치금 (602)</t>
         </is>
       </c>
-      <c r="B563" t="inlineStr">
+      <c r="B392" t="inlineStr">
         <is>
           <t>02. 의무예치금
 1. 「재난 및 안전관리 기본법 시행령」 제75조제2항에 따라 지방자치단체의 장이 의무적으로 예치·관리</t>
         </is>
       </c>
     </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
+    <row r="393">
+      <c r="A393" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 기타회계 전출금 (701)</t>
         </is>
       </c>
-      <c r="B564" t="inlineStr">
+      <c r="B393" t="inlineStr">
         <is>
           <t>01. 기타회계 전출금
 등 전출금
@@ -8978,26 +6857,26 @@
         </is>
       </c>
     </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
+    <row r="394">
+      <c r="A394" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 기금전출금 (702)</t>
         </is>
       </c>
-      <c r="B565" t="inlineStr">
+      <c r="B394" t="inlineStr">
         <is>
           <t>01. 기금전출금
 1.법령 및 조례에 의해 자치단체가 직접 관리하는 기금에 전출하는 경비(감채기금, 재해대책기금 등)</t>
         </is>
       </c>
     </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
+    <row r="395">
+      <c r="A395" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 시·도 법정전출금 (703)</t>
         </is>
       </c>
-      <c r="B566" t="inlineStr">
+      <c r="B395" t="inlineStr">
         <is>
           <t>01. 시·도 법정전출금
 1. 「지방교육재정교부금법」 제11조(단, 제8항의 경우는 교육기관에 대한 보조금으로 편성) 및 제14조, 「학교용지 확보 등에 관한 특례법」 제4조제4항 등 법령의 규정에 따른 부담금
@@ -9007,13 +6886,13 @@
         </is>
       </c>
     </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
+    <row r="396">
+      <c r="A396" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 시·도 비법정전출금 (703)</t>
         </is>
       </c>
-      <c r="B567" t="inlineStr">
+      <c r="B396" t="inlineStr">
         <is>
           <t>02. 시·도 비법정전출금
 1. 「지방교육재정교부금법」 제11조제9항 및 시·도 조례에 따라 교육·학예 진흥을 위해 부담하는 부담금
@@ -9021,13 +6900,13 @@
         </is>
       </c>
     </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
+    <row r="397">
+      <c r="A397" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 예탁금 (704)</t>
         </is>
       </c>
-      <c r="B568" t="inlineStr">
+      <c r="B397" t="inlineStr">
         <is>
           <t>01. 예탁금
 1.일반회계와 특별회계, 일반회계와 기금, 특별회계와 기금 상호간 및 특별회계 계정간의 예탁금
@@ -9035,13 +6914,13 @@
         </is>
       </c>
     </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
+    <row r="398">
+      <c r="A398" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 예수금원금 상환 (705)</t>
         </is>
       </c>
-      <c r="B569" t="inlineStr">
+      <c r="B398" t="inlineStr">
         <is>
           <t>01. 예수금원금 상환
 원리금상환
@@ -9049,26 +6928,26 @@
         </is>
       </c>
     </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
+    <row r="399">
+      <c r="A399" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 일반예비비 (801)</t>
         </is>
       </c>
-      <c r="B570" t="inlineStr">
+      <c r="B399" t="inlineStr">
         <is>
           <t>01. 일반예비비
 1. 「지방자치법」 제144조 및 「지방재정법」 제43조제1항에 따른 예비비 (각 회계별로 예산총액 대비 1% 범위 내에서 편성, 기타 특별회계의 경우 편성하지 아니할 수 있음)</t>
         </is>
       </c>
     </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
+    <row r="400">
+      <c r="A400" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 재해·재난목적예비비 (801)</t>
         </is>
       </c>
-      <c r="B571" t="inlineStr">
+      <c r="B400" t="inlineStr">
         <is>
           <t>02. 재해·재난목적예비비
 1. 「지방자치법」 제144조 및 「지방재정법」 제43조제2항에 따른예비비(예비비 편성 한도는 없음)
@@ -9076,26 +6955,26 @@
         </is>
       </c>
     </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
+    <row r="401">
+      <c r="A401" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 내부유보금 (801)</t>
         </is>
       </c>
-      <c r="B572" t="inlineStr">
+      <c r="B401" t="inlineStr">
         <is>
           <t>03. 내부유보금
 1. 지방의회의 예산심의 과정에서 삭감된 경비 중 일반예비비 등 다른 세출예산으로 편성하지 못한 경비</t>
         </is>
       </c>
     </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
+    <row r="402">
+      <c r="A402" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 국고보조금 반환금 (802)</t>
         </is>
       </c>
-      <c r="B573" t="inlineStr">
+      <c r="B402" t="inlineStr">
         <is>
           <t>01. 국고보조금 반환금
 1.지방자치단체가 국고에 반납하는 국고보조금 사용잔액
@@ -9105,13 +6984,13 @@
         </is>
       </c>
     </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
+    <row r="403">
+      <c r="A403" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 시･도비보조금 반환금 (802)</t>
         </is>
       </c>
-      <c r="B574" t="inlineStr">
+      <c r="B403" t="inlineStr">
         <is>
           <t>02. 시･도비보조금 반환금
 1.시･군･자치구가 시･도에 반납하는 시･도비보조금 사용잔액
@@ -9119,13 +6998,13 @@
         </is>
       </c>
     </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
+    <row r="404">
+      <c r="A404" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 기타 반환금 등 (802)</t>
         </is>
       </c>
-      <c r="B575" t="inlineStr">
+      <c r="B404" t="inlineStr">
         <is>
           <t>03. 기타 반환금 등
 1.과오납금, 반환금, 수표지불미청산금, 상환금, 기타 반환금
@@ -9133,13 +7012,13 @@
         </is>
       </c>
     </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
+    <row r="405">
+      <c r="A405" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 잡손금 (802)</t>
         </is>
       </c>
-      <c r="B576" t="inlineStr">
+      <c r="B405" t="inlineStr">
         <is>
           <t>04. 잡손금
 1. 결손보전 기타잡손금
@@ -9211,26 +7090,26 @@
         </is>
       </c>
     </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
+    <row r="406">
+      <c r="A406" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 공유재산 관련 서류 (802)</t>
         </is>
       </c>
-      <c r="B577" t="inlineStr">
+      <c r="B406" t="inlineStr">
         <is>
           <t>12. 공유재산 관련 서류
 ※「공유재산 및 물품관리법」제10조에 따른 중기공유재산 관리계획,「공유재산 및 물품관리법」 제10조의2에 따른 공유재산 관리계획, 공유재산 총괄현황 등</t>
         </is>
       </c>
     </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
+    <row r="407">
+      <c r="A407" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 회계와 기금간의 이전 관련 서류 (802)</t>
         </is>
       </c>
-      <c r="B578" t="inlineStr">
+      <c r="B407" t="inlineStr">
         <is>
           <t>13. 회계와 기금간의 이전 관련 서류
 14.「지방재정법」제38조제2항의 규정에 의한 지방자치단체 예산편성기준
@@ -9238,13 +7117,13 @@
         </is>
       </c>
     </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
+    <row r="408">
+      <c r="A408" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 세입예산 추계분석보고서 (802)</t>
         </is>
       </c>
-      <c r="B579" t="inlineStr">
+      <c r="B408" t="inlineStr">
         <is>
           <t>16. 세입예산 추계분석보고서
 17. 지방채증권 및 차입금에 관한 전전년도 말의 발행 및 상환실적, 전년도말 및 해당 연도말의 현재액의 추정액
@@ -9282,13 +7161,13 @@
         </is>
       </c>
     </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
+    <row r="409">
+      <c r="A409" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 참고사항 (802)</t>
         </is>
       </c>
-      <c r="B580" t="inlineStr">
+      <c r="B409" t="inlineStr">
         <is>
           <t>14. 참고사항
 ※ 사업별 설명서 편제 방식은 자치단체가 자율적으로 결정
@@ -9327,26 +7206,26 @@
         </is>
       </c>
     </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
+    <row r="410">
+      <c r="A410" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 공유재산 관련 서류 (168)</t>
         </is>
       </c>
-      <c r="B581" t="inlineStr">
+      <c r="B410" t="inlineStr">
         <is>
           <t>12. 공유재산 관련 서류
 ※「공유재산 및 물품관리법」제10조에 따른 중기공유재산 관리계획,「공유재산 및 물품관리법」 제10조의2에 따른 공유재산 관리계획, 공유재산 총괄현황 등</t>
         </is>
       </c>
     </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
+    <row r="411">
+      <c r="A411" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 회계와 기금간의 이전 관련 서류 (168)</t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
+      <c r="B411" t="inlineStr">
         <is>
           <t>13. 회계와 기금간의 이전 관련 서류
 14.「지방재정법」법 제38조제2항의 규정에 의한 지방자치단체 예산편성기준
@@ -9354,13 +7233,13 @@
         </is>
       </c>
     </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
+    <row r="412">
+      <c r="A412" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 세입예산 추계분석보고서 (168)</t>
         </is>
       </c>
-      <c r="B583" t="inlineStr">
+      <c r="B412" t="inlineStr">
         <is>
           <t>16. 세입예산 추계분석보고서
 17. 지방채증권 및 차입금에 관한 전전년도 말의 발행 및 상환실적, 전년도말 및 해당 연도말의 현재액의 추정액
@@ -9419,13 +7298,13 @@
         </is>
       </c>
     </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
+    <row r="413">
+      <c r="A413" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 경제자유구역청업무수당 (100)</t>
         </is>
       </c>
-      <c r="B584" t="inlineStr">
+      <c r="B413" t="inlineStr">
         <is>
           <t>10. 경제자유구역청업무수당
 「경제자유구역의 지정 및 운영에 관한 특별법」 제27조의2에 따른 행정기구에 근무하는 공무원
@@ -9436,13 +7315,13 @@
         </is>
       </c>
     </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
+    <row r="414">
+      <c r="A414" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 특수직무수당 (100)</t>
         </is>
       </c>
-      <c r="B585" t="inlineStr">
+      <c r="B414" t="inlineStr">
         <is>
           <t>11. 특수직무수당
 가. 각종 행정기관에 설치된 민원실에서 민원창구를 담당하여 상시로 직접 민원서류를 취급하는 공무원
@@ -9501,13 +7380,13 @@
         </is>
       </c>
     </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
+    <row r="415">
+      <c r="A415" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 우수 대민 공무원 수당 (100)</t>
         </is>
       </c>
-      <c r="B586" t="inlineStr">
+      <c r="B415" t="inlineStr">
         <is>
           <t>12. 우수 대민 공무원 수당
 경제 활력 제고 및 국민 편익 증진 등의 분야에서 우수한 성과를 창출한 공무원
@@ -9517,13 +7396,13 @@
         </is>
       </c>
     </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
+    <row r="416">
+      <c r="A416" t="inlineStr">
         <is>
           <t>[예산편성 운영기준] 비상근무수당 (100)</t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
+      <c r="B416" t="inlineStr">
         <is>
           <t>13. 비상근무수당
 재난의 발생으로 비상근무 명령을 받고 근무하는 공무원으로서 다음 각 목의 어느 하나에 해당하는 공무원
@@ -11441,13 +9320,13 @@
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
+    <row r="417">
+      <c r="A417" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q1. 세종시에서 오송으로 출장 시 근무지 내 출장으로 처리할 수 있는지?</t>
         </is>
       </c>
-      <c r="B588" t="inlineStr">
+      <c r="B417" t="inlineStr">
         <is>
           <t>[질문] 세종시에서 오송으로 출장 시 근무지 내 출장으로 처리할 수 있는지?
 [답변]
@@ -11460,13 +9339,13 @@
         </is>
       </c>
     </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
+    <row r="418">
+      <c r="A418" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q2. 출장명령이 있을 경우, 반드시 출장여비를 지급해야 하는지?</t>
         </is>
       </c>
-      <c r="B589" t="inlineStr">
+      <c r="B418" t="inlineStr">
         <is>
           <t>[질문] 출장명령이 있을 경우, 반드시 출장여비를 지급해야 하는지?
 [답변]
@@ -11480,13 +9359,13 @@
         </is>
       </c>
     </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
+    <row r="419">
+      <c r="A419" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q3. 서무담당자가 금융업무처리를 위해 근처 은행을 방문하는 경우, 근무지 내 출장여비를 지급해야 하는지?</t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
+      <c r="B419" t="inlineStr">
         <is>
           <t>[질문] 서무담당자가 금융업무처리를 위해 근처 은행을 방문하는 경우, 근무지 내 출장여비를 지급해야 하는지?
 [답변]
@@ -11497,13 +9376,13 @@
         </is>
       </c>
     </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
+    <row r="420">
+      <c r="A420" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q4. 운전원이 근무지 내에서 업무수행을 위해 차량을 운행하는 경우, 근무지 내 출장여비를 지급해야 하는지</t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
+      <c r="B420" t="inlineStr">
         <is>
           <t>[질문] 운전원이 근무지 내에서 업무수행을 위해 차량을 운행하는 경우, 근무지 내 출장여비를 지급해야 하는지?
 [답변]
@@ -11514,13 +9393,13 @@
         </is>
       </c>
     </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
+    <row r="421">
+      <c r="A421" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q5. 운전원이 1박2일 일정으로 근무지 외 장소로 차량을 운전한 경우, 출장여비 지급여부는?</t>
         </is>
       </c>
-      <c r="B592" t="inlineStr">
+      <c r="B421" t="inlineStr">
         <is>
           <t>[질문] 운전원이 1박2일 일정으로 근무지 외 장소로 차량을 운전한 경우, 출장여비 지급여부는?
 [답변]
@@ -11533,13 +9412,13 @@
         </is>
       </c>
     </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
+    <row r="422">
+      <c r="A422" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q6. 오전에 근무지 내 출장을 다녀온 후, 동일한 날에 근무지 외 출장을 다녀온 경우, 여비지급은 어떻게</t>
         </is>
       </c>
-      <c r="B593" t="inlineStr">
+      <c r="B422" t="inlineStr">
         <is>
           <t>[질문] 오전에 근무지 내 출장을 다녀온 후, 동일한 날에 근무지 외 출장을 다녀온 경우, 여비지급은 어떻게 해야 하는지?
 [답변]
@@ -11554,13 +9433,13 @@
         </is>
       </c>
     </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
+    <row r="423">
+      <c r="A423" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q7. 근무지 내 출장 중에 업무수행과 관련한 만찬이 포함된 경우, 출장여비 지급 방법은?</t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
+      <c r="B423" t="inlineStr">
         <is>
           <t>[질문] 근무지 내 출장 중에 업무수행과 관련한 만찬이 포함된 경우, 출장여비 지급 방법은?
 [답변]
@@ -11570,13 +9449,13 @@
         </is>
       </c>
     </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
+    <row r="424">
+      <c r="A424" t="inlineStr">
         <is>
           <t xml:space="preserve">[공무원 여비 100문100답] Q8. 근무지 내 출장 시 차량을 렌트하여 이용한 경우, 여비 항목에서 해당 차량렌트비(임차료)를 지급할 </t>
         </is>
       </c>
-      <c r="B595" t="inlineStr">
+      <c r="B424" t="inlineStr">
         <is>
           <t>[질문] 근무지 내 출장 시 차량을 렌트하여 이용한 경우, 여비 항목에서 해당 차량렌트비(임차료)를 지급할 수 있는지?
 [답변]
@@ -11590,13 +9469,13 @@
         </is>
       </c>
     </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
+    <row r="425">
+      <c r="A425" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q9. 불가피하게 숙박을 해야 하는 근무지 내 출장에 대해 숙박비를 지급할 수 있는지?</t>
         </is>
       </c>
-      <c r="B596" t="inlineStr">
+      <c r="B425" t="inlineStr">
         <is>
           <t>[질문] 불가피하게 숙박을 해야 하는 근무지 내 출장에 대해 숙박비를 지급할 수 있는지?
 [답변]
@@ -11608,13 +9487,13 @@
         </is>
       </c>
     </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
+    <row r="426">
+      <c r="A426" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q10. 오전 09시~11시까지 근무지 내 출장, 오후 13시~17시까지 근무지 내 출장을 각각 다녀온 경우</t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
+      <c r="B426" t="inlineStr">
         <is>
           <t>[질문] 오전 09시~11시까지 근무지 내 출장, 오후 13시~17시까지 근무지 내 출장을 각각 다녀온 경우, 여비 지급은?
 [답변]
@@ -11624,13 +9503,13 @@
         </is>
       </c>
     </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
+    <row r="427">
+      <c r="A427" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q11. 하루 동안 4시간 미만 근무지 내 출장을 여러 차례 간 경우, 여비 지급 방법은?</t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
+      <c r="B427" t="inlineStr">
         <is>
           <t>[질문] 하루 동안 4시간 미만 근무지 내 출장을 여러 차례 간 경우, 여비 지급 방법은?
 [답변]
@@ -11642,13 +9521,13 @@
         </is>
       </c>
     </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
+    <row r="428">
+      <c r="A428" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q12. 왕복 2㎞ 이내의 근거리 출장을 다녀온 경우, 여비 지급 방법은?</t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
+      <c r="B428" t="inlineStr">
         <is>
           <t>[질문] 왕복 2㎞ 이내의 근거리 출장을 다녀온 경우, 여비 지급 방법은?
 [답변]
@@ -11666,13 +9545,13 @@
         </is>
       </c>
     </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
+    <row r="429">
+      <c r="A429" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q13. 당해 출장이 왕복 2km 이내에 해당하는 지 여부를 판단하기 위한 출장거리 계산시, 근무지에서 출장</t>
         </is>
       </c>
-      <c r="B600" t="inlineStr">
+      <c r="B429" t="inlineStr">
         <is>
           <t>[질문] 당해 출장이 왕복 2km 이내에 해당하는 지 여부를 판단하기 위한 출장거리 계산시, 근무지에서 출장지까지의 거리는 지도상의 직선거리로 봐야 하는지, 아니면 대중교통을 타고 이동하는 거리로 봐야 하는지?
 [답변]
@@ -11685,13 +9564,13 @@
         </is>
       </c>
     </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
+    <row r="430">
+      <c r="A430" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q14. 개인 철도마일리지를 사용하여 철도승차권(무료 또는 일부 할인)을 구매하여 근무지 외 출장을 간 경우</t>
         </is>
       </c>
-      <c r="B601" t="inlineStr">
+      <c r="B430" t="inlineStr">
         <is>
           <t>[질문] 개인 철도마일리지를 사용하여 철도승차권(무료 또는 일부 할인)을 구매하여 근무지 외 출장을 간 경우, 운임 지급 방법은?
 [답변]
@@ -11701,13 +9580,13 @@
         </is>
       </c>
     </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
+    <row r="431">
+      <c r="A431" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q15. 서울 소재 기관 근무자의 전체 출장일정(5.1.~5.15.)이 다음과 같을 경우, 총 지급되는 일비</t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
+      <c r="B431" t="inlineStr">
         <is>
           <t>[질문] 서울 소재 기관 근무자의 전체 출장일정(5.1.~5.15.)이 다음과 같을 경우, 총 지급되는 일비는(공적마일리지 사용)? - 5.1~5.5 부산출장(KTX 이용) / 5.6~5.15 제주출장(항공기 이용) - 단, 부산→제주는 공적 항공마일리지 보너스항공권(이코노미 16만원 상당) 이용, 제주→서울은 공적 항공마일리지 미사용
 [답변]
@@ -11721,13 +9600,13 @@
         </is>
       </c>
     </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
+    <row r="432">
+      <c r="A432" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q16. 공적 항공마일리지가 부족하여 사적 마일리지를 합산하여 사용할 경우 항공운임 산출 방법은?</t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
+      <c r="B432" t="inlineStr">
         <is>
           <t>[질문] 공적 항공마일리지가 부족하여 사적 마일리지를 합산하여 사용할 경우 항공운임 산출 방법은?
 [답변]
@@ -11739,13 +9618,13 @@
         </is>
       </c>
     </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
+    <row r="433">
+      <c r="A433" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q17. 국내선 항공기를 이용하여 출장을 갈 경우에도 공적 항공마일리지 사용가능 여부를 확인해야 하는지?</t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
+      <c r="B433" t="inlineStr">
         <is>
           <t>[질문] 국내선 항공기를 이용하여 출장을 갈 경우에도 공적 항공마일리지 사용가능 여부를 확인해야 하는지?
 [답변]
@@ -11762,13 +9641,13 @@
         </is>
       </c>
     </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
+    <row r="434">
+      <c r="A434" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q18. 서울에서 제주도로 출장 시, 보유하고 있는 공적 항공마일리지를 사용하려고 하였으나 2등석 보너스좌석</t>
         </is>
       </c>
-      <c r="B605" t="inlineStr">
+      <c r="B434" t="inlineStr">
         <is>
           <t>[질문] 서울에서 제주도로 출장 시, 보유하고 있는 공적 항공마일리지를 사용하려고 하였으나 2등석 보너스좌석이 없는 경우, 공적 항공마일리지 사용방법은?
 [답변]
@@ -11781,13 +9660,13 @@
         </is>
       </c>
     </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
+    <row r="435">
+      <c r="A435" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q19. 근무지는 세종청사(세종), 원거주지는 부산인 공무원이 부산으로 출장 (1박2일, 월~화)을 가는 경</t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
+      <c r="B435" t="inlineStr">
         <is>
           <t>[질문] 근무지는 세종청사(세종), 원거주지는 부산인 공무원이 부산으로 출장 (1박2일, 월~화)을 가는 경우, 금요일에 원거주지인 부산으로 이동 (KTX)하여 집에서 숙박한 후, 화요일에 세종으로 복귀(KTX)한 경우, 운임 등 여비지급 방법은?
 [답변]
@@ -11799,13 +9678,13 @@
         </is>
       </c>
     </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
+    <row r="436">
+      <c r="A436" t="inlineStr">
         <is>
           <t xml:space="preserve">[공무원 여비 100문100답] Q20. 자가용을 이용한 근무지 외 출장 시 근무지는 세종청사, 출발지는 대전 소재 거주지, 출장 목적지는 </t>
         </is>
       </c>
-      <c r="B607" t="inlineStr">
+      <c r="B436" t="inlineStr">
         <is>
           <t>[질문] 자가용을 이용한 근무지 외 출장 시 근무지는 세종청사, 출발지는 대전 소재 거주지, 출장 목적지는 부산광역시청인 경우, 자동차 연료비 지급을 위한 거리계산 방법은?
 [답변]
@@ -11818,13 +9697,13 @@
         </is>
       </c>
     </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
+    <row r="437">
+      <c r="A437" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q21. 자가용을 이용하여 근무지 외 출장을 간 경우, 운임 지급 방법은?</t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
+      <c r="B437" t="inlineStr">
         <is>
           <t>[질문] 자가용을 이용하여 근무지 외 출장을 간 경우, 운임 지급 방법은?
 [답변]
@@ -11842,13 +9721,13 @@
         </is>
       </c>
     </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
+    <row r="438">
+      <c r="A438" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q22. 겸직허가를 받아 대학으로 출강하는 경우, 소속기관에서 여비를 받을 수 있는지?</t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B438" t="inlineStr">
         <is>
           <t>[질문] 겸직허가를 받아 대학으로 출강하는 경우, 소속기관에서 여비를 받을 수 있는지?
 [답변]
@@ -11858,13 +9737,13 @@
         </is>
       </c>
     </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
+    <row r="439">
+      <c r="A439" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q23. 항공기를 이용하여 출장을 갈 경우, 사전 좌석지정 비용을 항공운임으로 지급할 수 있는지?</t>
         </is>
       </c>
-      <c r="B610" t="inlineStr">
+      <c r="B439" t="inlineStr">
         <is>
           <t>[질문] 항공기를 이용하여 출장을 갈 경우, 사전 좌석지정 비용을 항공운임으로 지급할 수 있는지?
 [답변]
@@ -11874,13 +9753,13 @@
         </is>
       </c>
     </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
+    <row r="440">
+      <c r="A440" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q24. 공무원이 시험감독(감독수당 10만원)을 받을 경우, 운임, 식비, 일비 등의 여비를 지급할 수 있는</t>
         </is>
       </c>
-      <c r="B611" t="inlineStr">
+      <c r="B440" t="inlineStr">
         <is>
           <t>[질문] 공무원이 시험감독(감독수당 10만원)을 받을 경우, 운임, 식비, 일비 등의 여비를 지급할 수 있는지?
 [답변]
@@ -11889,13 +9768,13 @@
         </is>
       </c>
     </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
+    <row r="441">
+      <c r="A441" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q25. 섬 지역으로 근무지 외 출장 시, 개인차량을 이용한 경우 발생한 도선료 지급 방법은?</t>
         </is>
       </c>
-      <c r="B612" t="inlineStr">
+      <c r="B441" t="inlineStr">
         <is>
           <t>[질문] 섬 지역으로 근무지 외 출장 시, 개인차량을 이용한 경우 발생한 도선료 지급 방법은?
 [답변]
@@ -11905,13 +9784,13 @@
         </is>
       </c>
     </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
+    <row r="442">
+      <c r="A442" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q26. 공무상 부득이하게 개인 차량을 이용하여 근무지 외 출장을 다녀왔으나, 통행료 및 주차비 영수증을 분</t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B442" t="inlineStr">
         <is>
           <t>[질문] 공무상 부득이하게 개인 차량을 이용하여 근무지 외 출장을 다녀왔으나, 통행료 및 주차비 영수증을 분실하였을 경우, 이에 대한 여비지급이 가능한지?
 [답변]
@@ -11921,13 +9800,13 @@
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
+    <row r="443">
+      <c r="A443" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q27. 장애인증을 제시하여 운임에서 할인을 적용받았다면 장애인 혜택으로 할인된 금액으로 운임을 지급해야 하</t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B443" t="inlineStr">
         <is>
           <t>[질문] 장애인증을 제시하여 운임에서 할인을 적용받았다면 장애인 혜택으로 할인된 금액으로 운임을 지급해야 하는지, 아니면 할인되지 않은 금액으로 운임을 지급해야 하는지?
 [답변]
@@ -11939,13 +9818,13 @@
         </is>
       </c>
     </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
+    <row r="444">
+      <c r="A444" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q28. 거주지가 서울이고 근무지가 대전인 「갑」이 대중교통을 이용하여 대구로 출장을 갈 경우, 거주지인 서</t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B444" t="inlineStr">
         <is>
           <t>[질문] 거주지가 서울이고 근무지가 대전인 「갑」이 대중교통을 이용하여 대구로 출장을 갈 경우, 거주지인 서울에서 직접 출발하는 때의 운임 지급 방법은?
 [답변]
@@ -11959,13 +9838,13 @@
         </is>
       </c>
     </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
+    <row r="445">
+      <c r="A445" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q29. 재택근무 시 업무상 부득이 출장을 가게 될 경우, 출장여비 지급이 가능한지?</t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
+      <c r="B445" t="inlineStr">
         <is>
           <t>[질문] 재택근무 시 업무상 부득이 출장을 가게 될 경우, 출장여비 지급이 가능한지?
 [답변]
@@ -11974,13 +9853,13 @@
         </is>
       </c>
     </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
+    <row r="446">
+      <c r="A446" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q30. 서울에서 제주도로 2박3일 출장 시, 출장 첫날 서울 근무지에서 김포 공항까지 공용차량을 이용한 경</t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
+      <c r="B446" t="inlineStr">
         <is>
           <t>[질문] 서울에서 제주도로 2박3일 출장 시, 출장 첫날 서울 근무지에서 김포 공항까지 공용차량을 이용한 경우, 첫날 일비를 감액하여야 하는지?
 [답변]
@@ -11992,13 +9871,13 @@
         </is>
       </c>
     </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
+    <row r="447">
+      <c r="A447" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q31. 다수의 출장자가 동행하여 근무지 외 출장 시, 개인별로 갹출하기로 하고 버스를 임대하여 이용한 경우</t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
+      <c r="B447" t="inlineStr">
         <is>
           <t>[질문] 다수의 출장자가 동행하여 근무지 외 출장 시, 개인별로 갹출하기로 하고 버스를 임대하여 이용한 경우, 운임 및 일비 지급 방법은?
 [답변]
@@ -12010,13 +9889,13 @@
         </is>
       </c>
     </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
+    <row r="448">
+      <c r="A448" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q32. 자가용을 이용하여 출장을 다녀온 경우, 연료비를 지급받기 위해서는 출장지에 소재한 주유소에서 결제한</t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B448" t="inlineStr">
         <is>
           <t>[질문] 자가용을 이용하여 출장을 다녀온 경우, 연료비를 지급받기 위해서는 출장지에 소재한 주유소에서 결제한 영수증 등을 제출토록 되어있는데, 중간 경유지 또는 출발지에서 결제한 영수증 인정 여부는?
 [답변]
@@ -12031,13 +9910,13 @@
         </is>
       </c>
     </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
+    <row r="449">
+      <c r="A449" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q33. 공용차량에 준하는 별도의 차량을 이용하거나 차량 임차 시 일비 1만원을 감액하도록 되어있는데, 자가</t>
         </is>
       </c>
-      <c r="B620" t="inlineStr">
+      <c r="B449" t="inlineStr">
         <is>
           <t>[질문] 공용차량에 준하는 별도의 차량을 이용하거나 차량 임차 시 일비 1만원을 감액하도록 되어있는데, 자가용을 이용한 출장 시에도 일비를 1/2 감액 해야 하는지?
 [답변]
@@ -12047,13 +9926,13 @@
         </is>
       </c>
     </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
+    <row r="450">
+      <c r="A450" t="inlineStr">
         <is>
           <t xml:space="preserve">[공무원 여비 100문100답] Q34. 거주지가 서울이고 근무지가 세종시인 공무원이, 근무지인 세종시에서 출발하지 않고 거주지인 서울에서 </t>
         </is>
       </c>
-      <c r="B621" t="inlineStr">
+      <c r="B450" t="inlineStr">
         <is>
           <t>[질문] 거주지가 서울이고 근무지가 세종시인 공무원이, 근무지인 세종시에서 출발하지 않고 거주지인 서울에서 출발해서 서울 소재 기관인 국회 등에 출장 후 근무지인 세종시로 복귀하는 경우, 여비 지급 방법은?
 [답변]
@@ -12065,13 +9944,13 @@
         </is>
       </c>
     </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
+    <row r="451">
+      <c r="A451" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q35. 세종시에서 오송역 또는 세종시에서 대전역 구간의 택시비는 운임으로 지급이 가능한지?</t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
+      <c r="B451" t="inlineStr">
         <is>
           <t>[질문] 세종시에서 오송역 또는 세종시에서 대전역 구간의 택시비는 운임으로 지급이 가능한지?
 [답변]
@@ -12084,13 +9963,13 @@
         </is>
       </c>
     </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
+    <row r="452">
+      <c r="A452" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q36. 서울에서 제주도로 1박2일 출장 시, 항공료(왕복 30만원)와 공무 형편상 부득이 2일차 제주도에서</t>
         </is>
       </c>
-      <c r="B623" t="inlineStr">
+      <c r="B452" t="inlineStr">
         <is>
           <t>[질문] 서울에서 제주도로 1박2일 출장 시, 항공료(왕복 30만원)와 공무 형편상 부득이 2일차 제주도에서 렌트차량(20만원 소요)을 이용한 경우, 여비지급 방법은?
 [답변]
@@ -12103,13 +9982,13 @@
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
+    <row r="453">
+      <c r="A453" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q37. 제주도 이외 지역으로의 국내 출장 시에도 항공운임 실비 지급이 가능한지?</t>
         </is>
       </c>
-      <c r="B624" t="inlineStr">
+      <c r="B453" t="inlineStr">
         <is>
           <t>[질문] 제주도 이외 지역으로의 국내 출장 시에도 항공운임 실비 지급이 가능한지?
 [답변]
@@ -12125,13 +10004,13 @@
         </is>
       </c>
     </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
+    <row r="454">
+      <c r="A454" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q38. 출장지에서 전기차 연료 충전 후, 발급되는 영수증에 소재지 등 기재되지 않을 경우, 여비 지급을 위</t>
         </is>
       </c>
-      <c r="B625" t="inlineStr">
+      <c r="B454" t="inlineStr">
         <is>
           <t>[질문] 출장지에서 전기차 연료 충전 후, 발급되는 영수증에 소재지 등 기재되지 않을 경우, 여비 지급을 위한 절차는?
 [답변]
@@ -12143,13 +10022,13 @@
         </is>
       </c>
     </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
+    <row r="455">
+      <c r="A455" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q39. 근무지 외 출장 시 1日 식비(2만원)를 일률적으로 정액 지급하는지?</t>
         </is>
       </c>
-      <c r="B626" t="inlineStr">
+      <c r="B455" t="inlineStr">
         <is>
           <t>[질문] 근무지 외 출장 시 1日 식비(2만원)를 일률적으로 정액 지급하는지?
 [답변]
@@ -12160,13 +10039,13 @@
         </is>
       </c>
     </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
+    <row r="456">
+      <c r="A456" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q40. 근무지 외 출장에서 복귀하여 시간외근무를 한 경우, 시간외근무수당 및 특근매식비 지급이 가능한지?</t>
         </is>
       </c>
-      <c r="B627" t="inlineStr">
+      <c r="B456" t="inlineStr">
         <is>
           <t>[질문] 근무지 외 출장에서 복귀하여 시간외근무를 한 경우, 시간외근무수당 및 특근매식비 지급이 가능한지?
 [답변]
@@ -12180,13 +10059,13 @@
         </is>
       </c>
     </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
+    <row r="457">
+      <c r="A457" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q41. 1박2일 근무지 외 출장 중 식사(첫날 점심, 저녁, 다음날 아침)를 제공받은 경우, 식비 지급 방</t>
         </is>
       </c>
-      <c r="B628" t="inlineStr">
+      <c r="B457" t="inlineStr">
         <is>
           <t>[질문] 1박2일 근무지 외 출장 중 식사(첫날 점심, 저녁, 다음날 아침)를 제공받은 경우, 식비 지급 방법은?
 [답변]
@@ -12197,13 +10076,13 @@
         </is>
       </c>
     </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
+    <row r="458">
+      <c r="A458" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q42. 동일지역 장기체재 중 일비는 감액토록 되어있는데, 식비와 숙박비도 감액해야 하는지?</t>
         </is>
       </c>
-      <c r="B629" t="inlineStr">
+      <c r="B458" t="inlineStr">
         <is>
           <t>[질문] 동일지역 장기체재 중 일비는 감액토록 되어있는데, 식비와 숙박비도 감액해야 하는지?
 [답변]
@@ -12214,13 +10093,13 @@
         </is>
       </c>
     </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
+    <row r="459">
+      <c r="A459" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q43. 그룹1 “교장(남) 1명, 교사(남) 4명”이 부산광역시 공동숙박 (20만원)하고, 그룹2 “교사(</t>
         </is>
       </c>
-      <c r="B630" t="inlineStr">
+      <c r="B459" t="inlineStr">
         <is>
           <t>[질문] 그룹1 “교장(남) 1명, 교사(남) 4명”이 부산광역시 공동숙박 (20만원)하고, 그룹2 “교사(여) 5명”이 부산광역시에서 공동숙박 (25만원)한 경우에 숙박비 추가 지급액은?
 [답변]
@@ -12241,13 +10120,13 @@
         </is>
       </c>
     </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
+    <row r="460">
+      <c r="A460" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q44. 자가(自家) 숙박한 경우 숙박비 지급여부는?</t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
+      <c r="B460" t="inlineStr">
         <is>
           <t>[질문] 자가(自家) 숙박한 경우 숙박비 지급여부는?
 [답변]
@@ -12258,13 +10137,13 @@
         </is>
       </c>
     </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
+    <row r="461">
+      <c r="A461" t="inlineStr">
         <is>
           <t xml:space="preserve">[공무원 여비 100문100답] Q45. 공무원이 산·학·연 논문심사의 건으로 근무지 외 출장(1박2일)을 다녀온 경우, 해당 주관기관에서 </t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
+      <c r="B461" t="inlineStr">
         <is>
           <t>[질문] 공무원이 산·학·연 논문심사의 건으로 근무지 외 출장(1박2일)을 다녀온 경우, 해당 주관기관에서 심사비를 지급받았다면, 숙박비(실비 6만원), 일비(2만원×2일), 운임(실비 3만원) 등 여비지급을 어떻게 해야 하는지?
 [답변]
@@ -12278,13 +10157,13 @@
         </is>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
+    <row r="462">
+      <c r="A462" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q46. 영 [별표1]의 제1호에 해당하는 공무원이 1박2일 숙박비로 15만원을 지출한 경우, 숙박비 지급액</t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
+      <c r="B462" t="inlineStr">
         <is>
           <t>[질문] 영 [별표1]의 제1호에 해당하는 공무원이 1박2일 숙박비로 15만원을 지출한 경우, 숙박비 지급액은?
 [답변]
@@ -12295,13 +10174,13 @@
         </is>
       </c>
     </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
+    <row r="463">
+      <c r="A463" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q47. 근무지 외 출장 시 숙박시설 부족, 성수기 요금 부과 등의 불가피한 사유로 실비상한액을 초과하여 지</t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
+      <c r="B463" t="inlineStr">
         <is>
           <t>[질문] 근무지 외 출장 시 숙박시설 부족, 성수기 요금 부과 등의 불가피한 사유로 실비상한액을 초과하여 지출한 경우, 숙박비 지급 방법은?
 [답변]
@@ -12311,13 +10190,13 @@
         </is>
       </c>
     </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
+    <row r="464">
+      <c r="A464" t="inlineStr">
         <is>
           <t xml:space="preserve">[공무원 여비 100문100답] Q48. 공무원이 2박3일의 제주시 출장기간 동안 첫날은 5만2천원, 둘째날은 4만7천원을 숙박비로 지출한 </t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
+      <c r="B464" t="inlineStr">
         <is>
           <t>[질문] 공무원이 2박3일의 제주시 출장기간 동안 첫날은 5만2천원, 둘째날은 4만7천원을 숙박비로 지출한 경우, 지급가능한 숙박비 총액은?
 [답변]
@@ -12327,13 +10206,13 @@
         </is>
       </c>
     </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
+    <row r="465">
+      <c r="A465" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q49. 국외 출장을 위해 부산에서 서울로 이동할 경우, 항공기 일정상, 부득이하게 숙박이 필요한 경우, 숙</t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
+      <c r="B465" t="inlineStr">
         <is>
           <t>[질문] 국외 출장을 위해 부산에서 서울로 이동할 경우, 항공기 일정상, 부득이하게 숙박이 필요한 경우, 숙박비 지급여부는?
 [답변]
@@ -12343,13 +10222,13 @@
         </is>
       </c>
     </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
+    <row r="466">
+      <c r="A466" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q50. 기상악화 등으로 당초 출장일정을 초과하여 숙박한 경우, 숙박비, 식비, 일비 등의 여비를 추가 지급</t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
+      <c r="B466" t="inlineStr">
         <is>
           <t>[질문] 기상악화 등으로 당초 출장일정을 초과하여 숙박한 경우, 숙박비, 식비, 일비 등의 여비를 추가 지급해야 하는지?
 [답변]
@@ -12360,13 +10239,13 @@
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
+    <row r="467">
+      <c r="A467" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q51. 출장지가 아닌 출장 경로상에 있는 지역에서 숙박을 하였을 경우, 숙박비 지급이 가능한지?</t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
+      <c r="B467" t="inlineStr">
         <is>
           <t>[질문] 출장지가 아닌 출장 경로상에 있는 지역에서 숙박을 하였을 경우, 숙박비 지급이 가능한지?
 [답변]
@@ -12379,13 +10258,13 @@
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
+    <row r="468">
+      <c r="A468" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q52. 2박을 하면서 첫째날에 한 번에 전체 숙박비를 같이 결제하였을 경우, 숙박비 지급여부는?</t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
+      <c r="B468" t="inlineStr">
         <is>
           <t>[질문] 2박을 하면서 첫째날에 한 번에 전체 숙박비를 같이 결제하였을 경우, 숙박비 지급여부는?
 [답변]
@@ -12395,13 +10274,13 @@
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
+    <row r="469">
+      <c r="A469" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q53. 영 [별표2] 국내여비 지급표상 숙박비 실비 상한액이 7만원인 특별시 및 6만원인 광역시에 세종특별</t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
+      <c r="B469" t="inlineStr">
         <is>
           <t>[질문] 영 [별표2] 국내여비 지급표상 숙박비 실비 상한액이 7만원인 특별시 및 6만원인 광역시에 세종특별자치시와 제주특별자치도가 포함되는지?
 [답변]
@@ -12413,13 +10292,13 @@
         </is>
       </c>
     </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
+    <row r="470">
+      <c r="A470" t="inlineStr">
         <is>
           <t xml:space="preserve">[공무원 여비 100문100답] Q54. 도서, 벽지 등 신용카드 가맹점이 없는 지역에서 출장업무를 수행함에 따라 현금으로 숙박비를 지급한 </t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
+      <c r="B470" t="inlineStr">
         <is>
           <t>[질문] 도서, 벽지 등 신용카드 가맹점이 없는 지역에서 출장업무를 수행함에 따라 현금으로 숙박비를 지급한 경우, 숙박비 지급 방법은?
 [답변]
@@ -12431,13 +10310,13 @@
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
+    <row r="471">
+      <c r="A471" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q55. 감사담당 공무원에 대한 숙박비 정액지급이 가능한지?</t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
+      <c r="B471" t="inlineStr">
         <is>
           <t>[질문] 감사담당 공무원에 대한 숙박비 정액지급이 가능한지?
 [답변]
@@ -12462,13 +10341,13 @@
         </is>
       </c>
     </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
+    <row r="472">
+      <c r="A472" t="inlineStr">
         <is>
           <t xml:space="preserve">[공무원 여비 100문100답] Q56. 서울 소재 기관에 근무하는 공무원 「갑」이 3박4일의 부산 출장기간 동안 첫날은 6만원, 둘째날은 </t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
+      <c r="B472" t="inlineStr">
         <is>
           <t>[질문] 서울 소재 기관에 근무하는 공무원 「갑」이 3박4일의 부산 출장기간 동안 첫날은 6만원, 둘째날은 8만원을 숙박비로 지출하고, 셋째날은 친지 숙박을 한 경우, 친지 숙박에 대한 정산 신청을 할 수 있는지?
 [답변]
@@ -12483,13 +10362,13 @@
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
+    <row r="473">
+      <c r="A473" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q57. 국외 출장 시 귀국당일의 일비는 국내 일비와 국외 일비 중 어떤 것을 적용해야 하는지?</t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B473" t="inlineStr">
         <is>
           <t>[질문] 국외 출장 시 귀국당일의 일비는 국내 일비와 국외 일비 중 어떤 것을 적용해야 하는지?
 [답변]
@@ -12501,13 +10380,13 @@
         </is>
       </c>
     </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
+    <row r="474">
+      <c r="A474" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q58. 국외 출장 시 대전근무지에서 인천공항까지의 교통비 지급이 가능한지?</t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
+      <c r="B474" t="inlineStr">
         <is>
           <t>[질문] 국외 출장 시 대전근무지에서 인천공항까지의 교통비 지급이 가능한지?
 [답변]
@@ -12521,13 +10400,13 @@
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
+    <row r="475">
+      <c r="A475" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q59. 국외 출장지에서 부득이하게 자가용을 이용한 경우 연료비, 통행료, 주차비를 지급받을 수 있는지?</t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
+      <c r="B475" t="inlineStr">
         <is>
           <t>[질문] 국외 출장지에서 부득이하게 자가용을 이용한 경우 연료비, 통행료, 주차비를 지급받을 수 있는지?
 [답변]
@@ -12538,13 +10417,13 @@
         </is>
       </c>
     </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
+    <row r="476">
+      <c r="A476" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q60. 국외 출장 중 차량렌트 비용을 기관차원에서 지원하면 일비는 감액해야 하는지?</t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
+      <c r="B476" t="inlineStr">
         <is>
           <t>[질문] 국외 출장 중 차량렌트 비용을 기관차원에서 지원하면 일비는 감액해야 하는지?
 [답변]
@@ -12555,13 +10434,13 @@
         </is>
       </c>
     </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
+    <row r="477">
+      <c r="A477" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q61. 코로나 19 상황 악화, 천재지변 등으로 출장 계획이 취소되어 사전예약 한 항공·숙박시설 등을 취소</t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
+      <c r="B477" t="inlineStr">
         <is>
           <t>[질문] 코로나 19 상황 악화, 천재지변 등으로 출장 계획이 취소되어 사전예약 한 항공·숙박시설 등을 취소해야하는 경우 취소 수수료 지급 가능한지?
 [답변]
@@ -12575,13 +10454,13 @@
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
+    <row r="478">
+      <c r="A478" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q62. 국외 출장 시 항공마일리지를 이용한 좌석 승급 대상 및 요건은?</t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
+      <c r="B478" t="inlineStr">
         <is>
           <t>[질문] 국외 출장 시 항공마일리지를 이용한 좌석 승급 대상 및 요건은?
 [답변]
@@ -12596,13 +10475,13 @@
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="479">
+      <c r="A479" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q63. 총 4박5일 출장 일정(3.1~3.5)이 다음과 같을 경우, 공적 항공마일리지 사용에 따른 일비 추</t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
+      <c r="B479" t="inlineStr">
         <is>
           <t>[질문] 총 4박5일 출장 일정(3.1~3.5)이 다음과 같을 경우, 공적 항공마일리지 사용에 따른 일비 추가지급 방법은? - 3.1~3.3, 서울 → 도쿄, 공적 항공마일리지 사용 - 3.3~3.5, 도쿄 → 베이징 → 서울, 공적 항공마일리지 미사용
 [답변]
@@ -12615,13 +10494,13 @@
         </is>
       </c>
     </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
+    <row r="480">
+      <c r="A480" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q64. 국외 출장(3박4일) 중 여행 첫날 기내에서 식사를 할 경우, 식비를 여행일수에 따라 모두 지급해야</t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
+      <c r="B480" t="inlineStr">
         <is>
           <t>[질문] 국외 출장(3박4일) 중 여행 첫날 기내에서 식사를 할 경우, 식비를 여행일수에 따라 모두 지급해야 하는지?
 [답변]
@@ -12634,13 +10513,13 @@
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
+    <row r="481">
+      <c r="A481" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q65. 국외여비는 사전에 반드시 개인별 통장으로 입금해야 하는지?</t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
+      <c r="B481" t="inlineStr">
         <is>
           <t>[질문] 국외여비는 사전에 반드시 개인별 통장으로 입금해야 하는지?
 [답변]
@@ -12652,13 +10531,13 @@
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
+    <row r="482">
+      <c r="A482" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q66. 상급자와 동행하여 국외 출장을 갈 경우, 숙박비 또는 식비의 모두 상한액을 모두 상향조정할 수 있는</t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B482" t="inlineStr">
         <is>
           <t>[질문] 상급자와 동행하여 국외 출장을 갈 경우, 숙박비 또는 식비의 모두 상한액을 모두 상향조정할 수 있는지?
 [답변]
@@ -12672,13 +10551,13 @@
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="483">
+      <c r="A483" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q67. 국외 출장 후 실비정산을 하려고 하는데 호텔 숙박비에 식대가 포함되어 있는 경우, 이미 지급받은 식</t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B483" t="inlineStr">
         <is>
           <t>[질문] 국외 출장 후 실비정산을 하려고 하는데 호텔 숙박비에 식대가 포함되어 있는 경우, 이미 지급받은 식비에 대한 정산방법은?
 [답변]
@@ -12688,13 +10567,13 @@
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="484">
+      <c r="A484" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q68. 독일로 갑, 을, 병 등 3인이 국외 출장을 다녀온 경우, 갑의 숙박비는 실비상한액을 초과하고 을,</t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B484" t="inlineStr">
         <is>
           <t>[질문] 독일로 갑, 을, 병 등 3인이 국외 출장을 다녀온 경우, 갑의 숙박비는 실비상한액을 초과하고 을, 병의 숙박비는 실비상한액 미만인 경우 정산방법은?
 [답변]
@@ -12707,13 +10586,13 @@
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="485">
+      <c r="A485" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q69. 영국(파운드貨)과 같이 국외여비 지급단위인 달러화를 사용하지 않는 국가로 공무여행을 가는 경우, 여</t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B485" t="inlineStr">
         <is>
           <t>[질문] 영국(파운드貨)과 같이 국외여비 지급단위인 달러화를 사용하지 않는 국가로 공무여행을 가는 경우, 여비 정산방법은?
 [답변]
@@ -12725,13 +10604,13 @@
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="486">
+      <c r="A486" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q70. 스페인으로 2박 3일간 출장을 갈 때 숙박비를 할인정액으로 지급받았는데 현지에서 숙박비가 부족한 경</t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B486" t="inlineStr">
         <is>
           <t>[질문] 스페인으로 2박 3일간 출장을 갈 때 숙박비를 할인정액으로 지급받았는데 현지에서 숙박비가 부족한 경우, 실비 상한액의 1/2에 해당하는 금액을 추가로 지급할 수 있는지?
 [답변]
@@ -12741,13 +10620,13 @@
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="487">
+      <c r="A487" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q71. 2명이 프랑스와 스페인으로 4박 5일간의 일정으로 국외 출장을 갈 때 1명은 숙박비 실비상한액 범위</t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B487" t="inlineStr">
         <is>
           <t>[질문] 2명이 프랑스와 스페인으로 4박 5일간의 일정으로 국외 출장을 갈 때 1명은 숙박비 실비상한액 범위 내에서 실비정산하고, 다른 1명은 할인정액으로 지급할 수 있는지 또는 프랑스에서는 실비상한액을 적용하고 스페인에서는 할인정액으로 지급할 수 있는지?
 [답변]
@@ -12757,13 +10636,13 @@
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="488">
+      <c r="A488" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q72. 국외 숙박비 정산 신청 기한은?</t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
+      <c r="B488" t="inlineStr">
         <is>
           <t>[질문] 국외 숙박비 정산 신청 기한은?
 [답변]
@@ -12775,13 +10654,13 @@
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="489">
+      <c r="A489" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q73. 부득이하게 여행사를 이용하여 국외 출장을 간 경우, 국외 숙박비 지급 방법은?</t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
+      <c r="B489" t="inlineStr">
         <is>
           <t>[질문] 부득이하게 여행사를 이용하여 국외 출장을 간 경우, 국외 숙박비 지급 방법은?
 [답변]
@@ -12794,13 +10673,13 @@
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="490">
+      <c r="A490" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q74. 국외여비 지급 및 정산시, 환율은 현찰 살 때과 현찰 팔 때 중 어느 것을 적용해야 하는지?</t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B490" t="inlineStr">
         <is>
           <t>[질문] 국외여비 지급 및 정산시, 환율은 현찰 살 때과 현찰 팔 때 중 어느 것을 적용해야 하는지?
 [답변]
@@ -12813,13 +10692,13 @@
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="491">
+      <c r="A491" t="inlineStr">
         <is>
           <t xml:space="preserve">[공무원 여비 100문100답] Q75. 1개월전 ‘말레이시아’로의 국외 출장 시에 준비금을 지급받았는데, ‘인도네시아’로의 국외 출장 시 </t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
+      <c r="B491" t="inlineStr">
         <is>
           <t>[질문] 1개월전 ‘말레이시아’로의 국외 출장 시에 준비금을 지급받았는데, ‘인도네시아’로의 국외 출장 시 다시 준비금을 지급받을 수 있는지?
 [답변]
@@ -12829,13 +10708,13 @@
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="492">
+      <c r="A492" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q76. 여행자보험료도 국외 출장 시 준비금으로 지급할 수 있는지?</t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
+      <c r="B492" t="inlineStr">
         <is>
           <t>[질문] 여행자보험료도 국외 출장 시 준비금으로 지급할 수 있는지?
 [답변]
@@ -12847,13 +10726,13 @@
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="493">
+      <c r="A493" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q77. 지방에 근무하는 관계로 직접 서울 소재 대사관을 방문하여 비자를 발급받는 것이 곤란한 경우, 여행사</t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B493" t="inlineStr">
         <is>
           <t>[질문] 지방에 근무하는 관계로 직접 서울 소재 대사관을 방문하여 비자를 발급받는 것이 곤란한 경우, 여행사를 통해 비자를 발급받을 수 있는지?
 [답변]
@@ -12864,13 +10743,13 @@
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="494">
+      <c r="A494" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q78. 대전 소재 A기관장이 인사발령 신고를 위해 서울로 출장(금요일)을 온 후 다음 월요일자로 부산 소재</t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
+      <c r="B494" t="inlineStr">
         <is>
           <t>[질문] 대전 소재 A기관장이 인사발령 신고를 위해 서울로 출장(금요일)을 온 후 다음 월요일자로 부산 소재 B기관장으로 부임(서울자택→부산)한 경우, 출장여비 및 부임여비 지급 방법은?
 [답변]
@@ -12883,13 +10762,13 @@
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="495">
+      <c r="A495" t="inlineStr">
         <is>
           <t xml:space="preserve">[공무원 여비 100문100답] Q79. 서울 소재 기관에 신규채용된 「갑」(서울 거주)와 「을」(부산 거주)에 대해 부임여비를 지급할 수 </t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
+      <c r="B495" t="inlineStr">
         <is>
           <t>[질문] 서울 소재 기관에 신규채용된 「갑」(서울 거주)와 「을」(부산 거주)에 대해 부임여비를 지급할 수 있는지?
 [답변]
@@ -12899,13 +10778,13 @@
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="496">
+      <c r="A496" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q80. 당초 서울의 A기관에서 대전 소재 B기관으로 발령이 난 후 다시 대전 소재 C기관으로 인사발령이 난</t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B496" t="inlineStr">
         <is>
           <t>[질문] 당초 서울의 A기관에서 대전 소재 B기관으로 발령이 난 후 다시 대전 소재 C기관으로 인사발령이 난 경우, 부임여비 지급방법 및 지급기관은?
 [답변]
@@ -12919,13 +10798,13 @@
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="497">
+      <c r="A497" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q81. 서울시 소재 ‘A기관에서 B기관’으로의 인사발령을 계기로, 종전 거주지(또는 주민등록지)인 원주시에</t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B497" t="inlineStr">
         <is>
           <t>[질문] 서울시 소재 ‘A기관에서 B기관’으로의 인사발령을 계기로, 종전 거주지(또는 주민등록지)인 원주시에서 서울시로 이사한 경우, 이전비를 지급할 수 있는지?
 [답변]
@@ -12936,13 +10815,13 @@
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="498">
+      <c r="A498" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q82. 전주의 A기관에서 춘천의 B기관으로 인사발령된 경우, 가정형편 (배우자 직장, 자녀교육 등)상 실제</t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
+      <c r="B498" t="inlineStr">
         <is>
           <t>[질문] 전주의 A기관에서 춘천의 B기관으로 인사발령된 경우, 가정형편 (배우자 직장, 자녀교육 등)상 실제 이사는 서울로 하고, 인사발령 후에는 춘천 소재 관사, 하숙집 등에 거주하는 경우, 서울로의 이전비를 지급할 수 있는지?
 [답변]
@@ -12959,13 +10838,13 @@
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="499">
+      <c r="A499" t="inlineStr">
         <is>
           <t xml:space="preserve">[공무원 여비 100문100답] Q83. 공무원 「을」이 강원도 정선에서 영월로 전보되었으나 태백시로 이전하여 영월로 통근하는 경우, 국내 </t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
+      <c r="B499" t="inlineStr">
         <is>
           <t>[질문] 공무원 「을」이 강원도 정선에서 영월로 전보되었으나 태백시로 이전하여 영월로 통근하는 경우, 국내 이전비를 지급받을 수 있는지?
 [답변]
@@ -12976,13 +10855,13 @@
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="500">
+      <c r="A500" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q84. 공무원 「갑」이 총 5톤의 이사화물을 광주에서 전주로 이전하면서 이사비용 150만원과 사다리차 비용</t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
+      <c r="B500" t="inlineStr">
         <is>
           <t>[질문] 공무원 「갑」이 총 5톤의 이사화물을 광주에서 전주로 이전하면서 이사비용 150만원과 사다리차 비용 20만원이 소요되었을 경우, 「갑」이 지급받을 수 있는 이전비는?
 [답변]
@@ -12992,13 +10871,13 @@
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="501">
+      <c r="A501" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q85. 공무원 「을」이 7.5톤 규모의 이사화물을 서울에서 원주까지 이사 하면서 총 150만원이 소요(사다</t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
+      <c r="B501" t="inlineStr">
         <is>
           <t>[질문] 공무원 「을」이 7.5톤 규모의 이사화물을 서울에서 원주까지 이사 하면서 총 150만원이 소요(사다리차 이용료 포함)되었을 경우, 「을」이 지급받을 수 있는 이전비는?(운송비, 인건비, 사다리차 이용료를 제외한 기타 소요비용 없음)
 [답변]
@@ -13011,13 +10890,13 @@
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="502">
+      <c r="A502" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q86. 공무원 「병」이 10톤 규모의 이사화물을 서울에서 대구까지 이사하면서 총 200만원이 소요(사다리차</t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
+      <c r="B502" t="inlineStr">
         <is>
           <t>[질문] 공무원 「병」이 10톤 규모의 이사화물을 서울에서 대구까지 이사하면서 총 200만원이 소요(사다리차 이용료 포함)되었을 경우, 「병」이 지급받을 수 있는 이전비는?(운송비, 인건비, 사다리차 이용료를 제외한 기타 소요비용 없음)
 [답변]
@@ -13030,13 +10909,13 @@
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="503">
+      <c r="A503" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q87. 부산 소재 A기관에서 대구 소재 B기관으로의 인사발령을 계기로 2021년 1월 31일 대구로 이사를</t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
+      <c r="B503" t="inlineStr">
         <is>
           <t>[질문] 부산 소재 A기관에서 대구 소재 B기관으로의 인사발령을 계기로 2021년 1월 31일 대구로 이사를 한 후, 2021년 3월 1일자로 육아휴직을 시작하여 2021년 11월 30일에 복직한 경우, 이전비 지급신청기한은?
 [답변]
@@ -13047,13 +10926,13 @@
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="504">
+      <c r="A504" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q88. 세종에서 제주시로 인사발령이 나서 제주시로 이사를 하게 되었다. 이전비와 더불어 자가용 승용차 탁송</t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B504" t="inlineStr">
         <is>
           <t>[질문] 세종에서 제주시로 인사발령이 나서 제주시로 이사를 하게 되었다. 이전비와 더불어 자가용 승용차 탁송비도 여비 신청이 가능한지?
 [답변]
@@ -13069,13 +10948,13 @@
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="505">
+      <c r="A505" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q89. 1월 1일자로 발령을 받아 귀국하였으나, 실제 이사일은 6월 1일인 경우, 이전비 지급신청기한은?</t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
+      <c r="B505" t="inlineStr">
         <is>
           <t>[질문] 1월 1일자로 발령을 받아 귀국하였으나, 실제 이사일은 6월 1일인 경우, 이전비 지급신청기한은?
 [답변]
@@ -13088,13 +10967,13 @@
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="506">
+      <c r="A506" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q90. 외국으로 단신부임하는 경우, 이사화물을 항공기로 운송할 수 있는지?</t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
+      <c r="B506" t="inlineStr">
         <is>
           <t>[질문] 외국으로 단신부임하는 경우, 이사화물을 항공기로 운송할 수 있는지?
 [답변]
@@ -13107,13 +10986,13 @@
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="507">
+      <c r="A507" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q91. 공무원 「갑」이 서울에서 로스엔젤레스로 부임명령을 받아 15㎥ 이사화물을 $5,000를 지급하고 이</t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B507" t="inlineStr">
         <is>
           <t>[질문] 공무원 「갑」이 서울에서 로스엔젤레스로 부임명령을 받아 15㎥ 이사화물을 $5,000를 지급하고 이전한 경우, 「갑」이 지급받을 수 있는 국외 이전비는?
 [답변]
@@ -13125,13 +11004,13 @@
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="508">
+      <c r="A508" t="inlineStr">
         <is>
           <t xml:space="preserve">[공무원 여비 100문100답] Q92. 공무원 「을」이 워싱턴에서 베이징으로 전근 명령을 받아 25㎥의 이사화물을 $7,000를 지급하고 </t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
+      <c r="B508" t="inlineStr">
         <is>
           <t>[질문] 공무원 「을」이 워싱턴에서 베이징으로 전근 명령을 받아 25㎥의 이사화물을 $7,000를 지급하고 이전한 경우, 「을」이 지급받을 수 있는 국외 이전비는?
 [답변]
@@ -13145,13 +11024,13 @@
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="509">
+      <c r="A509" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q93. 서울(전임지)에서 대전(신임지)으로 인사발령을 받은 후, 특별한 사정으로 인해 인근 공주시(거주지)</t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
+      <c r="B509" t="inlineStr">
         <is>
           <t>[질문] 서울(전임지)에서 대전(신임지)으로 인사발령을 받은 후, 특별한 사정으로 인해 인근 공주시(거주지)로 이전하는 공무원의 경우, 동반가족에 대해 여비를 지급받을 수 있는지?
 [답변]
@@ -13166,13 +11045,13 @@
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="510">
+      <c r="A510" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q94. 뉴욕에서 근무하는 주재관이 귀국하면서, 런던에서 유학중인 20세의 자녀를 한국으로 불러올 경우, 국</t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
+      <c r="B510" t="inlineStr">
         <is>
           <t>[질문] 뉴욕에서 근무하는 주재관이 귀국하면서, 런던에서 유학중인 20세의 자녀를 한국으로 불러올 경우, 국외 가족여비를 지급할 수 있는지?
 [답변]
@@ -13184,13 +11063,13 @@
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="511">
+      <c r="A511" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q95. 뉴욕에서 근무하는 주재관이 런던에서 유학하고 있는 20세의 자녀를 근무지로 불러올 경우, 국외 가족</t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
+      <c r="B511" t="inlineStr">
         <is>
           <t>[질문] 뉴욕에서 근무하는 주재관이 런던에서 유학하고 있는 20세의 자녀를 근무지로 불러올 경우, 국외 가족여비를 지급할 수 있는지?
 [답변]
@@ -13204,13 +11083,13 @@
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="512">
+      <c r="A512" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q96. 근무조건이 매우 불리한 경우 등 일정한 조건하의 재외공무원이 가족동반으로 전지(轉地) 휴양 등을 갈</t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
+      <c r="B512" t="inlineStr">
         <is>
           <t>[질문] 근무조건이 매우 불리한 경우 등 일정한 조건하의 재외공무원이 가족동반으로 전지(轉地) 휴양 등을 갈 수 있는 횟수 및 여비 지급액은?
 [답변]
@@ -13224,13 +11103,13 @@
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="513">
+      <c r="A513" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q97. 공무원 「갑」이 허위출장으로 8만원의 출장비를 부당수령한 경우, 환수조치 방법은?</t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
+      <c r="B513" t="inlineStr">
         <is>
           <t>[질문] 공무원 「갑」이 허위출장으로 8만원의 출장비를 부당수령한 경우, 환수조치 방법은?
 [답변]
@@ -13244,13 +11123,13 @@
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="514">
+      <c r="A514" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q98. 외국에서 근무중인 공무원이 공무상 출장으로 일시 귀국하였을 경우, 국내에서의 여비 지급 방법은?</t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B514" t="inlineStr">
         <is>
           <t>[질문] 외국에서 근무중인 공무원이 공무상 출장으로 일시 귀국하였을 경우, 국내에서의 여비 지급 방법은?
 [답변]
@@ -13262,13 +11141,13 @@
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="515">
+      <c r="A515" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q99. 과장급 공무원(제2호)이 국장급(제1호라목) 직위에 직무대리 발령을 받아 근무하고 있는 경우, 직무</t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
+      <c r="B515" t="inlineStr">
         <is>
           <t>[질문] 과장급 공무원(제2호)이 국장급(제1호라목) 직위에 직무대리 발령을 받아 근무하고 있는 경우, 직무대리 중인 과장급 공무원의 출장여비는 어느 직급으로 지급해야 하는지?
 [답변]
@@ -13277,13 +11156,13 @@
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="516">
+      <c r="A516" t="inlineStr">
         <is>
           <t>[공무원 여비 100문100답] Q100. 중앙부처 공무원이 파견명령에 의해 ○○시 보건소로 1개월 파견되었을 경우, 1개월 파견기간을 출장처</t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
+      <c r="B516" t="inlineStr">
         <is>
           <t>[질문] 중앙부처 공무원이 파견명령에 의해 ○○시 보건소로 1개월 파견되었을 경우, 1개월 파견기간을 출장처리하여 여비지급이 가능한지?
 [답변]
@@ -13298,13 +11177,13 @@
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="517">
+      <c r="A517" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] [별표 5] 경조사 휴가일수표(제17조제1항 관련)</t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
+      <c r="B517" t="inlineStr">
         <is>
           <t>경조사 휴가일수표(제17조제1항 관련) &lt;개정 2025. 7. 14.&gt;
 1. 결혼
@@ -13321,18 +11200,17 @@
   라. 본인 및 배우자의 형제자매와 그 형제자매의 배우자 : 3일
   마. 본인 및 배우자의 부모의 형제자매와 그 형제자매의 배우자 : 1일
 * 비고 : 입양은 「국내입양에 관한 특별법」 및 「국제입양에 관한 법률」에 따른 입양에 한정하며, 입양 외의 경조사 휴가를 실시할 때 원격지일 경우에는 실제 필요한 왕복소요일수를 가산할 수 있다.
-(검색용 쉬운 표현 — 원문 아님) 부모님이 돌아가셨을 때 = 본인 부모 사망 5일 / 장인·장모·시부모 사망 = 배우자의 부모 5일 / 할아버지·할머니·외할아버지·외할머니 = 조부모·외조부모 3일 / 형·누나·오빠·언니·동생 = 형제자매 3일 / 삼촌·고모·이모·외삼촌 = 부모의 형제자매 1일 / 경조사 휴가, 특별휴가, 결혼식, 장례, 상(喪), 조사, 배우자 출산휴가</t>
-        </is>
-      </c>
-      <c r="C688" t="inlineStr"/>
-    </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+(검색용 쉬운 표현 — 원문 아님) 부모님·아버지·어머니·부친·모친이 돌아가셨을 때(부친상·모친상) = 본인 부모 사망 5일 / 장인·장모·빙부·빙모·시아버지·시어머니·시부모 사망 = 배우자의 부모 5일 / 남편·아내·배우자 사망 = 5일 / 할아버지·할머니·외할아버지·외할머니(조부상·조모상) = 조부모·외조부모 3일 / 아들·딸·사위·며느리 사망 = 자녀와 그 자녀의 배우자 3일 / 형·누나·오빠·언니·동생·처남·처제·시누이·매형·제수 = 형제자매와 그 배우자 3일 / 삼촌·고모·이모·외삼촌·숙부·숙모 = 부모의 형제자매 1일 / 본인 결혼(결혼식) 5일, 자녀 결혼 1일, 아내·배우자 출산(출산휴가) 20일(쌍둥이 등 25일), 입양 20일 / 경조사 휴가, 특별휴가, 장례, 상(喪), 상을 당함, 조사, 경사</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
         <is>
           <t>[경상북도 공무원 복무 조례] [별표 4] 경력직공무원 및 특수경력직공무원 연가가산 방법(제13조 관련)</t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
+      <c r="B518" t="inlineStr">
         <is>
           <t>경력직공무원 및 특수경력직공무원 연가가산 방법(제13조 관련) &lt;개정 2025. 7. 14.&gt;
 1. 민간 경력 인정 대상자
@@ -13343,7 +11221,6 @@
 (검색용 쉬운 표현 — 원문 아님) 민간경력 연가 추가, 경력 있으면 연가 며칠 더, 연가 가산</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel_system/modules/서무규정.xlsx
+++ b/excel_system/modules/서무규정.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C518"/>
+  <dimension ref="A1:C519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11222,6 +11222,36 @@
         </is>
       </c>
     </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>[출장·초과근무 실무] 출장 중 초과근무수당(시간외·휴일근무수당) 병급 지급 가능 여부 — 관외출장(근무지외)·관내출장</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>질문 : 관외출장(근무지 외 출장)이나 관내출장 중 근무시간을 넘겨 일한 경우, 출장여비와 초과근무수당(시간외근무수당·휴일근무수당)을 함께(병급) 받을 수 있는가?
+1. 원칙 — 출장 중 초과근무는 원칙적으로 불인정
+  - "출장기간 중의 초과근무는 원칙적으로 인정되지 않으므로, 국내출장의 경우 시간외근무수당·야간근무수당 및 휴일근무수당은 원칙적으로 지급할 수 없다."
+    (국가공무원 복무·징계 관련 예규 제6장 제3절 '출장과 초과근무'. 지방공무원은 「지방공무원 복무에 관한 예규」와 행정안전부 유권해석이 같은 취지)
+  - 「공무원보수 등의 업무지침」 : "국내출장의 경우 수당 등을 전액 지급하되, 시간외근무수당은 원칙적으로 지급할 수 없음"
+2. 예외 — 병급이 가능한 경우
+  - "출장의 목적상 필연적으로 시간외근무의 발생이 예상되는 경우 시간외근무명령에 따라 출장 중 또는 출장 후 근무시간 외에 근무를 한 자에게는 시간외근무수당 지급 가능" (같은 예규)
+  - 행정안전부 유권해석(출장여비와 초과근무수당 병급 가능여부) 요지 :
+    ① 부서장의 정당한 시간외근무명령이 있을 것
+    ② 출장 목적상 초과근무가 필연적으로 발생할 것으로 예상될 것
+    ③ 엄격하게 적용하며, 단순 이동시간은 초과근무로 인정하지 않음
+3. 출장여비와의 관계
+  - 출장여비(「공무원 여비 규정」 : 운임·일비·식비·숙박비)는 여행 경비이고, 시간외근무수당(「지방공무원 수당 등에 관한 규정」 제15조)은 근무시간 외 근무에 대한 수당으로 근거가 다르다.
+    따라서 위 2.의 예외 요건을 갖춰 초과근무가 인정되면 여비와 함께 지급될 수 있다.
+4. 인정 시간 한도
+  - 시간외근무 인정 한도는 「지방공무원 수당 등에 관한 규정」 제15조 및 지방공무원 보수업무 등 처리지침에 따른다.
+※ 출처 : 국가공무원 복무·징계 관련 예규(제6장 제3절), 공무원보수 등의 업무지침, 행정안전부 유권해석. 적용 전 최신 「지방공무원 복무에 관한 예규」 원문으로 재확인 권장.
+(검색용 쉬운 표현 — 원문 아님) 관외출장 초과수당, 관내출장 초과근무, 출장 가서 야근, 출장 중 시간외근무, 출장 다녀와서 초과근무, 주말·휴일 출장 휴일근무수당, 출장비랑 초과수당 같이 받기, 병급, 중복 지급</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
